--- a/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
+++ b/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,16 +35,16 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
       <color rgb="00898781"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F3E4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,22 +74,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -536,49 +550,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>-0.0667</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>16709800</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.63</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>2829100</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>57.74</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="7" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>现价0.51高于50日均线0.485，SAR转多信号获均线支撑；RSI 57.74处中性偏上，未超买，信号可靠性尚可。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,42 +610,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>16337900</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.66</v>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>-0.1333</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>57198700</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0.16</v>
       </c>
       <c r="H3" t="n">
-        <v>83.92</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
+        <v>31.79</v>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.555</v>
+      <c r="J3" s="9" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0.259</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -633,42 +655,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-0.0306</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>8652600</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.24</v>
+          <t>AXTERIA</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>22612700</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>24.46</v>
       </c>
       <c r="H4" t="n">
-        <v>72.55</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+        <v>86.39</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.318</v>
+      <c r="J4" s="9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.116</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr"/>
+      <c r="M4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -678,42 +700,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JAKS</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>3402400</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.05</v>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>21180800</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.58</v>
       </c>
       <c r="H5" t="n">
-        <v>53.64</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+        <v>70.62</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.147</v>
+      <c r="J5" s="9" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.318</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -723,42 +745,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>597200</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.05</v>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>17412100</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>7.15</v>
       </c>
       <c r="H6" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>5.428</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>5.515</v>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.076</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,45 +790,1703 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>0069</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VINVEST</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>16997800</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H7" t="n">
+        <v>74.81</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>7336100</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H8" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>7071000</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H9" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0187</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BCMALL</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>5023500</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>4623700</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0163</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>4166900</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H12" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>3962800</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H13" t="n">
+        <v>83.92</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>3644100</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H14" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>3191500</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H15" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-0.0235</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>2789300</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H16" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>2520700</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="n">
+        <v>34.39</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SUNLOGY</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.04940000000000001</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>2203000</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H18" t="n">
+        <v>37.96</v>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>5151</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>HEXTAR</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D19" s="9" t="n">
         <v>0.775</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E19" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>548600</v>
-      </c>
-      <c r="G7" s="5" t="n">
+      <c r="F19" s="11" t="n">
+        <v>2108600</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>1509000</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H20" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>1494600</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H21" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>5.416</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>5.513</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5932</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BPURI</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>1443300</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H22" t="n">
+        <v>50.21</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>1406400</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H23" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>3.248</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>1259100</v>
+      </c>
+      <c r="G24" s="12" t="n">
         <v>0.04</v>
       </c>
-      <c r="H7" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>1198800</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H25" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="J25" s="9" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>1159000</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H26" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>2.579</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>1130300</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H27" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>1087400</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>951600</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H29" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>943300</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H30" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>1.964</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>801400</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H31" t="n">
+        <v>37.53</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>769600</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H32" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>769300</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>2.231</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.0174</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>652900</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>636900</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H35" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>9954</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>RGTBHD</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>636500</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H36" t="n">
+        <v>70.76000000000001</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.0345</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>616700</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>596400</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>44.96</v>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>592000</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H39" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>571200</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H40" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>549300</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H41" t="n">
+        <v>47.76</v>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>4.764</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>539700</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H42" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>1.866</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>532100</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>525800</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H44" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>1.502</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
+++ b/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,8 +97,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0515</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2829100</v>
+        <v>3747400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>57.74</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.51高于50日均线0.485，SAR转多信号获均线支撑；RSI 57.74处中性偏上，未超买，信号可靠性尚可。</t>
+          <t>SAR转多信号，RSI 57.74处中性偏上区间，未超买；现价0.51高于50日均线0.485约5%，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-0.1333</v>
+        <v>-0.0667</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>57198700</v>
+        <v>75485900</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="n">
-        <v>31.79</v>
+        <v>32.63</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>0.259</v>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.3571</v>
+        <v>0.2857</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>22612700</v>
+        <v>33292600</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>24.46</v>
+        <v>36.02</v>
       </c>
       <c r="H4" t="n">
-        <v>86.39</v>
+        <v>84.98</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.116</v>
@@ -715,10 +715,10 @@
         <v>-0.0408</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>21180800</v>
+        <v>27706500</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.58</v>
+        <v>0.76</v>
       </c>
       <c r="H5" t="n">
         <v>70.62</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0</v>
+        <v>0.09</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>17412100</v>
+        <v>20141300</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>7.15</v>
+        <v>8.27</v>
       </c>
       <c r="H6" t="n">
-        <v>72.56999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
         <v>0.1667</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>16997800</v>
+        <v>18516000</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>6.52</v>
+        <v>7.11</v>
       </c>
       <c r="H7" t="n">
         <v>74.81</v>
@@ -835,39 +835,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0</v>
+        <v>0.06</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>7336100</v>
+        <v>10691400</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.76</v>
+        <v>1.3</v>
       </c>
       <c r="H8" t="n">
-        <v>21.02</v>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
+        <v>63.07</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.389</v>
+        <v>0.05</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.403</v>
+        <v>0.047</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>7071000</v>
+        <v>9638000</v>
       </c>
       <c r="G9" s="12" t="n">
         <v>0.11</v>
       </c>
       <c r="H9" t="n">
-        <v>53.64</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.21</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.16</v>
+        <v>0.315</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.147</v>
+        <v>0.266</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
+        <v>0.745</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>5023500</v>
+        <v>8185100</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>5.5</v>
+        <v>0.34</v>
       </c>
       <c r="H10" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.41</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.005</v>
+        <v>0.66</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.006</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>4623700</v>
+        <v>7952300</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="H11" t="n">
-        <v>60.52</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
+        <v>39.68</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.316</v>
+        <v>0.285</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.266</v>
+        <v>0.279</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,28 +1015,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0163</v>
+        <v>0.165</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>4166900</v>
+        <v>7531800</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H12" t="n">
-        <v>61.71</v>
+        <v>53.64</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.858</v>
+        <v>0.16</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.763</v>
+        <v>0.147</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,39 +1060,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E13" s="16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>3962800</v>
+        <v>7349100</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.16</v>
+        <v>0.76</v>
       </c>
       <c r="H13" t="n">
-        <v>83.92</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.02</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.66</v>
+        <v>0.389</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.403</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,39 +1105,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.265</v>
+        <v>0.915</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.0185</v>
+        <v>-0.0054</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>3644100</v>
+        <v>6475500</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.34</v>
+        <v>0.09</v>
       </c>
       <c r="H14" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.78</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.286</v>
+        <v>0.859</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.279</v>
+        <v>0.763</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,40 +1150,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>3191500</v>
+        <v>6095700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H15" t="n">
-        <v>59.72</v>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <v>0.385</v>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
     </row>
@@ -1195,39 +1188,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>-0.0235</v>
+        <v>0.455</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>2789300</v>
+        <v>5625600</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.08</v>
+        <v>0.28</v>
       </c>
       <c r="H16" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
+        <v>59.72</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.455</v>
+        <v>0.432</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.474</v>
+        <v>0.385</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1240,39 +1233,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>-0.0166</v>
+        <v>0.005</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>2520700</v>
+        <v>5023500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.24</v>
+        <v>5.5</v>
       </c>
       <c r="H17" t="n">
-        <v>34.39</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
+        <v>47.02</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1.001</v>
+        <v>0.005</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.98</v>
+        <v>0.006</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1285,39 +1278,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>-0.04940000000000001</v>
+        <v>0.11</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2203000</v>
+        <v>4834900</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.29</v>
+        <v>1.08</v>
       </c>
       <c r="H18" t="n">
-        <v>37.96</v>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.55</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.423</v>
+        <v>0.099</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.439</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1330,39 +1323,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>-0.04940000000000001</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>2108600</v>
+        <v>3664000</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.14</v>
+        <v>0.48</v>
       </c>
       <c r="H19" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.96</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.775</v>
+        <v>0.423</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.776</v>
+        <v>0.439</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1375,28 +1368,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E20" s="16" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E20" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1509000</v>
+        <v>3607100</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="H20" t="n">
-        <v>54.27</v>
+        <v>50.44</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1404,10 +1397,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.775</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.776</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1420,39 +1413,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>5.15</v>
+        <v>0.415</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>-0.032</v>
+        <v>-0.0235</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1494600</v>
+        <v>3322500</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="H21" t="n">
-        <v>37.79</v>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
+        <v>36.3</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>5.416</v>
+        <v>0.455</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>5.513</v>
+        <v>0.474</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1465,39 +1458,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.225</v>
+        <v>0.91</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0.0227</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>1443300</v>
+        <v>3264500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1.46</v>
+        <v>0.31</v>
       </c>
       <c r="H22" t="n">
-        <v>50.21</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.65</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.223</v>
+        <v>1.003</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.23</v>
+        <v>0.981</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1510,39 +1503,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0</v>
+        <v>5.15</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>-0.032</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1406400</v>
+        <v>3243600</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H23" t="n">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.79</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>3.795</v>
+        <v>5.416</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>3.248</v>
+        <v>5.513</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1555,33 +1548,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.705</v>
+        <v>0.505</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.0098</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1259100</v>
+        <v>3128800</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
+        <v>0.93</v>
+      </c>
+      <c r="H24" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.437</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1593,39 +1593,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>-0.0098</v>
+        <v>0.17</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1198800</v>
+        <v>3029800</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.35</v>
+        <v>1.36</v>
       </c>
       <c r="H25" t="n">
-        <v>76.12</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.01</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.449</v>
+        <v>0.166</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.437</v>
+        <v>0.156</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1638,28 +1638,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.0117</v>
+        <v>0.635</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1159000</v>
+        <v>2892600</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.37</v>
+        <v>0.27</v>
       </c>
       <c r="H26" t="n">
-        <v>89.7</v>
+        <v>60.81</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>3.049</v>
+        <v>0.624</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.579</v>
+        <v>0.618</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1683,28 +1683,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.0133</v>
+        <v>0.82</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1130300</v>
+        <v>2849000</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H27" t="n">
-        <v>48.14</v>
+        <v>54.27</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.372</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.37</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1728,39 +1728,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1087400</v>
+        <v>2748700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.1</v>
+        <v>0.54</v>
       </c>
       <c r="H28" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.3</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.624</v>
+        <v>0.267</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.618</v>
+        <v>0.269</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1773,39 +1773,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>-0.0256</v>
+        <v>0.375</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>951600</v>
+        <v>2746100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="H29" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.17</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.644</v>
+        <v>0.373</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1818,39 +1818,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>-0.005</v>
+        <v>0.73</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>943300</v>
+        <v>2644400</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.03</v>
+        <v>0.55</v>
       </c>
       <c r="H30" t="n">
-        <v>53.96</v>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
+        <v>46.34</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>1.964</v>
+        <v>0.823</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1.794</v>
+        <v>0.628</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1863,40 +1863,33 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>-0.0423</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>801400</v>
+        <v>2481200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H31" t="n">
-        <v>37.53</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>0.894</v>
-      </c>
-      <c r="K31" s="9" t="n">
-        <v>0.957</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
     </row>
@@ -1908,28 +1901,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>0</v>
+        <v>4.19</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>769600</v>
+        <v>2409600</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="H32" t="n">
-        <v>68.73</v>
+        <v>65.56</v>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
@@ -1937,10 +1930,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.805</v>
+        <v>3.801</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.779</v>
+        <v>3.249</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1953,39 +1946,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>-0.0145</v>
+        <v>2</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.005</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>769300</v>
+        <v>2276600</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H33" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.23</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>2.111</v>
+        <v>1.966</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>2.231</v>
+        <v>1.795</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1998,28 +1991,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>-0.0174</v>
+        <v>0.825</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>652900</v>
+        <v>1990100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="H34" t="n">
-        <v>56.1</v>
+        <v>68.73</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2027,10 +2020,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>1.091</v>
+        <v>0.805</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.056</v>
+        <v>0.779</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2043,40 +2036,36 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>0.006</v>
+        <v>0.225</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>636900</v>
+        <v>1947700</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="H35" t="n">
-        <v>54.95</v>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="n">
-        <v>0.828</v>
-      </c>
-      <c r="K35" s="9" t="n">
-        <v>0.799</v>
-      </c>
+        <v>51.42</v>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
     </row>
@@ -2088,28 +2077,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RGTBHD</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.0737</v>
+        <v>0.37</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>636500</v>
+        <v>1748000</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>2.68</v>
+        <v>0.16</v>
       </c>
       <c r="H36" t="n">
-        <v>70.76000000000001</v>
+        <v>27.15</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2117,10 +2106,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.442</v>
+        <v>0.468</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.372</v>
+        <v>0.583</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2133,39 +2122,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>PCCS</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>-0.0345</v>
+        <v>0.32</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.0667</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>616700</v>
+        <v>1674100</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.13</v>
+        <v>13.28</v>
       </c>
       <c r="H37" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.25</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.821</v>
+        <v>0.286</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.627</v>
+        <v>0.282</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2178,39 +2167,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.265</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>596400</v>
+        <v>1566400</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="H38" t="n">
-        <v>44.96</v>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
+        <v>41.25</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>2.594</v>
+        <v>0.282</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>2.604</v>
+        <v>0.282</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2223,39 +2212,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E39" s="16" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E39" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>592000</v>
+        <v>1521500</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.96</v>
+        <v>0.23</v>
       </c>
       <c r="H39" t="n">
-        <v>59.82</v>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.35</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.314</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.663</v>
+        <v>0.359</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2268,39 +2257,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>0</v>
+        <v>2.47</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>571200</v>
+        <v>1464300</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.27</v>
+        <v>0.08</v>
       </c>
       <c r="H40" t="n">
-        <v>54.73</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.42</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.641</v>
+        <v>2.591</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.628</v>
+        <v>2.559</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2313,39 +2302,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>-0.0062</v>
+        <v>0.225</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>549300</v>
+        <v>1447000</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.02</v>
+        <v>1.46</v>
       </c>
       <c r="H41" t="n">
-        <v>47.76</v>
-      </c>
-      <c r="I41" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.21</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>4.87</v>
+        <v>0.223</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>4.764</v>
+        <v>0.23</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2358,39 +2347,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.0089</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>539700</v>
+        <v>1306600</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="H42" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I42" s="17" t="inlineStr">
+        <v>17.77</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>1.572</v>
+        <v>1.297</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1.866</v>
+        <v>1.501</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2403,39 +2392,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>0</v>
+        <v>3.47</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0146</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>532100</v>
+        <v>1290400</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="H43" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.84999999999999</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.767</v>
+        <v>3.05</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.771</v>
+        <v>2.579</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2448,45 +2437,1350 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>0</v>
+        <v>0.885</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>525800</v>
+        <v>1222400</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="H44" t="n">
-        <v>18.24</v>
-      </c>
-      <c r="I44" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.51</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>1.298</v>
+        <v>0.895</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1.502</v>
+        <v>0.958</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>1137300</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H45" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>1082800</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>2.231</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>-0.0171</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>1037900</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H47" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>1015700</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H48" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7217</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EMETALL</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>1006000</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H49" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>-0.0174</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>863100</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H50" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>812600</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H51" t="n">
+        <v>47.76</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>4.764</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>790800</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H52" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>1.967</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>1.961</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>789200</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H53" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>1.866</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>779300</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>763600</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H55" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>2.289</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>750500</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H56" t="n">
+        <v>44.96</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>712100</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H57" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>9954</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>RGTBHD</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>710000</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H58" t="n">
+        <v>70.06</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>700900</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H59" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>645000</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H60" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>617800</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>53.46</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>609900</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H62" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>600200</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H63" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>2.732</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>2.747</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>592000</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H64" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>572300</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H65" t="n">
+        <v>38.98</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>571200</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H66" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>555200</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H67" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>548000</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H68" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>-0.009399999999999999</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>545100</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H69" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>545000</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H70" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>532200</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H71" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>522400</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H72" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>2.787</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>502000</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H73" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M44"/>
+  <autoFilter ref="A1:M73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
+++ b/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0515</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3747400</v>
+        <v>3949200</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>57.74</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 57.74处中性偏上区间，未超买；现价0.51高于50日均线0.485约5%，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，RSI 57.74处中性偏上区间，现价0.51高于50日均线0.485约5%，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>-0.0667</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>75485900</v>
+        <v>84044000</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H3" t="n">
         <v>32.63</v>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.2857</v>
+        <v>0.3571</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>33292600</v>
+        <v>39087600</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>36.02</v>
+        <v>42.29</v>
       </c>
       <c r="H4" t="n">
-        <v>84.98</v>
+        <v>86.39</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.116</v>
@@ -715,10 +715,10 @@
         <v>-0.0408</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>27706500</v>
+        <v>30860000</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="H5" t="n">
         <v>70.62</v>
@@ -760,10 +760,10 @@
         <v>0.0588</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>20141300</v>
+        <v>21293500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>8.27</v>
+        <v>8.74</v>
       </c>
       <c r="H6" t="n">
         <v>78.40000000000001</v>
@@ -805,10 +805,10 @@
         <v>0.1667</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>18516000</v>
+        <v>18677000</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>7.11</v>
+        <v>7.17</v>
       </c>
       <c r="H7" t="n">
         <v>74.81</v>
@@ -850,10 +850,10 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>10691400</v>
+        <v>16055500</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1.3</v>
+        <v>1.96</v>
       </c>
       <c r="H8" t="n">
         <v>63.07</v>
@@ -880,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.325</v>
+        <v>0.16</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>-0.0152</v>
+        <v>-0.0303</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>9638000</v>
+        <v>10934800</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="H9" t="n">
-        <v>58.21</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.17</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.315</v>
+        <v>0.16</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.266</v>
+        <v>0.147</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.33</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>8185100</v>
+        <v>9904300</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.34</v>
+        <v>0.12</v>
       </c>
       <c r="H10" t="n">
-        <v>84.41</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.52</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.66</v>
+        <v>0.316</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.745</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>7952300</v>
+        <v>9083600</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.75</v>
+        <v>0.38</v>
       </c>
       <c r="H11" t="n">
-        <v>39.68</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.41</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.285</v>
+        <v>0.66</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.279</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,39 +1015,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>7531800</v>
+        <v>8104300</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.12</v>
+        <v>0.76</v>
       </c>
       <c r="H12" t="n">
-        <v>53.64</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.68</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.16</v>
+        <v>0.285</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.147</v>
+        <v>0.279</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1075,10 +1075,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7349100</v>
+        <v>7874100</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>21.02</v>
@@ -1114,19 +1114,19 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>-0.0054</v>
+        <v>0.925</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.0054</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6475500</v>
+        <v>7737900</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H14" t="n">
-        <v>63.78</v>
+        <v>65.45</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.859</v>
+        <v>0.86</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0.763</v>
@@ -1165,10 +1165,10 @@
         <v>-0.0263</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6095700</v>
+        <v>7021700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0</v>
+        <v>0.46</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.011</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>5625600</v>
+        <v>6410500</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="H16" t="n">
-        <v>59.72</v>
+        <v>60.81</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0.385</v>
@@ -1233,39 +1233,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.005</v>
+        <v>0.82</v>
       </c>
       <c r="E17" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5023500</v>
+        <v>5569000</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>5.5</v>
+        <v>0.35</v>
       </c>
       <c r="H17" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.005</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.006</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1278,28 +1278,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.775</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>4834900</v>
+        <v>5218100</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.08</v>
+        <v>0.34</v>
       </c>
       <c r="H18" t="n">
-        <v>66.55</v>
+        <v>50.44</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.099</v>
+        <v>0.775</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.776</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1323,28 +1323,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>-0.04940000000000001</v>
+        <v>0.275</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.0784</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>3664000</v>
+        <v>5137100</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>37.96</v>
+        <v>62.8</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.423</v>
+        <v>0.268</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.439</v>
+        <v>0.27</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1368,39 +1368,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.775</v>
+        <v>0.005</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>3607100</v>
+        <v>5023500</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.23</v>
+        <v>5.5</v>
       </c>
       <c r="H20" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.775</v>
+        <v>0.005</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.776</v>
+        <v>0.006</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1413,40 +1413,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.415</v>
+        <v>0.68</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>-0.0235</v>
+        <v>-0.0423</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>3322500</v>
+        <v>4952500</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H21" t="n">
-        <v>36.3</v>
+        <v>0.14</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J21" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>0.474</v>
-      </c>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
     </row>
@@ -1458,39 +1451,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.91</v>
+        <v>0.11</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0476</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>3264500</v>
+        <v>4915100</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.31</v>
+        <v>1.1</v>
       </c>
       <c r="H22" t="n">
-        <v>36.65</v>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.55</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1.003</v>
+        <v>0.099</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.981</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1503,39 +1496,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>-0.032</v>
+        <v>0.92</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.05139999999999999</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3243600</v>
+        <v>4759600</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.24</v>
+        <v>1.28</v>
       </c>
       <c r="H23" t="n">
-        <v>37.79</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.17</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>5.416</v>
+        <v>0.899</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>5.513</v>
+        <v>0.958</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1548,39 +1541,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>-0.0098</v>
+        <v>0.295</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>3128800</v>
+        <v>4143400</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.93</v>
+        <v>1.22</v>
       </c>
       <c r="H24" t="n">
-        <v>76.12</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.06</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.449</v>
+        <v>0.295</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.437</v>
+        <v>0.295</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1593,39 +1586,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.635</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3029800</v>
+        <v>4132900</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.36</v>
+        <v>0.39</v>
       </c>
       <c r="H25" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.81</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.166</v>
+        <v>0.624</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.156</v>
+        <v>0.618</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1638,39 +1631,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.635</v>
+        <v>0.305</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>2892600</v>
+        <v>4131300</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="H26" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.624</v>
+        <v>0.307</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.618</v>
+        <v>0.302</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1683,39 +1676,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.04940000000000001</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2849000</v>
+        <v>3900600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="H27" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.96</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.423</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.439</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1728,28 +1721,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.0392</v>
+        <v>5.12</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>2748700</v>
+        <v>3797400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.54</v>
+        <v>0.29</v>
       </c>
       <c r="H28" t="n">
-        <v>48.3</v>
+        <v>36.9</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
@@ -1757,10 +1750,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.267</v>
+        <v>5.413</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.269</v>
+        <v>5.512</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1773,39 +1766,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2746100</v>
+        <v>3661800</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="H29" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.3</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.373</v>
+        <v>0.455</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.37</v>
+        <v>0.474</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1818,39 +1811,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.73</v>
+        <v>0.515</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.0069</v>
+        <v>0.0098</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>2644400</v>
+        <v>3579600</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.55</v>
+        <v>1.06</v>
       </c>
       <c r="H30" t="n">
-        <v>46.34</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.16</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.823</v>
+        <v>0.45</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.628</v>
+        <v>0.437</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1863,33 +1856,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>-0.0423</v>
+        <v>0.905</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2481200</v>
+        <v>3492200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.33</v>
+      </c>
+      <c r="H31" t="n">
+        <v>35.79</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="9" t="n"/>
+      <c r="J31" s="9" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0.981</v>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
     </row>
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>4.19</v>
+        <v>0.17</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>0.0145</v>
+        <v>0.0303</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2409600</v>
+        <v>3124600</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.32</v>
+        <v>1.4</v>
       </c>
       <c r="H32" t="n">
-        <v>65.56</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.01</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>3.801</v>
+        <v>0.166</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>3.249</v>
+        <v>0.156</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1946,39 +1946,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>0.005</v>
+        <v>0.405</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>2276600</v>
+        <v>2995200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="H33" t="n">
-        <v>55.23</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.95</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.966</v>
+        <v>0.4</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.795</v>
+        <v>0.383</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1991,39 +1991,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>0</v>
+        <v>0.72</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>1990100</v>
+        <v>2823100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.39</v>
+        <v>0.59</v>
       </c>
       <c r="H34" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.69</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.805</v>
+        <v>0.822</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.779</v>
+        <v>0.627</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2036,36 +2036,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>-0.0217</v>
+        <v>0.375</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1947700</v>
+        <v>2817700</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.09</v>
+        <v>0.41</v>
       </c>
       <c r="H35" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
+        <v>54.17</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.37</v>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
     </row>
@@ -2077,28 +2081,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>2795400</v>
+      </c>
+      <c r="G36" s="12" t="n">
         <v>0.37</v>
       </c>
-      <c r="E36" s="10" t="n">
-        <v>-0.0133</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>1748000</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>0.16</v>
-      </c>
       <c r="H36" t="n">
-        <v>27.15</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2106,10 +2110,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.468</v>
+        <v>3.802</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.583</v>
+        <v>3.249</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2122,40 +2126,36 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PCCS</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>0.0667</v>
+        <v>0.225</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>1674100</v>
+        <v>2693600</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>13.28</v>
+        <v>0.13</v>
       </c>
       <c r="H37" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>0.282</v>
-      </c>
+        <v>51.42</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
     </row>
@@ -2167,39 +2167,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0</v>
+        <v>1.63</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1566400</v>
+        <v>2588300</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="H38" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.41</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.282</v>
+        <v>1.625</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.282</v>
+        <v>1.675</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2212,28 +2212,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1521500</v>
+        <v>2520800</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0.23</v>
       </c>
       <c r="H39" t="n">
-        <v>36.35</v>
+        <v>28.85</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.314</v>
+        <v>0.469</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.359</v>
+        <v>0.583</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2257,28 +2257,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>-0.0159</v>
+        <v>1.99</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1464300</v>
+        <v>2441400</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H40" t="n">
-        <v>42.42</v>
+        <v>54.66</v>
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.591</v>
+        <v>1.965</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.559</v>
+        <v>1.794</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2302,28 +2302,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>PCCS</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.225</v>
+        <v>0.325</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>0.0227</v>
+        <v>0.0833</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1447000</v>
+        <v>2326100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>1.46</v>
+        <v>18.45</v>
       </c>
       <c r="H41" t="n">
-        <v>50.21</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.223</v>
+        <v>0.286</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.23</v>
+        <v>0.282</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2347,39 +2347,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1.11</v>
+        <v>2.01</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>-0.0089</v>
+        <v>-0.029</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1306600</v>
+        <v>2253000</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="H42" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.82</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>1.297</v>
+        <v>2.108</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1.501</v>
+        <v>2.231</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2392,28 +2392,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>3.47</v>
+        <v>2.13</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>0.0146</v>
+        <v>0.0143</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1290400</v>
+        <v>2179500</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.41</v>
+        <v>1.04</v>
       </c>
       <c r="H43" t="n">
-        <v>89.84999999999999</v>
+        <v>54.3</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>3.05</v>
+        <v>2.113</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.579</v>
+        <v>2.077</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2437,28 +2437,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.0114</v>
+        <v>0.825</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1222400</v>
+        <v>2152400</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="H44" t="n">
-        <v>41.51</v>
+        <v>68.73</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.895</v>
+        <v>0.805</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.958</v>
+        <v>0.779</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2482,39 +2482,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
         <v>1.14</v>
       </c>
-      <c r="E45" s="10" t="n">
-        <v>-0.008699999999999999</v>
+      <c r="E45" s="15" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1137300</v>
+        <v>2134100</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H45" t="n">
-        <v>57.55</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.3</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.092</v>
+        <v>1.3</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.056</v>
+        <v>1.502</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2527,28 +2527,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>-0.0145</v>
+        <v>3.47</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.0146</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1082800</v>
+        <v>2094800</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.1</v>
+        <v>0.67</v>
       </c>
       <c r="H46" t="n">
-        <v>37.48</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>2.111</v>
+        <v>3.05</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.231</v>
+        <v>2.579</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2572,28 +2572,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>-0.0171</v>
+        <v>1.39</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0.0146</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1037900</v>
+        <v>1941000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H47" t="n">
-        <v>34.05</v>
+        <v>24.56</v>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.645</v>
+        <v>1.574</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.867</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2617,39 +2617,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.405</v>
+        <v>2.47</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>-0.0122</v>
+        <v>-0.0159</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1015700</v>
+        <v>1727100</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>0.09</v>
       </c>
       <c r="H48" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.42</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.4</v>
+        <v>2.591</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.383</v>
+        <v>2.559</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2662,28 +2662,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.445</v>
+        <v>0.295</v>
       </c>
       <c r="E49" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1006000</v>
+        <v>1664800</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.87</v>
+        <v>0.25</v>
       </c>
       <c r="H49" t="n">
-        <v>68.98999999999999</v>
+        <v>36.35</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.441</v>
+        <v>0.314</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.44</v>
+        <v>0.359</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2707,39 +2707,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>-0.0174</v>
+        <v>1.15</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>863100</v>
+        <v>1601000</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.39</v>
+        <v>0.17</v>
       </c>
       <c r="H50" t="n">
-        <v>29.22</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.07</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1.198</v>
+        <v>1.093</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>1.303</v>
+        <v>1.056</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2752,39 +2752,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>4.82</v>
+        <v>0.865</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>-0.0062</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>812600</v>
+        <v>1594600</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="H51" t="n">
-        <v>47.76</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>4.87</v>
+        <v>0.868</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>4.764</v>
+        <v>0.869</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2797,39 +2797,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>0.0193</v>
+        <v>0.265</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>790800</v>
+        <v>1577100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="H52" t="n">
-        <v>68.97</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.25</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>1.967</v>
+        <v>0.282</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>1.961</v>
+        <v>0.282</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2842,39 +2842,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.0073</v>
+        <v>0.225</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>789200</v>
+        <v>1447000</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.06</v>
+        <v>1.46</v>
       </c>
       <c r="H53" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.21</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>1.571</v>
+        <v>0.223</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>1.866</v>
+        <v>0.23</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2887,39 +2887,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>0.006</v>
+        <v>0.23</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>779300</v>
+        <v>1443300</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.2</v>
+        <v>1.03</v>
       </c>
       <c r="H54" t="n">
-        <v>54.95</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.828</v>
+        <v>0.23</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.799</v>
+        <v>0.238</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2932,39 +2932,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.0126</v>
+        <v>1.14</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>763600</v>
+        <v>1376100</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="H55" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.43</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>2.289</v>
+        <v>1.203</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>2.208</v>
+        <v>1.29</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2977,28 +2977,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>2.54</v>
+        <v>0.755</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0066</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>750500</v>
+        <v>1304100</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H56" t="n">
-        <v>44.96</v>
+        <v>45.8</v>
       </c>
       <c r="I56" s="16" t="inlineStr">
         <is>
@@ -3006,10 +3006,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>2.594</v>
+        <v>0.767</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2.604</v>
+        <v>0.771</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3022,28 +3022,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>0</v>
+        <v>0.895</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>712100</v>
+        <v>1256000</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.09</v>
+        <v>0.72</v>
       </c>
       <c r="H57" t="n">
-        <v>33.75</v>
+        <v>48.61</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.204</v>
+        <v>0.905</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1.29</v>
+        <v>0.892</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3067,28 +3067,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RGTBHD</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.34</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>710000</v>
+        <v>1184600</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>2.98</v>
+        <v>0.26</v>
       </c>
       <c r="H58" t="n">
-        <v>70.06</v>
+        <v>52.96</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.442</v>
+        <v>0.336</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.372</v>
+        <v>0.343</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3112,39 +3112,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.62</v>
+        <v>2.12</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>0.0248</v>
+        <v>0.0242</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>700900</v>
+        <v>1183300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="H59" t="n">
-        <v>36.29</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.69</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.68</v>
+        <v>1.968</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.734</v>
+        <v>1.961</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3157,28 +3157,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.755</v>
+        <v>0.58</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>-0.0066</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>645000</v>
+        <v>1170900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="H60" t="n">
-        <v>45.8</v>
+        <v>34.72</v>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.767</v>
+        <v>0.645</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.771</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3202,28 +3202,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>0</v>
+        <v>2.66</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>617800</v>
+        <v>1088100</v>
       </c>
       <c r="G61" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="H61" t="n">
-        <v>53.46</v>
+        <v>43.55</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>1.175</v>
+        <v>2.732</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.149</v>
+        <v>2.747</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3247,28 +3247,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>0.0429</v>
+        <v>4.73</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>609900</v>
+        <v>1060900</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1.05</v>
+        <v>0.05</v>
       </c>
       <c r="H62" t="n">
-        <v>78.95</v>
+        <v>48.74</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.643</v>
+        <v>4.729</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.614</v>
+        <v>4.812</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3292,28 +3292,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>-0.0075</v>
+        <v>1.57</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.0129</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>600200</v>
+        <v>1010200</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H63" t="n">
-        <v>43.55</v>
+        <v>36.76</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>2.732</v>
+        <v>1.657</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>2.747</v>
+        <v>1.741</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3337,39 +3337,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.695</v>
+        <v>0.445</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>592000</v>
+        <v>1006000</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="H64" t="n">
-        <v>59.82</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.98999999999999</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.441</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.663</v>
+        <v>0.44</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3382,28 +3382,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.805</v>
+        <v>2.55</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>-0.0123</v>
+        <v>-0.0039</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>572300</v>
+        <v>956400</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H65" t="n">
-        <v>38.98</v>
+        <v>45.76</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.882</v>
+        <v>2.594</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.858</v>
+        <v>2.604</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3427,28 +3427,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>0</v>
+        <v>2.42</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>571200</v>
+        <v>940700</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>0.27</v>
       </c>
       <c r="H66" t="n">
-        <v>54.73</v>
+        <v>62.86</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.641</v>
+        <v>2.289</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.628</v>
+        <v>2.208</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3472,28 +3472,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.92</v>
+        <v>0.615</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>555200</v>
+        <v>914400</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="H67" t="n">
-        <v>46.89</v>
+        <v>35.18</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.924</v>
+        <v>0.68</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1.01</v>
+        <v>0.734</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3517,28 +3517,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.865</v>
+        <v>10</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.006</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>548000</v>
+        <v>887200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>46.13</v>
+        <v>48.61</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.868</v>
+        <v>9.997</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.869</v>
+        <v>10.112</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3562,28 +3562,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>0.85</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>545100</v>
+        <v>878300</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H69" t="n">
-        <v>38.96</v>
+        <v>55.8</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.122</v>
+        <v>0.829</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.112</v>
+        <v>0.799</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3607,28 +3607,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.535</v>
+        <v>1.12</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>-0.0183</v>
+        <v>-0.0261</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>545000</v>
+        <v>866300</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.06</v>
+        <v>0.39</v>
       </c>
       <c r="H70" t="n">
-        <v>35.75</v>
+        <v>28.01</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.607</v>
+        <v>1.197</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.616</v>
+        <v>1.303</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3652,28 +3652,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>532200</v>
+        <v>865700</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="H71" t="n">
-        <v>48.61</v>
+        <v>40.01</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.905</v>
+        <v>0.883</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.892</v>
+        <v>0.858</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3697,28 +3697,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>0.0036</v>
+        <v>4.82</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>522400</v>
+        <v>840100</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H72" t="n">
-        <v>51.42</v>
+        <v>47.76</v>
       </c>
       <c r="I72" s="16" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>2.787</v>
+        <v>4.87</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2.69</v>
+        <v>4.764</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3742,28 +3742,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>-0.0179</v>
+        <v>2.78</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>502000</v>
+        <v>823400</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="H73" t="n">
-        <v>47.42</v>
+        <v>50.84</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3771,16 +3771,1096 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>2.786</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.546</v>
+        <v>2.69</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>796600</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>6.087</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>787500</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H75" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>737400</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H76" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>716900</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H77" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>691000</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H78" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>2.065</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>689500</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H79" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="14" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.0315</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>681400</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H80" t="n">
+        <v>51.09</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>672600</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H81" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="14" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>669100</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>630100</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H83" t="n">
+        <v>48.45</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="14" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>622900</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H84" t="n">
+        <v>48.51</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>620100</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H85" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>597000</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H86" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>592800</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H87" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>592500</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H88" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>592000</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H89" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>580900</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H90" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>7.362</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>7.625</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>580400</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H91" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>1.362</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>577900</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H92" t="n">
+        <v>40.13</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>7.409</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>7.819</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>557700</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H93" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>2.481</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>2.646</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>510000</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H94" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>1.206</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.0147</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>505400</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H95" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>2.831</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>501800</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H96" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0239</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ECOMATE</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H97" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M73"/>
+  <autoFilter ref="A1:M97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
+++ b/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,8 +97,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.51</v>
+        <v>0.505</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0515</v>
+        <v>0.0412</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3949200</v>
+        <v>4448300</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>57.74</v>
+        <v>56.25</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.491</v>
+        <v>0.49</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.485</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 57.74处中性偏上区间，现价0.51高于50日均线0.485约5%，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，现价0.505高于50日均线0.485，RSI 56.25处中性区间，未超买，信号技术面较可靠。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>-0.0667</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>84044000</v>
+        <v>87491100</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H3" t="n">
         <v>32.63</v>
@@ -670,10 +670,10 @@
         <v>0.3571</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>39087600</v>
+        <v>43955400</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>42.29</v>
+        <v>47.55</v>
       </c>
       <c r="H4" t="n">
         <v>86.39</v>
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-0.0408</v>
+        <v>-0.0306</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>30860000</v>
+        <v>31330600</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="H5" t="n">
-        <v>70.62</v>
+        <v>72.55</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.419</v>
+        <v>0.42</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0.318</v>
@@ -760,10 +760,10 @@
         <v>0.0588</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>21293500</v>
+        <v>21396800</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>8.74</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>78.40000000000001</v>
@@ -799,19 +799,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.1667</v>
+        <v>0.03</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>18677000</v>
+        <v>20046200</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>7.17</v>
+        <v>7.69</v>
       </c>
       <c r="H7" t="n">
-        <v>74.81</v>
+        <v>70.62</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>16055500</v>
+        <v>16057300</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>1.96</v>
@@ -858,7 +858,7 @@
       <c r="H8" t="n">
         <v>63.07</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -895,10 +895,10 @@
         <v>-0.0303</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>10934800</v>
+        <v>15214500</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H9" t="n">
         <v>51.17</v>
@@ -925,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0</v>
+        <v>0.745</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>9904300</v>
+        <v>11816700</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.12</v>
+        <v>0.49</v>
       </c>
       <c r="H10" t="n">
-        <v>60.52</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.41</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.316</v>
+        <v>0.66</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.266</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.33</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9083600</v>
+        <v>10058800</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="H11" t="n">
-        <v>84.41</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.52</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.66</v>
+        <v>0.316</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,39 +1015,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.38</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>8104300</v>
+        <v>8958000</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="H12" t="n">
-        <v>39.68</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
+        <v>31.76</v>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.285</v>
+        <v>0.39</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.279</v>
+        <v>0.403</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,39 +1060,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E13" s="17" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E13" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7874100</v>
+        <v>8285700</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H13" t="n">
-        <v>21.02</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.86</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.389</v>
+        <v>0.859</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.403</v>
+        <v>0.763</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,28 +1105,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.0054</v>
+        <v>0.82</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>7737900</v>
+        <v>8196000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.1</v>
+        <v>0.51</v>
       </c>
       <c r="H14" t="n">
-        <v>65.45</v>
+        <v>54.27</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.86</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.763</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1159,18 +1159,18 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.185</v>
+        <v>0.18</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.0263</v>
+        <v>-0.0526</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>7021700</v>
+        <v>8194500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
+        <v>0.24</v>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1188,39 +1188,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.46</v>
+        <v>0.27</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>0.011</v>
+        <v>0.0588</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6410500</v>
+        <v>8186900</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.32</v>
+        <v>1.6</v>
       </c>
       <c r="H16" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
+        <v>56.73</v>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.433</v>
+        <v>0.267</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.385</v>
+        <v>0.27</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1233,39 +1233,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5569000</v>
+        <v>8167800</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.35</v>
+        <v>0.77</v>
       </c>
       <c r="H17" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.68</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.285</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.279</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1278,39 +1278,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.022</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>5218100</v>
+        <v>8056800</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="H18" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.85</v>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.775</v>
+        <v>0.433</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.776</v>
+        <v>0.385</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1323,39 +1323,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.0784</v>
+        <v>0.775</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5137100</v>
+        <v>7413200</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H19" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.44</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.268</v>
+        <v>0.775</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.27</v>
+        <v>0.776</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1368,39 +1368,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E20" s="17" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E20" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>5023500</v>
+        <v>6555200</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>5.5</v>
+        <v>0.34</v>
       </c>
       <c r="H20" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
+        <v>47.42</v>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.005</v>
+        <v>0.307</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.006</v>
+        <v>0.302</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1413,33 +1413,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>-0.0423</v>
+        <v>0.92</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.05139999999999999</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4952500</v>
+        <v>5823700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
+        <v>1.56</v>
+      </c>
+      <c r="H21" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.958</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
     </row>
@@ -1451,40 +1458,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.675</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0493</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>4915100</v>
+        <v>5688800</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>66.55</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>0.08400000000000001</v>
-      </c>
+        <v>0.16</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1496,28 +1496,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>0.05139999999999999</v>
+        <v>0.105</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>4759600</v>
+        <v>5592900</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="H23" t="n">
-        <v>52.17</v>
+        <v>62.33</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.899</v>
+        <v>0.099</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.958</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1541,39 +1541,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>-0.0617</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>4143400</v>
+        <v>5347500</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1.22</v>
+        <v>0.7</v>
       </c>
       <c r="H24" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
+        <v>36.95</v>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.295</v>
+        <v>0.422</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.295</v>
+        <v>0.439</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1597,14 +1597,14 @@
       <c r="D25" s="9" t="n">
         <v>0.635</v>
       </c>
-      <c r="E25" s="17" t="n">
+      <c r="E25" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4132900</v>
+        <v>5198300</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.39</v>
+        <v>0.49</v>
       </c>
       <c r="H25" t="n">
         <v>60.81</v>
@@ -1631,39 +1631,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E26" s="17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E26" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4131300</v>
+        <v>5023500</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.21</v>
+        <v>5.5</v>
       </c>
       <c r="H26" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
+        <v>47.02</v>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.307</v>
+        <v>0.005</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.302</v>
+        <v>0.006</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1676,39 +1676,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.04940000000000001</v>
+        <v>0.915</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.011</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3900600</v>
+        <v>4545700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="H27" t="n">
-        <v>37.96</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
+        <v>37.48</v>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.423</v>
+        <v>1.003</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.439</v>
+        <v>0.981</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1730,30 +1730,30 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>5.12</v>
+        <v>5.07</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.047</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3797400</v>
+        <v>4489700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="H28" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
+        <v>35.5</v>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>5.413</v>
+        <v>5.408</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>5.512</v>
+        <v>5.511</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1766,39 +1766,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>-0.0235</v>
+        <v>0.41</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3661800</v>
+        <v>4207800</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="H29" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.71</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.455</v>
+        <v>0.401</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.474</v>
+        <v>0.383</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1811,39 +1811,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>0.0098</v>
+        <v>0.295</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3579600</v>
+        <v>4143400</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="H30" t="n">
-        <v>80.16</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.06</v>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.45</v>
+        <v>0.295</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.437</v>
+        <v>0.295</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1856,39 +1856,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E31" s="17" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E31" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3492200</v>
+        <v>3994600</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.33</v>
+        <v>1.18</v>
       </c>
       <c r="H31" t="n">
-        <v>35.79</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.31999999999999</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.002</v>
+        <v>0.45</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.981</v>
+        <v>0.437</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.42</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3124600</v>
+        <v>3992000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.4</v>
+        <v>0.11</v>
       </c>
       <c r="H32" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
+        <v>37.37</v>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.166</v>
+        <v>0.455</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.156</v>
+        <v>0.475</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1946,28 +1946,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>-0.0122</v>
+        <v>2.14</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.019</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>2995200</v>
+        <v>3822400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.25</v>
+        <v>1.83</v>
       </c>
       <c r="H33" t="n">
-        <v>52.95</v>
+        <v>55.64</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.4</v>
+        <v>2.114</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.383</v>
+        <v>2.078</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1991,39 +1991,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>-0.0069</v>
+        <v>0.375</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>2823100</v>
+        <v>3210500</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.59</v>
+        <v>0.29</v>
       </c>
       <c r="H34" t="n">
-        <v>45.69</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>27.62</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.822</v>
+        <v>0.468</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.627</v>
+        <v>0.583</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2036,39 +2036,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2817700</v>
+        <v>3130000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.41</v>
+        <v>1.4</v>
       </c>
       <c r="H35" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.01</v>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.373</v>
+        <v>0.166</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.37</v>
+        <v>0.156</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2081,40 +2081,36 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.0169</v>
+        <v>0.225</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>2795400</v>
+        <v>3123600</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.37</v>
+        <v>0.15</v>
       </c>
       <c r="H36" t="n">
-        <v>65.76000000000001</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>3.802</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <v>3.249</v>
-      </c>
+        <v>51.42</v>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
     </row>
@@ -2126,36 +2122,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>-0.0217</v>
+        <v>4.18</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2693600</v>
+        <v>3082500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.13</v>
+        <v>0.41</v>
       </c>
       <c r="H37" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="9" t="n"/>
+        <v>65.36</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>3.249</v>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
     </row>
@@ -2167,28 +2167,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>0.0062</v>
+        <v>0.37</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2588300</v>
+        <v>2933800</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.32</v>
+        <v>0.43</v>
       </c>
       <c r="H38" t="n">
-        <v>49.41</v>
+        <v>48.14</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.625</v>
+        <v>0.372</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.675</v>
+        <v>0.37</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2212,39 +2212,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.705</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>-0.0276</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2520800</v>
+        <v>2916400</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.23</v>
+        <v>0.61</v>
       </c>
       <c r="H39" t="n">
-        <v>28.85</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.82</v>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.469</v>
+        <v>0.821</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.583</v>
+        <v>0.627</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2257,39 +2257,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0</v>
+        <v>0.74</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2441400</v>
+        <v>2888300</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="H40" t="n">
-        <v>54.66</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
+        <v>50.67</v>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>1.965</v>
+        <v>0.736</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1.794</v>
+        <v>0.725</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2302,39 +2302,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PCCS</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.325</v>
+        <v>1.4</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>0.0833</v>
+        <v>0.0219</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2326100</v>
+        <v>2874300</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>18.45</v>
+        <v>0.21</v>
       </c>
       <c r="H41" t="n">
-        <v>78.79000000000001</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.96</v>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.286</v>
+        <v>1.575</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.282</v>
+        <v>1.867</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2347,28 +2347,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>-0.029</v>
+        <v>2.17</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0.0483</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2253000</v>
+        <v>2825600</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.2</v>
+        <v>0.46</v>
       </c>
       <c r="H42" t="n">
-        <v>34.82</v>
+        <v>72.84</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.108</v>
+        <v>1.973</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.231</v>
+        <v>1.962</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2392,39 +2392,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0143</v>
+        <v>1.98</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2179500</v>
+        <v>2817400</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1.04</v>
+        <v>0.1</v>
       </c>
       <c r="H43" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.96</v>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.113</v>
+        <v>1.964</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.077</v>
+        <v>1.794</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2437,28 +2437,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0</v>
+        <v>2.01</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>-0.029</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2152400</v>
+        <v>2812300</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="H44" t="n">
-        <v>68.73</v>
+        <v>34.82</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.805</v>
+        <v>2.108</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.779</v>
+        <v>2.231</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2482,39 +2482,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>0.0179</v>
+        <v>0.0123</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2134100</v>
+        <v>2612300</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="H45" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.8</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.3</v>
+        <v>1.625</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.502</v>
+        <v>1.676</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2527,28 +2527,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0.0146</v>
+        <v>0.825</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2094800</v>
+        <v>2606000</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="H46" t="n">
-        <v>89.84999999999999</v>
+        <v>68.73</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>3.05</v>
+        <v>0.805</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.579</v>
+        <v>0.779</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2572,39 +2572,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>PCCS</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1.39</v>
+        <v>0.315</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.0146</v>
+        <v>0.05</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1941000</v>
+        <v>2573900</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.14</v>
+        <v>20.41</v>
       </c>
       <c r="H47" t="n">
-        <v>24.56</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.47</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.574</v>
+        <v>0.285</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1.867</v>
+        <v>0.282</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2617,39 +2617,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>-0.0159</v>
+        <v>0.3</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1727100</v>
+        <v>2426100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="H48" t="n">
-        <v>42.42</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.96</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.591</v>
+        <v>0.315</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2.559</v>
+        <v>0.359</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2662,39 +2662,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E49" s="17" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E49" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1664800</v>
+        <v>2291500</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="H49" t="n">
-        <v>36.35</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.25</v>
+      </c>
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.314</v>
+        <v>0.282</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.359</v>
+        <v>0.282</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2707,28 +2707,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1601000</v>
+        <v>2263300</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="H50" t="n">
-        <v>59.07</v>
+        <v>46.13</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1.093</v>
+        <v>0.868</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>1.056</v>
+        <v>0.869</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2752,28 +2752,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>3.46</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0.0117</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1594600</v>
+        <v>2259300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.08</v>
+        <v>0.72</v>
       </c>
       <c r="H51" t="n">
-        <v>46.13</v>
+        <v>89.7</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.868</v>
+        <v>3.049</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.869</v>
+        <v>2.579</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2797,39 +2797,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>0</v>
+        <v>1.14</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1577100</v>
+        <v>2251100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.22</v>
+        <v>0.36</v>
       </c>
       <c r="H52" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
+        <v>22.3</v>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.282</v>
+        <v>1.3</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.282</v>
+        <v>1.502</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2842,39 +2842,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>0.0227</v>
+        <v>2.48</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1447000</v>
+        <v>2215500</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.46</v>
+        <v>0.11</v>
       </c>
       <c r="H53" t="n">
-        <v>50.21</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.93</v>
+      </c>
+      <c r="I53" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.223</v>
+        <v>2.592</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.23</v>
+        <v>2.559</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2887,39 +2887,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E54" s="17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E54" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1443300</v>
+        <v>1999800</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1.03</v>
+        <v>0.26</v>
       </c>
       <c r="H54" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.75</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.23</v>
+        <v>1.204</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.238</v>
+        <v>1.29</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2932,39 +2932,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>1.15</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1376100</v>
+        <v>1823200</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H55" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.07</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.203</v>
+        <v>1.093</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>1.29</v>
+        <v>1.056</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2977,39 +2977,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.755</v>
+        <v>0.225</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>-0.0066</v>
+        <v>-0.0217</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1304100</v>
+        <v>1534300</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.17</v>
+        <v>1.1</v>
       </c>
       <c r="H56" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.32</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.767</v>
+        <v>0.23</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.771</v>
+        <v>0.237</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3022,39 +3022,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>0.005600000000000001</v>
+        <v>7.1</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1256000</v>
+        <v>1466600</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.72</v>
+        <v>0.09</v>
       </c>
       <c r="H57" t="n">
-        <v>48.61</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
+        <v>31.47</v>
+      </c>
+      <c r="I57" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.905</v>
+        <v>7.359</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.892</v>
+        <v>7.625</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3067,28 +3067,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1184600</v>
+        <v>1447000</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.26</v>
+        <v>1.46</v>
       </c>
       <c r="H58" t="n">
-        <v>52.96</v>
+        <v>50.21</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.336</v>
+        <v>0.223</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.343</v>
+        <v>0.23</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3112,39 +3112,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>0.0242</v>
+        <v>2.37</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1183300</v>
+        <v>1441500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="H59" t="n">
-        <v>69.69</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.5</v>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.968</v>
+        <v>2.432</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.961</v>
+        <v>2.412</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3157,39 +3157,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.58</v>
+        <v>4.8</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1170900</v>
+        <v>1371800</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="H60" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
+        <v>46.64</v>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.645</v>
+        <v>4.868</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>4.763</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3202,39 +3202,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>-0.0075</v>
+        <v>2.04</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1088100</v>
+        <v>1369600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.1</v>
+        <v>0.34</v>
       </c>
       <c r="H61" t="n">
-        <v>43.55</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
+        <v>48.91</v>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>2.732</v>
+        <v>2.039</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>2.747</v>
+        <v>2.064</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         <v>-0.0042</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1060900</v>
+        <v>1349900</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H62" t="n">
         <v>48.74</v>
@@ -3292,39 +3292,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.57</v>
+        <v>0.345</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.0129</v>
+        <v>0.0147</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1010200</v>
+        <v>1348300</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="H63" t="n">
-        <v>36.76</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.71</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.657</v>
+        <v>0.337</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.741</v>
+        <v>0.343</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3337,39 +3337,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>0</v>
+        <v>2.53</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.0117</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1006000</v>
+        <v>1334900</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.87</v>
+        <v>0.23</v>
       </c>
       <c r="H64" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.2</v>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.441</v>
+        <v>2.593</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.44</v>
+        <v>2.604</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3382,39 +3382,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2.55</v>
+        <v>0.755</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>-0.0039</v>
+        <v>-0.0066</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>956400</v>
+        <v>1324100</v>
       </c>
       <c r="G65" s="12" t="n">
         <v>0.17</v>
       </c>
       <c r="H65" t="n">
-        <v>45.76</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
+        <v>45.8</v>
+      </c>
+      <c r="I65" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.594</v>
+        <v>0.767</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.604</v>
+        <v>0.771</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3427,39 +3427,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.42</v>
+        <v>0.825</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>0.0126</v>
+        <v>0.0123</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>940700</v>
+        <v>1311800</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="H66" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.57</v>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.289</v>
+        <v>0.884</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.208</v>
+        <v>0.859</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3472,40 +3472,38 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.615</v>
+        <v>0.37</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>0.0165</v>
+        <v>0.0423</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>914400</v>
+        <v>1301500</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="H67" t="n">
-        <v>35.18</v>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.24</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="K67" s="9" t="n">
-        <v>0.734</v>
-      </c>
+        <v>0.337</v>
+      </c>
+      <c r="K67" s="9" t="n"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
     </row>
@@ -3517,39 +3515,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>-0.006</v>
+        <v>-0.0037</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>887200</v>
+        <v>1283300</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="H68" t="n">
-        <v>48.61</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.27</v>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>9.997</v>
+        <v>2.733</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>10.112</v>
+        <v>2.747</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3562,39 +3560,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.85</v>
+        <v>0.895</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>0.0119</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>878300</v>
+        <v>1256000</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.23</v>
+        <v>0.72</v>
       </c>
       <c r="H69" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
+        <v>48.61</v>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.829</v>
+        <v>0.905</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.799</v>
+        <v>0.892</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3607,39 +3605,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>-0.0261</v>
+        <v>1.57</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.0129</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>866300</v>
+        <v>1241400</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="H70" t="n">
-        <v>28.01</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
+        <v>36.76</v>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.197</v>
+        <v>1.657</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.303</v>
+        <v>1.741</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3652,39 +3650,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E71" s="17" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E71" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>865700</v>
+        <v>1240700</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H71" t="n">
-        <v>40.01</v>
-      </c>
-      <c r="I71" s="16" t="inlineStr">
+        <v>35.41</v>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.883</v>
+        <v>0.646</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.858</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3697,39 +3695,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>-0.0062</v>
+        <v>2.42</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>840100</v>
+        <v>1216500</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.04</v>
+        <v>0.35</v>
       </c>
       <c r="H72" t="n">
-        <v>47.76</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.86</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>4.87</v>
+        <v>2.289</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>4.764</v>
+        <v>2.208</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3742,39 +3740,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>0</v>
+        <v>5.74</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>-0.0017</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>823400</v>
+        <v>1128300</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H73" t="n">
-        <v>50.84</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.86</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>2.786</v>
+        <v>5.828</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>2.69</v>
+        <v>6.087</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3787,39 +3785,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>0.0017</v>
+        <v>1.13</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>-0.0174</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>796600</v>
+        <v>1123600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.1</v>
+        <v>0.51</v>
       </c>
       <c r="H74" t="n">
-        <v>41.18</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.22</v>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>5.83</v>
+        <v>1.198</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>6.087</v>
+        <v>1.303</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3832,39 +3830,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>-0.0061</v>
+        <v>0.45</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>787500</v>
+        <v>1123000</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.27</v>
+        <v>0.12</v>
       </c>
       <c r="H75" t="n">
-        <v>29.37</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
+        <v>42.42</v>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.867</v>
+        <v>0.492</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.931</v>
+        <v>0.469</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3877,39 +3875,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0.0429</v>
+        <v>0.865</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>737400</v>
+        <v>1121000</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1.27</v>
+        <v>0.38</v>
       </c>
       <c r="H76" t="n">
-        <v>78.95</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.44</v>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.643</v>
+        <v>0.866</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.614</v>
+        <v>0.861</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3922,39 +3920,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E77" s="17" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>716900</v>
+        <v>1049300</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="H77" t="n">
-        <v>40.12</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.18</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.123</v>
+        <v>0.429</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.112</v>
+        <v>0.418</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3967,39 +3965,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0.009899999999999999</v>
+        <v>10</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>691000</v>
+        <v>1034800</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H78" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.61</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>2.04</v>
+        <v>9.997</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2.065</v>
+        <v>10.112</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4012,28 +4010,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.445</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>689500</v>
+        <v>1008500</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.32</v>
+        <v>0.88</v>
       </c>
       <c r="H79" t="n">
-        <v>51.65</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4041,10 +4039,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.64</v>
+        <v>0.441</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.628</v>
+        <v>0.44</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4057,39 +4055,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>-0.0315</v>
+        <v>2.79</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>681400</v>
+        <v>1002500</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="H80" t="n">
-        <v>51.09</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.42</v>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>1.242</v>
+        <v>2.787</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1.114</v>
+        <v>2.69</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4102,39 +4100,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.695</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>-0.0071</v>
+        <v>-0.0061</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>672600</v>
+        <v>972700</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="H81" t="n">
-        <v>37.05</v>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
+        <v>29.37</v>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.755</v>
+        <v>0.867</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.768</v>
+        <v>0.931</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4147,39 +4145,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0303</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>669100</v>
+        <v>958300</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>54.86</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.05</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1.176</v>
+        <v>1.364</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.149</v>
+        <v>1.439</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4192,39 +4190,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>-0.0136</v>
+        <v>0.74</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>630100</v>
+        <v>955000</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.05</v>
+        <v>1.64</v>
       </c>
       <c r="H83" t="n">
-        <v>48.45</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.09999999999999</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.735</v>
+        <v>0.644</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.725</v>
+        <v>0.615</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4237,39 +4235,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0164</v>
+        <v>0.0119</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>622900</v>
+        <v>952100</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.61</v>
+        <v>0.25</v>
       </c>
       <c r="H84" t="n">
-        <v>48.51</v>
-      </c>
-      <c r="I84" s="16" t="inlineStr">
+        <v>55.8</v>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.925</v>
+        <v>0.829</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.011</v>
+        <v>0.799</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4282,39 +4280,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>-0.0068</v>
+        <v>0.61</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>620100</v>
+        <v>949900</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.11</v>
+        <v>0.31</v>
       </c>
       <c r="H85" t="n">
-        <v>49.32</v>
-      </c>
-      <c r="I85" s="16" t="inlineStr">
+        <v>34.03</v>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.737</v>
+        <v>0.679</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.734</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4327,39 +4325,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>-0.0179</v>
+        <v>-0.0052</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>597000</v>
+        <v>882700</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
       <c r="H86" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.51</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.546</v>
+        <v>0.892</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4372,39 +4370,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>2.38</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>592800</v>
+        <v>851300</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="H87" t="n">
-        <v>47.92</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
+        <v>33.86</v>
+      </c>
+      <c r="I87" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.548</v>
+        <v>2.481</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.525</v>
+        <v>2.646</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4417,39 +4415,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>-0.0092</v>
+        <v>1.19</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>592500</v>
+        <v>782300</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="H88" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="I88" s="16" t="inlineStr">
+        <v>53.46</v>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.607</v>
+        <v>1.175</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.616</v>
+        <v>1.149</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4462,39 +4460,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>0</v>
+        <v>1.23</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>-0.0315</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>592000</v>
+        <v>734000</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.96</v>
+        <v>0.21</v>
       </c>
       <c r="H89" t="n">
-        <v>59.82</v>
-      </c>
-      <c r="I89" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.09</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>1.242</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.663</v>
+        <v>1.114</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4507,39 +4505,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>-0.0028</v>
+        <v>7.34</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0.0027</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>580900</v>
+        <v>718900</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H90" t="n">
-        <v>32.51</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.43</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>7.362</v>
+        <v>7.411</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>7.625</v>
+        <v>7.819</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4552,39 +4550,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E91" s="15" t="n">
-        <v>0.0152</v>
+        <v>1.05</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>580400</v>
+        <v>717800</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="H91" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
+        <v>38.96</v>
+      </c>
+      <c r="I91" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.362</v>
+        <v>1.122</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.438</v>
+        <v>1.112</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4597,39 +4595,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>0</v>
+        <v>0.53</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.0275</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>577900</v>
+        <v>708500</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H92" t="n">
-        <v>40.13</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.15</v>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>7.409</v>
+        <v>0.606</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>7.819</v>
+        <v>0.616</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4642,39 +4640,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>557700</v>
+        <v>689500</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.14</v>
+        <v>0.32</v>
       </c>
       <c r="H93" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.65</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.481</v>
+        <v>0.64</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>2.646</v>
+        <v>0.628</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4687,39 +4685,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0.008</v>
+        <v>6.32</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>510000</v>
+        <v>682000</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H94" t="n">
-        <v>56.88</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.55</v>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.227</v>
+        <v>6.345</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.206</v>
+        <v>6.647</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4732,39 +4730,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>2.68</v>
+        <v>0.725</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>-0.0147</v>
+        <v>-0.0068</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>505400</v>
+        <v>681400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="H95" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="I95" s="16" t="inlineStr">
+        <v>49.32</v>
+      </c>
+      <c r="I95" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>2.831</v>
+        <v>0.737</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>2.97</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4777,39 +4775,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.955</v>
+        <v>0.695</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>-0.0104</v>
+        <v>-0.0071</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>501800</v>
+        <v>677600</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="H96" t="n">
-        <v>58.46</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.05</v>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.892</v>
+        <v>0.768</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4822,45 +4820,405 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.925</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>500000</v>
+        <v>638600</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.17</v>
+        <v>0.62</v>
       </c>
       <c r="H97" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I97" s="16" t="inlineStr">
+        <v>47.71</v>
+      </c>
+      <c r="I97" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.866</v>
+        <v>0.924</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.861</v>
+        <v>1.01</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>637800</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H98" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>-0.0268</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>618000</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H99" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="I99" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>593000</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H100" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>591100</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H101" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="I101" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>7.051</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>7.494</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>-0.0147</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>585800</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H102" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>2.831</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>565400</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H103" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>562400</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H104" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="I104" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>3.641</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>527300</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H105" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M97"/>
+  <autoFilter ref="A1:M105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
+++ b/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M105"/>
+  <dimension ref="A1:M128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0412</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4448300</v>
+        <v>4946400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>56.25</v>
@@ -598,54 +598,62 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.505高于50日均线0.485，RSI 56.25处中性区间，未超买，信号技术面较可靠。</t>
+          <t>SAR转多信号，现价0.505高于50日均线0.485，RSI 56.25处中性区间未超买，信号技术面可靠性尚可。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>-0.0667</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>87491100</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H3" t="n">
-        <v>32.63</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1160700</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J3" s="9" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>RSI 80.62 已处超买区，现价高于50日均线约21%，SAR转多信号可靠性受超买制约。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,28 +663,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>0.3571</v>
+        <v>0.065</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>-0.1333</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>43955400</v>
+        <v>90252500</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>47.55</v>
+        <v>0.24</v>
       </c>
       <c r="H4" t="n">
-        <v>86.39</v>
+        <v>31.79</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -684,10 +692,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.12</v>
+        <v>0.098</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.116</v>
+        <v>0.259</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -700,28 +708,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>-0.0306</v>
+        <v>0.19</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.3571</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>31330600</v>
+        <v>51401400</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.86</v>
+        <v>55.61</v>
       </c>
       <c r="H5" t="n">
-        <v>72.55</v>
+        <v>86.39</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -729,10 +737,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.42</v>
+        <v>0.12</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.318</v>
+        <v>0.116</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -745,28 +753,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.475</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>-0.0306</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>21396800</v>
+        <v>36225400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>8.779999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="H6" t="n">
-        <v>78.40000000000001</v>
+        <v>72.55</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -774,10 +782,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.078</v>
+        <v>0.42</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.076</v>
+        <v>0.318</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,28 +798,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0069</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VINVEST</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0</v>
+        <v>0.155</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-0.06059999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>20046200</v>
+        <v>27502300</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>7.69</v>
+        <v>0.44</v>
       </c>
       <c r="H7" t="n">
-        <v>70.62</v>
+        <v>48.93</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -819,10 +827,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.019</v>
+        <v>0.159</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.018</v>
+        <v>0.147</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,39 +843,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0588</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>16057300</v>
+        <v>21798800</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1.96</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>63.07</v>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.05</v>
+        <v>0.078</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.047</v>
+        <v>0.076</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,28 +888,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0069</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>VINVEST</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>-0.0303</v>
+        <v>0.035</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.1667</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>15214500</v>
+        <v>20055200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.24</v>
+        <v>7.7</v>
       </c>
       <c r="H9" t="n">
-        <v>51.17</v>
+        <v>74.81</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -909,10 +917,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.16</v>
+        <v>0.019</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.147</v>
+        <v>0.018</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,39 +933,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.055</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>11816700</v>
+        <v>16157300</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.49</v>
+        <v>1.97</v>
       </c>
       <c r="H10" t="n">
-        <v>84.41</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.63</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.66</v>
+        <v>0.049</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.047</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,39 +978,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.0135</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>10058800</v>
+        <v>12969200</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="H11" t="n">
-        <v>60.52</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.87</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.316</v>
+        <v>0.661</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.266</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1030,10 +1038,10 @@
         <v>0.0133</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>8958000</v>
+        <v>11507600</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.93</v>
+        <v>1.19</v>
       </c>
       <c r="H12" t="n">
         <v>31.76</v>
@@ -1060,39 +1068,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>8285700</v>
+        <v>10782100</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.11</v>
+        <v>1.01</v>
       </c>
       <c r="H13" t="n">
-        <v>64.86</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.24</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.859</v>
+        <v>0.286</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.763</v>
+        <v>0.279</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,39 +1113,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.82</v>
+        <v>0.33</v>
       </c>
       <c r="E14" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>8196000</v>
+        <v>10299500</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.51</v>
+        <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.52</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.316</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.266</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,33 +1158,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>-0.0526</v>
+        <v>0.82</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>8194500</v>
+        <v>10114500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="H15" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.8139999999999999</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
     </row>
@@ -1188,28 +1203,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.305</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>8186900</v>
+        <v>9491200</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1.6</v>
+        <v>0.49</v>
       </c>
       <c r="H16" t="n">
-        <v>56.73</v>
+        <v>47.42</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1217,10 +1232,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.267</v>
+        <v>0.307</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.27</v>
+        <v>0.302</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1233,39 +1248,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.92</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8167800</v>
+        <v>8900600</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.77</v>
+        <v>0.12</v>
       </c>
       <c r="H17" t="n">
-        <v>39.68</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.86</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.285</v>
+        <v>0.859</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.279</v>
+        <v>0.763</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1278,28 +1293,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.465</v>
+        <v>0.27</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0.022</v>
+        <v>0.0588</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>8056800</v>
+        <v>8900500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.4</v>
+        <v>1.74</v>
       </c>
       <c r="H18" t="n">
-        <v>61.85</v>
+        <v>56.73</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -1307,10 +1322,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.433</v>
+        <v>0.267</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.385</v>
+        <v>0.27</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1323,39 +1338,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.022</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7413200</v>
+        <v>8792100</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="H19" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.85</v>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.775</v>
+        <v>0.433</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.776</v>
+        <v>0.385</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1368,39 +1383,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.305</v>
+        <v>0.775</v>
       </c>
       <c r="E20" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>6555200</v>
+        <v>8344200</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.34</v>
+        <v>0.54</v>
       </c>
       <c r="H20" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.44</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.307</v>
+        <v>0.775</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.302</v>
+        <v>0.776</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1413,40 +1428,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.05139999999999999</v>
+        <v>0.185</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5823700</v>
+        <v>8324500</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="H21" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>0.899</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>0.958</v>
-      </c>
+        <v>0.24</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
     </row>
@@ -1458,33 +1466,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.675</v>
+        <v>5.04</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>-0.0493</v>
+        <v>-0.0526</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5688800</v>
+        <v>7164400</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.16</v>
+        <v>0.54</v>
+      </c>
+      <c r="H22" t="n">
+        <v>34.72</v>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="J22" s="9" t="n">
+        <v>5.405</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>5.511</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1496,40 +1511,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>-0.0423</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5592900</v>
+        <v>6295000</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H23" t="n">
-        <v>62.33</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>0.08400000000000001</v>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1541,39 +1549,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>-0.0617</v>
+        <v>0.915</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0.0457</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5347500</v>
+        <v>6222100</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.7</v>
+        <v>1.67</v>
       </c>
       <c r="H24" t="n">
-        <v>36.95</v>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.89</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.422</v>
+        <v>0.898</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.439</v>
+        <v>0.958</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1586,39 +1594,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0</v>
+        <v>0.39</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>5198300</v>
+        <v>6196100</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.02</v>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.624</v>
+        <v>0.423</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.618</v>
+        <v>0.439</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1631,39 +1639,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>0</v>
+        <v>0.11</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>5023500</v>
+        <v>5716500</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>5.5</v>
+        <v>1.28</v>
       </c>
       <c r="H26" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.55</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.005</v>
+        <v>0.099</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.006</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1676,39 +1684,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.011</v>
+        <v>0.635</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4545700</v>
+        <v>5608300</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="H27" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.81</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1.003</v>
+        <v>0.624</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.981</v>
+        <v>0.618</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1721,39 +1729,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>-0.047</v>
+        <v>0.41</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4489700</v>
+        <v>5465200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="H28" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.71</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>5.408</v>
+        <v>0.401</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>5.511</v>
+        <v>0.383</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1766,39 +1774,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>0</v>
+        <v>1.99</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>-0.0386</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4207800</v>
+        <v>5445000</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="H29" t="n">
-        <v>54.71</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.25</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.401</v>
+        <v>2.106</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.383</v>
+        <v>2.23</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1811,28 +1819,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.295</v>
+        <v>0.005</v>
       </c>
       <c r="E30" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4143400</v>
+        <v>5345500</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.22</v>
+        <v>5.85</v>
       </c>
       <c r="H30" t="n">
-        <v>49.06</v>
+        <v>47.02</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
@@ -1840,10 +1848,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.295</v>
+        <v>0.005</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.295</v>
+        <v>0.006</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1856,39 +1864,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>0</v>
+        <v>0.93</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0276</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3994600</v>
+        <v>5294700</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.18</v>
+        <v>0.5</v>
       </c>
       <c r="H31" t="n">
-        <v>79.31999999999999</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.86</v>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.45</v>
+        <v>1.005</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.437</v>
+        <v>0.981</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1901,39 +1909,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.42</v>
+        <v>0.155</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>-0.0118</v>
+        <v>-0.0313</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3992000</v>
+        <v>5156100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="H32" t="n">
-        <v>37.37</v>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.73</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.455</v>
+        <v>0.156</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.475</v>
+        <v>0.156</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1946,28 +1954,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.14</v>
+        <v>0.52</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>0.019</v>
+        <v>0.0196</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3822400</v>
+        <v>4510600</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="H33" t="n">
-        <v>55.64</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1975,10 +1983,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>2.114</v>
+        <v>0.451</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>2.078</v>
+        <v>0.437</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1991,28 +1999,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3210500</v>
+        <v>4337800</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="H34" t="n">
-        <v>27.62</v>
+        <v>48.14</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2020,10 +2028,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.468</v>
+        <v>0.372</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.583</v>
+        <v>0.37</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2036,39 +2044,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.865</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3130000</v>
+        <v>4231300</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="H35" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.166</v>
+        <v>0.868</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.156</v>
+        <v>0.869</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2081,36 +2089,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>-0.0217</v>
+        <v>1.41</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0292</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3123600</v>
+        <v>4223300</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="H36" t="n">
-        <v>51.42</v>
+        <v>27.3</v>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
+      <c r="J36" s="9" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>1.867</v>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
     </row>
@@ -2122,39 +2134,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>0.0121</v>
+        <v>0.295</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3082500</v>
+        <v>4143400</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.41</v>
+        <v>1.22</v>
       </c>
       <c r="H37" t="n">
-        <v>65.36</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.06</v>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>3.8</v>
+        <v>0.295</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>3.249</v>
+        <v>0.295</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2167,39 +2179,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>-0.0133</v>
+        <v>0.195</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2933800</v>
+        <v>4128700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.43</v>
+        <v>0.22</v>
       </c>
       <c r="H38" t="n">
-        <v>48.14</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.92</v>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.372</v>
+        <v>0.209</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.37</v>
+        <v>0.229</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2212,28 +2224,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.705</v>
+        <v>0.73</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>-0.0276</v>
+        <v>-0.0068</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2916400</v>
+        <v>4065700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="H39" t="n">
-        <v>44.82</v>
+        <v>49.17</v>
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
@@ -2241,10 +2253,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.821</v>
+        <v>0.735</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.627</v>
+        <v>0.725</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2257,39 +2269,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.74</v>
+        <v>0.38</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.0133</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2888300</v>
+        <v>4038800</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="H40" t="n">
-        <v>50.67</v>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>28.85</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.736</v>
+        <v>0.469</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.725</v>
+        <v>0.583</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2302,28 +2314,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.0219</v>
+        <v>0.42</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2874300</v>
+        <v>3994700</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="H41" t="n">
-        <v>25.96</v>
+        <v>37.37</v>
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
@@ -2331,10 +2343,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.575</v>
+        <v>0.455</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1.867</v>
+        <v>0.475</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2347,28 +2359,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>0.0483</v>
+        <v>0.019</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2825600</v>
+        <v>3885400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.46</v>
+        <v>1.86</v>
       </c>
       <c r="H42" t="n">
-        <v>72.84</v>
+        <v>55.64</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2376,10 +2388,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>1.973</v>
+        <v>2.114</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1.962</v>
+        <v>2.078</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2392,39 +2404,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>-0.005</v>
+        <v>2.17</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0483</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2817400</v>
+        <v>3827000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="H43" t="n">
-        <v>53.96</v>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.84</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.964</v>
+        <v>1.973</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.794</v>
+        <v>1.962</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2437,40 +2449,36 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>2.01</v>
+        <v>0.225</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>-0.029</v>
+        <v>-0.0217</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2812300</v>
+        <v>3341600</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H44" t="n">
-        <v>34.82</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>2.231</v>
-      </c>
+        <v>51.42</v>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
     </row>
@@ -2482,28 +2490,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.64</v>
+        <v>4.19</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>0.0123</v>
+        <v>0.0145</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2612300</v>
+        <v>3253400</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.32</v>
+        <v>0.43</v>
       </c>
       <c r="H45" t="n">
-        <v>50.8</v>
+        <v>65.56</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2511,10 +2519,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.625</v>
+        <v>3.801</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.676</v>
+        <v>3.249</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2542,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2606000</v>
+        <v>3248600</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="H46" t="n">
         <v>68.73</v>
@@ -2572,39 +2580,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PCCS</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.315</v>
+        <v>1.15</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.05</v>
+        <v>0.0268</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2573900</v>
+        <v>3203900</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>20.41</v>
+        <v>0.52</v>
       </c>
       <c r="H47" t="n">
-        <v>75.47</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.18</v>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.285</v>
+        <v>1.301</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.282</v>
+        <v>1.502</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2617,39 +2625,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0.0169</v>
+        <v>2.48</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2426100</v>
+        <v>3188300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="H48" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.93</v>
+      </c>
+      <c r="I48" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.315</v>
+        <v>2.592</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.359</v>
+        <v>2.559</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2662,28 +2670,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.265</v>
+        <v>1.99</v>
       </c>
       <c r="E49" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2291500</v>
+        <v>3151100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.32</v>
+        <v>0.11</v>
       </c>
       <c r="H49" t="n">
-        <v>41.25</v>
+        <v>54.66</v>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
@@ -2691,10 +2699,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.282</v>
+        <v>1.965</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.282</v>
+        <v>1.794</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2707,39 +2715,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.17</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2263300</v>
+        <v>3135000</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.11</v>
+        <v>1.4</v>
       </c>
       <c r="H50" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.01</v>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.868</v>
+        <v>0.166</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.869</v>
+        <v>0.156</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2752,39 +2760,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>0.0117</v>
+        <v>1.14</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2259300</v>
+        <v>3113900</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.72</v>
+        <v>0.41</v>
       </c>
       <c r="H51" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.43</v>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>3.049</v>
+        <v>1.203</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.579</v>
+        <v>1.29</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2797,39 +2805,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>0.0179</v>
+        <v>4.7</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2251100</v>
+        <v>3060500</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.36</v>
+        <v>0.14</v>
       </c>
       <c r="H52" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I52" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.16</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>1.3</v>
+        <v>4.726</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>1.502</v>
+        <v>4.811</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2842,28 +2850,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>2.48</v>
+        <v>0.705</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>-0.012</v>
+        <v>-0.0276</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2215500</v>
+        <v>2996300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.11</v>
+        <v>0.63</v>
       </c>
       <c r="H53" t="n">
-        <v>42.93</v>
+        <v>44.82</v>
       </c>
       <c r="I53" s="17" t="inlineStr">
         <is>
@@ -2871,10 +2879,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>2.592</v>
+        <v>0.821</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.559</v>
+        <v>0.627</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2887,28 +2895,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.15</v>
+        <v>0.265</v>
       </c>
       <c r="E54" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1999800</v>
+        <v>2691800</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="H54" t="n">
-        <v>33.75</v>
+        <v>41.25</v>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
@@ -2916,10 +2924,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.204</v>
+        <v>0.282</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.29</v>
+        <v>0.282</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2932,28 +2940,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>0</v>
+        <v>1.63</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1823200</v>
+        <v>2667400</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="H55" t="n">
-        <v>59.07</v>
+        <v>49.41</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2961,10 +2969,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.093</v>
+        <v>1.625</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>1.056</v>
+        <v>1.675</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2977,28 +2985,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>PCCS</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.0217</v>
+        <v>0.315</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.05</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1534300</v>
+        <v>2613000</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1.1</v>
+        <v>20.72</v>
       </c>
       <c r="H56" t="n">
-        <v>43.32</v>
+        <v>75.47</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3006,10 +3014,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.23</v>
+        <v>0.285</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.237</v>
+        <v>0.282</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3022,39 +3030,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.295</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1466600</v>
+        <v>2579300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.09</v>
+        <v>0.39</v>
       </c>
       <c r="H57" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="I57" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.35</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>7.359</v>
+        <v>0.314</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>7.625</v>
+        <v>0.359</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3067,28 +3075,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.225</v>
+        <v>3.46</v>
       </c>
       <c r="E58" s="15" t="n">
-        <v>0.0227</v>
+        <v>0.0117</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1447000</v>
+        <v>2278900</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>1.46</v>
+        <v>0.73</v>
       </c>
       <c r="H58" t="n">
-        <v>50.21</v>
+        <v>89.7</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3096,10 +3104,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.223</v>
+        <v>3.049</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.23</v>
+        <v>2.579</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3112,39 +3120,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>1.15</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1441500</v>
+        <v>2269300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="H59" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.07</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>2.432</v>
+        <v>1.093</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.412</v>
+        <v>1.056</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3157,39 +3165,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>-0.0103</v>
+        <v>1.41</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.0682</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1371800</v>
+        <v>1925200</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.06</v>
+        <v>1.13</v>
       </c>
       <c r="H60" t="n">
-        <v>46.64</v>
-      </c>
-      <c r="I60" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.26</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>4.868</v>
+        <v>1.369</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>4.763</v>
+        <v>1.44</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3202,28 +3210,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>2.04</v>
+        <v>0.86</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>0.0049</v>
+        <v>0.0238</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1369600</v>
+        <v>1893200</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
       <c r="H61" t="n">
-        <v>48.91</v>
+        <v>57.4</v>
       </c>
       <c r="I61" s="17" t="inlineStr">
         <is>
@@ -3231,10 +3239,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>2.039</v>
+        <v>0.83</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>2.064</v>
+        <v>0.799</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3247,39 +3255,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>4.73</v>
+        <v>0.33</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>-0.0042</v>
+        <v>-0.0149</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1349900</v>
+        <v>1796400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
       <c r="H62" t="n">
-        <v>48.74</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.09</v>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>4.729</v>
+        <v>0.348</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>4.812</v>
+        <v>0.33</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3292,39 +3300,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>0.0147</v>
+        <v>7.1</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1348300</v>
+        <v>1748200</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.29</v>
+        <v>0.11</v>
       </c>
       <c r="H63" t="n">
-        <v>57.71</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.47</v>
+      </c>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.337</v>
+        <v>7.359</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.343</v>
+        <v>7.625</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3337,28 +3345,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>-0.0117</v>
+        <v>1.56</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1334900</v>
+        <v>1658000</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H64" t="n">
-        <v>44.2</v>
+        <v>35.3</v>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
@@ -3366,10 +3374,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>2.593</v>
+        <v>1.656</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>2.604</v>
+        <v>1.741</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3382,28 +3390,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.755</v>
+        <v>2.67</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>-0.0066</v>
+        <v>-0.0037</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1324100</v>
+        <v>1642600</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H65" t="n">
-        <v>45.8</v>
+        <v>44.27</v>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
@@ -3411,10 +3419,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.767</v>
+        <v>2.733</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.771</v>
+        <v>2.747</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3427,28 +3435,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.825</v>
+        <v>2.04</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>0.0123</v>
+        <v>0.0049</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1311800</v>
+        <v>1640700</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.21</v>
+        <v>0.41</v>
       </c>
       <c r="H66" t="n">
-        <v>41.57</v>
+        <v>48.91</v>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
@@ -3456,10 +3464,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.884</v>
+        <v>2.039</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.859</v>
+        <v>2.064</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3472,38 +3480,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.37</v>
+        <v>0.435</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>0.0423</v>
+        <v>0.0116</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1301500</v>
+        <v>1623200</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="H67" t="n">
-        <v>61.24</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.55</v>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="K67" s="9" t="n"/>
+        <v>0.479</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>0.619</v>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
     </row>
@@ -3515,28 +3525,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>-0.0037</v>
+        <v>0.83</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.0184</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1283300</v>
+        <v>1622800</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="H68" t="n">
-        <v>44.27</v>
+        <v>42.31</v>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
@@ -3544,10 +3554,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>2.733</v>
+        <v>0.885</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>2.747</v>
+        <v>0.859</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3560,39 +3570,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>0.005600000000000001</v>
+        <v>5.75</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1256000</v>
+        <v>1604400</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.72</v>
+        <v>0.2</v>
       </c>
       <c r="H69" t="n">
-        <v>48.61</v>
-      </c>
-      <c r="I69" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.39</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.905</v>
+        <v>5.829</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.892</v>
+        <v>6.087</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3605,39 +3615,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>0.0129</v>
+        <v>0.225</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1241400</v>
+        <v>1584300</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.2</v>
+        <v>1.13</v>
       </c>
       <c r="H70" t="n">
-        <v>36.76</v>
-      </c>
-      <c r="I70" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.32</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.657</v>
+        <v>0.23</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.741</v>
+        <v>0.237</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3650,28 +3660,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>0</v>
+        <v>2.38</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1240700</v>
+        <v>1529800</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H71" t="n">
-        <v>35.41</v>
+        <v>42.66</v>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
@@ -3679,10 +3689,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.646</v>
+        <v>2.433</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>2.412</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3695,28 +3705,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>2.42</v>
+        <v>0.37</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>0.0126</v>
+        <v>0.0423</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1216500</v>
+        <v>1522900</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="H72" t="n">
-        <v>62.86</v>
+        <v>61.24</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3724,11 +3734,9 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>2.289</v>
-      </c>
-      <c r="K72" s="9" t="n">
-        <v>2.208</v>
-      </c>
+        <v>0.337</v>
+      </c>
+      <c r="K72" s="9" t="n"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
     </row>
@@ -3740,39 +3748,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>5.74</v>
+        <v>2.54</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>-0.0017</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1128300</v>
+        <v>1454300</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H73" t="n">
-        <v>39.86</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.96</v>
+      </c>
+      <c r="I73" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>5.828</v>
+        <v>2.594</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>6.087</v>
+        <v>2.604</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3785,39 +3793,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>-0.0174</v>
+        <v>0.225</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1123600</v>
+        <v>1447000</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.51</v>
+        <v>1.46</v>
       </c>
       <c r="H74" t="n">
-        <v>29.22</v>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.21</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.198</v>
+        <v>0.223</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.303</v>
+        <v>0.23</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3830,28 +3838,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>0.0112</v>
+        <v>4.81</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1123000</v>
+        <v>1425300</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H75" t="n">
-        <v>42.42</v>
+        <v>47.19</v>
       </c>
       <c r="I75" s="17" t="inlineStr">
         <is>
@@ -3859,10 +3867,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.492</v>
+        <v>4.869</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.469</v>
+        <v>4.763</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3875,28 +3883,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.865</v>
+        <v>0.755</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0066</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1121000</v>
+        <v>1376100</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.38</v>
+        <v>0.18</v>
       </c>
       <c r="H76" t="n">
-        <v>50.44</v>
+        <v>45.8</v>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
@@ -3904,10 +3912,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.866</v>
+        <v>0.767</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.861</v>
+        <v>0.771</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3920,28 +3928,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>-0.0115</v>
+        <v>0.345</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1049300</v>
+        <v>1367600</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="H77" t="n">
-        <v>51.18</v>
+        <v>57.71</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3949,10 +3957,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.429</v>
+        <v>0.337</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.418</v>
+        <v>0.343</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3965,39 +3973,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>-0.006</v>
+        <v>0.585</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1034800</v>
+        <v>1311800</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="H78" t="n">
-        <v>48.61</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.41</v>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>9.997</v>
+        <v>0.646</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>10.112</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4010,39 +4018,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E79" s="16" t="n">
-        <v>0</v>
+        <v>6.3</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1008500</v>
+        <v>1311800</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.88</v>
+        <v>0.18</v>
       </c>
       <c r="H79" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.57</v>
+      </c>
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.441</v>
+        <v>6.343</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.44</v>
+        <v>6.647</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4055,39 +4063,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>2.79</v>
+        <v>2.41</v>
       </c>
       <c r="E80" s="15" t="n">
-        <v>0.0036</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1002500</v>
+        <v>1307800</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="H80" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.27</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>2.787</v>
+        <v>2.288</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>2.69</v>
+        <v>2.207</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4100,28 +4108,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>-0.0061</v>
+        <v>2.79</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.0036</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>972700</v>
+        <v>1293300</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="H81" t="n">
-        <v>29.37</v>
+        <v>51.42</v>
       </c>
       <c r="I81" s="17" t="inlineStr">
         <is>
@@ -4129,10 +4137,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.867</v>
+        <v>2.787</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.931</v>
+        <v>2.69</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4145,39 +4153,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.36</v>
+        <v>0.745</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.0205</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>958300</v>
+        <v>1286800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="H82" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.58</v>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1.364</v>
+        <v>0.739</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.439</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4190,28 +4198,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>0.0571</v>
+        <v>0.43</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>955000</v>
+        <v>1280600</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>1.64</v>
+        <v>0.19</v>
       </c>
       <c r="H83" t="n">
-        <v>80.09999999999999</v>
+        <v>51.18</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4219,10 +4227,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.644</v>
+        <v>0.429</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.615</v>
+        <v>0.418</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4235,28 +4243,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0119</v>
+        <v>0.0112</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>952100</v>
+        <v>1266300</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="H84" t="n">
-        <v>55.8</v>
+        <v>42.42</v>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
@@ -4264,10 +4272,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.829</v>
+        <v>0.492</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.799</v>
+        <v>0.469</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4280,28 +4288,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.61</v>
+        <v>0.895</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>0.0083</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>949900</v>
+        <v>1256000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.31</v>
+        <v>0.72</v>
       </c>
       <c r="H85" t="n">
-        <v>34.03</v>
+        <v>48.61</v>
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
@@ -4309,10 +4317,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.679</v>
+        <v>0.905</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.734</v>
+        <v>0.892</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4325,28 +4333,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.96</v>
+        <v>10</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>-0.0052</v>
+        <v>-0.006</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>882700</v>
+        <v>1184700</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="H86" t="n">
-        <v>60.51</v>
+        <v>48.61</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4354,10 +4362,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.9419999999999999</v>
+        <v>9.997</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.892</v>
+        <v>10.112</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4370,28 +4378,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>0</v>
+        <v>1.13</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>-0.0174</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>851300</v>
+        <v>1152600</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.21</v>
+        <v>0.52</v>
       </c>
       <c r="H87" t="n">
-        <v>33.86</v>
+        <v>29.22</v>
       </c>
       <c r="I87" s="17" t="inlineStr">
         <is>
@@ -4399,10 +4407,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.481</v>
+        <v>1.198</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>2.646</v>
+        <v>1.303</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4415,28 +4423,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="E88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>782300</v>
+        <v>1146100</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="H88" t="n">
-        <v>53.46</v>
+        <v>40.12</v>
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
@@ -4444,10 +4452,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>1.175</v>
+        <v>1.123</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>1.149</v>
+        <v>1.112</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4460,39 +4468,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.23</v>
+        <v>0.865</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>-0.0315</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>734000</v>
+        <v>1121000</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.21</v>
+        <v>0.38</v>
       </c>
       <c r="H89" t="n">
-        <v>51.09</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.44</v>
+      </c>
+      <c r="I89" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.242</v>
+        <v>0.866</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.114</v>
+        <v>0.861</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4505,28 +4513,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v>0.0027</v>
+        <v>0.3</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>718900</v>
+        <v>1114600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.06</v>
+        <v>0.85</v>
       </c>
       <c r="H90" t="n">
-        <v>41.43</v>
+        <v>49.39</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4534,10 +4542,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>7.411</v>
+        <v>0.296</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>7.819</v>
+        <v>0.327</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4550,28 +4558,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>4.17</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.0425</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>717800</v>
+        <v>1087600</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="H91" t="n">
-        <v>38.96</v>
+        <v>59.46</v>
       </c>
       <c r="I91" s="17" t="inlineStr">
         <is>
@@ -4579,10 +4587,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.122</v>
+        <v>3.98</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.112</v>
+        <v>3.643</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4595,28 +4603,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>-0.0275</v>
+        <v>2.38</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>708500</v>
+        <v>1085900</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
       <c r="H92" t="n">
-        <v>35.15</v>
+        <v>33.86</v>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
@@ -4624,10 +4632,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.606</v>
+        <v>2.481</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.616</v>
+        <v>2.646</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4640,39 +4648,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0122</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>689500</v>
+        <v>1019900</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="H93" t="n">
-        <v>51.65</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.52</v>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.64</v>
+        <v>0.867</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.628</v>
+        <v>0.931</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4685,28 +4693,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>-0.004699999999999999</v>
+        <v>0.605</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>682000</v>
+        <v>1018200</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
       </c>
       <c r="H94" t="n">
-        <v>45.55</v>
+        <v>32.83</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -4714,10 +4722,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>6.345</v>
+        <v>0.679</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>6.647</v>
+        <v>0.734</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4730,39 +4738,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>-0.0068</v>
+        <v>0.445</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>681400</v>
+        <v>1013500</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.12</v>
+        <v>0.88</v>
       </c>
       <c r="H95" t="n">
-        <v>49.32</v>
-      </c>
-      <c r="I95" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.98999999999999</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.737</v>
+        <v>0.441</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4775,28 +4783,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.695</v>
+        <v>0.535</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>-0.0071</v>
+        <v>-0.0183</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>677600</v>
+        <v>984000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.29</v>
+        <v>0.11</v>
       </c>
       <c r="H96" t="n">
-        <v>37.05</v>
+        <v>35.75</v>
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
@@ -4804,10 +4812,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.755</v>
+        <v>0.607</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.768</v>
+        <v>0.616</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4820,28 +4828,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.925</v>
+        <v>1.2</v>
       </c>
       <c r="E97" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>638600</v>
+        <v>974000</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.62</v>
+        <v>0.15</v>
       </c>
       <c r="H97" t="n">
-        <v>47.71</v>
+        <v>54.86</v>
       </c>
       <c r="I97" s="17" t="inlineStr">
         <is>
@@ -4849,10 +4857,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.924</v>
+        <v>1.176</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.01</v>
+        <v>1.149</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4865,28 +4873,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.575</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>637800</v>
+        <v>956600</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="H98" t="n">
-        <v>47.92</v>
+        <v>60.29</v>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
@@ -4894,10 +4902,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.548</v>
+        <v>0.539</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.525</v>
+        <v>0.485</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4910,39 +4918,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.545</v>
+        <v>0.96</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>-0.0268</v>
+        <v>-0.0052</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>618000</v>
+        <v>902700</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
       <c r="H99" t="n">
-        <v>46.52</v>
-      </c>
-      <c r="I99" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.51</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.546</v>
+        <v>0.892</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4955,28 +4963,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>-0.0072</v>
+        <v>-0.0179</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>593000</v>
+        <v>870500</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.96</v>
+        <v>0.04</v>
       </c>
       <c r="H100" t="n">
-        <v>56.44</v>
+        <v>47.42</v>
       </c>
       <c r="I100" s="17" t="inlineStr">
         <is>
@@ -4984,10 +4992,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.663</v>
+        <v>0.546</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5000,39 +5008,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>6.77</v>
+        <v>7.34</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>0.0059</v>
+        <v>0.0027</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>591100</v>
+        <v>861300</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H101" t="n">
-        <v>36.66</v>
-      </c>
-      <c r="I101" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.43</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>7.051</v>
+        <v>7.411</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>7.494</v>
+        <v>7.819</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5045,39 +5053,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2.68</v>
+        <v>1.26</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>-0.0147</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>585800</v>
+        <v>854300</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="H102" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="I102" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.67</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>2.831</v>
+        <v>1.245</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2.97</v>
+        <v>1.115</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5090,39 +5098,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>0</v>
+        <v>6.76</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>565400</v>
+        <v>830400</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H103" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.25</v>
+      </c>
+      <c r="I103" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.226</v>
+        <v>7.05</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.205</v>
+        <v>7.494</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5135,28 +5143,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v>0.0175</v>
+        <v>0.505</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>562400</v>
+        <v>809100</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.06</v>
+        <v>0.28</v>
       </c>
       <c r="H104" t="n">
-        <v>56.34</v>
+        <v>29.83</v>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
@@ -5164,10 +5172,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>3.97</v>
+        <v>0.529</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>3.641</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5180,28 +5188,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>-0.0189</v>
+        <v>-0.02</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>527300</v>
+        <v>802400</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H105" t="n">
-        <v>46.82</v>
+        <v>44.11</v>
       </c>
       <c r="I105" s="17" t="inlineStr">
         <is>
@@ -5209,16 +5217,1051 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.094</v>
+        <v>1.023</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.926</v>
+        <v>0.973</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>-0.008100000000000001</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>800300</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H106" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="I106" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0388</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SEMICO</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>760000</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H107" t="n">
+        <v>63.67</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>759500</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H108" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>750700</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H109" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="I109" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>749000</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H110" t="n">
+        <v>48.88</v>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>724000</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H111" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>705900</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H112" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>692800</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H113" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="I113" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>649100</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H114" t="n">
+        <v>51.19</v>
+      </c>
+      <c r="I114" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>640000</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H115" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.0147</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>629400</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H116" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>2.831</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0299</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>628100</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H117" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="I117" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>613000</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="I118" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>602800</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H119" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>1.271</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>589500</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>2.828</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>LWSABAH</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>583500</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H121" t="n">
+        <v>26.97</v>
+      </c>
+      <c r="I121" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>582000</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H122" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>554100</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H123" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="I123" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>537200</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H124" t="n">
+        <v>42.28</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>537100</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H125" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>6.807</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>6.822</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>534200</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H126" t="n">
+        <v>53.57</v>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>6.288</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>5.997</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>-0.0203</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>520300</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H127" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="I127" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>7197</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>GESHEN</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>506700</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H128" t="n">
+        <v>78.51000000000001</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M105"/>
+  <autoFilter ref="A1:M128"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
+++ b/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M128"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0412</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4946400</v>
+        <v>5298300</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>56.25</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.505高于50日均线0.485，RSI 56.25处中性区间未超买，信号技术面可靠性尚可。</t>
+          <t>SAR转多信号，现价0.505高于50日均线0.485，RSI 56.25处中性区间，未超买，信号技术面较可靠。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0643</v>
+        <v>0.0571</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1160700</v>
+        <v>1218200</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>80.62</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.645</v>
+        <v>0.644</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.615</v>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>RSI 80.62 已处超买区，现价高于50日均线约21%，SAR转多信号可靠性受超买制约。</t>
+          <t>RSI 80.1 已处超买区，现价高于50日均线约20%，SAR转多信号可靠性受超买制约。</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-0.1333</v>
+        <v>-0.0667</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>90252500</v>
+        <v>95587000</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H4" t="n">
-        <v>31.79</v>
+        <v>32.63</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.259</v>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.19</v>
+        <v>0.195</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.3571</v>
+        <v>0.3929</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>51401400</v>
+        <v>58876200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>55.61</v>
+        <v>63.69</v>
       </c>
       <c r="H5" t="n">
-        <v>86.39</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>0.12</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -768,10 +768,10 @@
         <v>-0.0306</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>36225400</v>
+        <v>37498600</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="H6" t="n">
         <v>72.55</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.155</v>
+        <v>0.145</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>-0.06059999999999999</v>
+        <v>-0.1212</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>27502300</v>
+        <v>36639200</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="H7" t="n">
-        <v>48.93</v>
+        <v>44.98</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
         <v>0.0588</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>21798800</v>
+        <v>22273200</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>8.949999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>78.40000000000001</v>
@@ -903,10 +903,10 @@
         <v>0.1667</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>20055200</v>
+        <v>20342100</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>7.7</v>
+        <v>7.81</v>
       </c>
       <c r="H9" t="n">
         <v>74.81</v>
@@ -987,19 +987,19 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.75</v>
+        <v>0.745</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0.0135</v>
+        <v>0.0068</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>12969200</v>
+        <v>13049200</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0.54</v>
       </c>
       <c r="H11" t="n">
-        <v>84.87</v>
+        <v>84.41</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.661</v>
+        <v>0.66</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0.5620000000000001</v>
@@ -1023,39 +1023,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.82</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>11507600</v>
+        <v>12402600</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.19</v>
+        <v>0.77</v>
       </c>
       <c r="H12" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.39</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.403</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1068,28 +1068,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>-0.0185</v>
+        <v>0.305</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>10782100</v>
+        <v>11902700</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.01</v>
+        <v>0.61</v>
       </c>
       <c r="H13" t="n">
-        <v>41.24</v>
+        <v>47.42</v>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.286</v>
+        <v>0.307</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.279</v>
+        <v>0.302</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1113,28 +1113,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>10299500</v>
+        <v>11799000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.12</v>
+        <v>1.11</v>
       </c>
       <c r="H14" t="n">
-        <v>60.52</v>
+        <v>41.24</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.316</v>
+        <v>0.286</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.266</v>
+        <v>0.279</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1158,39 +1158,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>10114500</v>
+        <v>11685800</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.63</v>
+        <v>1.21</v>
       </c>
       <c r="H15" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.76</v>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.403</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1203,28 +1203,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.305</v>
+        <v>0.33</v>
       </c>
       <c r="E16" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>9491200</v>
+        <v>10459200</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.49</v>
+        <v>0.12</v>
       </c>
       <c r="H16" t="n">
-        <v>47.42</v>
+        <v>60.52</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.307</v>
+        <v>0.316</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.302</v>
+        <v>0.266</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1257,19 +1257,19 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0</v>
+        <v>0.925</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.0054</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8900600</v>
+        <v>9609000</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H17" t="n">
-        <v>64.86</v>
+        <v>65.45</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.859</v>
+        <v>0.86</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0.763</v>
@@ -1293,39 +1293,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.775</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>8900500</v>
+        <v>9370000</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.74</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="n">
-        <v>56.73</v>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.44</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.267</v>
+        <v>0.775</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.27</v>
+        <v>0.776</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1338,39 +1338,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.022</v>
+        <v>0.155</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>8792100</v>
+        <v>9361100</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="H19" t="n">
-        <v>61.85</v>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.73</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.433</v>
+        <v>0.156</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.385</v>
+        <v>0.156</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1383,39 +1383,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>8344200</v>
+        <v>9294300</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.54</v>
+        <v>1.81</v>
       </c>
       <c r="H20" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.3</v>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.775</v>
+        <v>0.267</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.776</v>
+        <v>0.269</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1428,33 +1428,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>-0.0263</v>
+        <v>0.465</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.022</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>8324500</v>
+        <v>9264500</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.24</v>
+        <v>0.46</v>
+      </c>
+      <c r="H21" t="n">
+        <v>61.85</v>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
+      <c r="J21" s="9" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.385</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
     </row>
@@ -1481,10 +1488,10 @@
         <v>-0.0526</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>7164400</v>
+        <v>8474300</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="H22" t="n">
         <v>34.72</v>
@@ -1511,25 +1518,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.68</v>
+        <v>0.185</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>-0.0423</v>
+        <v>-0.0263</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6295000</v>
+        <v>8434500</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
@@ -1549,39 +1556,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>0.0457</v>
+        <v>0.005</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>6222100</v>
+        <v>7775000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1.67</v>
+        <v>8.51</v>
       </c>
       <c r="H24" t="n">
-        <v>50.89</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.898</v>
+        <v>0.005</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.958</v>
+        <v>0.006</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1594,28 +1601,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.39</v>
+        <v>1.99</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0386</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6196100</v>
+        <v>7339700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H25" t="n">
-        <v>39.02</v>
+        <v>33.25</v>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
@@ -1623,10 +1630,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.423</v>
+        <v>2.106</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.439</v>
+        <v>2.23</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1639,40 +1646,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.675</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.0493</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>5716500</v>
+        <v>6979300</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="H26" t="n">
-        <v>66.55</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>0.08400000000000001</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
     </row>
@@ -1684,28 +1684,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>0</v>
+        <v>0.91</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.04</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5608300</v>
+        <v>6450600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.53</v>
+        <v>1.73</v>
       </c>
       <c r="H27" t="n">
-        <v>60.81</v>
+        <v>49.54</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.624</v>
+        <v>0.898</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.618</v>
+        <v>0.958</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1729,39 +1729,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>0</v>
+        <v>0.39</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>5465200</v>
+        <v>6240300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.46</v>
+        <v>0.82</v>
       </c>
       <c r="H28" t="n">
-        <v>54.71</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.02</v>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.401</v>
+        <v>0.423</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.383</v>
+        <v>0.439</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1774,39 +1774,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>1.99</v>
+        <v>0.865</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>-0.0386</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5445000</v>
+        <v>6155100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
       <c r="H29" t="n">
-        <v>33.25</v>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>2.106</v>
+        <v>0.868</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2.23</v>
+        <v>0.869</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1819,28 +1819,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.0331</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5345500</v>
+        <v>5899500</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>5.85</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>47.02</v>
+        <v>40.62</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.005</v>
+        <v>1.005</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.006</v>
+        <v>0.981</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1864,39 +1864,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.93</v>
+        <v>0.415</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>0.0276</v>
+        <v>0.0122</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5294700</v>
+        <v>5882300</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0.5</v>
       </c>
       <c r="H31" t="n">
-        <v>39.86</v>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.17</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.005</v>
+        <v>0.401</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.981</v>
+        <v>0.383</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1909,39 +1909,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.155</v>
+        <v>0.05</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>-0.0313</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5156100</v>
+        <v>5843500</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.14</v>
+        <v>0.62</v>
       </c>
       <c r="H32" t="n">
-        <v>47.73</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.17</v>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.156</v>
+        <v>0.061</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.156</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1954,28 +1954,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.52</v>
+        <v>0.11</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>0.0196</v>
+        <v>0.0476</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4510600</v>
+        <v>5778400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="H33" t="n">
-        <v>80.93000000000001</v>
+        <v>66.55</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.451</v>
+        <v>0.099</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.437</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1999,28 +1999,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>-0.0133</v>
+        <v>2.13</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0.029</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4337800</v>
+        <v>5760400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.63</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>48.14</v>
+        <v>70.38</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.372</v>
+        <v>1.969</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.37</v>
+        <v>1.961</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2044,39 +2044,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.2</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.0526</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4231300</v>
+        <v>5687000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H35" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.57</v>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.868</v>
+        <v>0.209</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.869</v>
+        <v>0.229</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2089,39 +2089,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.0292</v>
+        <v>0.635</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4223300</v>
+        <v>5608300</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="H36" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.81</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.576</v>
+        <v>0.624</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1.867</v>
+        <v>0.618</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2134,39 +2134,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.0267</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4143400</v>
+        <v>4806200</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1.22</v>
+        <v>0.44</v>
       </c>
       <c r="H37" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>30.04</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.295</v>
+        <v>0.469</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.295</v>
+        <v>0.583</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2179,39 +2179,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.195</v>
+        <v>0.52</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>0.0263</v>
+        <v>0.0196</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4128700</v>
+        <v>4699600</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.22</v>
+        <v>1.39</v>
       </c>
       <c r="H38" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.93000000000001</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.209</v>
+        <v>0.451</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.229</v>
+        <v>0.437</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2224,39 +2224,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.73</v>
+        <v>0.37</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>-0.0068</v>
+        <v>-0.0133</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4065700</v>
+        <v>4563400</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.35</v>
+        <v>0.67</v>
       </c>
       <c r="H39" t="n">
-        <v>49.17</v>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.14</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.735</v>
+        <v>0.372</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.725</v>
+        <v>0.37</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2269,39 +2269,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.38</v>
+        <v>1.41</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.0292</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4038800</v>
+        <v>4514300</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="H40" t="n">
-        <v>28.85</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.3</v>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.469</v>
+        <v>1.576</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.583</v>
+        <v>1.867</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2314,28 +2314,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.42</v>
+        <v>0.73</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>-0.0118</v>
+        <v>-0.0068</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3994700</v>
+        <v>4243500</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.11</v>
+        <v>0.37</v>
       </c>
       <c r="H41" t="n">
-        <v>37.37</v>
+        <v>49.17</v>
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.455</v>
+        <v>0.735</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.475</v>
+        <v>0.725</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2359,39 +2359,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>0.019</v>
+        <v>0.295</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3885400</v>
+        <v>4143400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.86</v>
+        <v>1.22</v>
       </c>
       <c r="H42" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.06</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.114</v>
+        <v>0.295</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.078</v>
+        <v>0.295</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2404,39 +2404,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0483</v>
+        <v>0.42</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3827000</v>
+        <v>4075400</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.62</v>
+        <v>0.11</v>
       </c>
       <c r="H43" t="n">
-        <v>72.84</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.37</v>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.973</v>
+        <v>0.455</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.962</v>
+        <v>0.475</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2449,36 +2449,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.225</v>
+        <v>2.5</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>-0.0217</v>
+        <v>-0.004</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3341600</v>
+        <v>4047300</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H44" t="n">
-        <v>51.42</v>
+        <v>43.98</v>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
+      <c r="J44" s="9" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>2.56</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
     </row>
@@ -2490,39 +2494,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>4.19</v>
+        <v>2.01</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>0.0145</v>
+        <v>0.0101</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3253400</v>
+        <v>4003900</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.43</v>
+        <v>0.14</v>
       </c>
       <c r="H45" t="n">
-        <v>65.56</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.8</v>
+      </c>
+      <c r="I45" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>3.801</v>
+        <v>1.967</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>3.249</v>
+        <v>1.795</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2535,40 +2539,36 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3248600</v>
+        <v>3999700</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.63</v>
+        <v>0.19</v>
       </c>
       <c r="H46" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J46" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="K46" s="9" t="n">
-        <v>0.779</v>
-      </c>
+        <v>51.42</v>
+      </c>
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
     </row>
@@ -2580,39 +2580,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1.15</v>
+        <v>2.14</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.0268</v>
+        <v>0.019</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3203900</v>
+        <v>3911100</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.52</v>
+        <v>1.87</v>
       </c>
       <c r="H47" t="n">
-        <v>24.18</v>
-      </c>
-      <c r="I47" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.64</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.301</v>
+        <v>2.114</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1.502</v>
+        <v>2.078</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2625,39 +2625,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>-0.012</v>
+        <v>0.825</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3188300</v>
+        <v>3687100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.16</v>
+        <v>0.72</v>
       </c>
       <c r="H48" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="I48" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.73</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.592</v>
+        <v>0.805</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2.559</v>
+        <v>0.779</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2670,28 +2670,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0</v>
+        <v>1.14</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3151100</v>
+        <v>3670700</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.11</v>
+        <v>0.59</v>
       </c>
       <c r="H49" t="n">
-        <v>54.66</v>
+        <v>22.3</v>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>1.965</v>
+        <v>1.3</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>1.794</v>
+        <v>1.502</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2715,39 +2715,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>0.0303</v>
+        <v>4.7</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3135000</v>
+        <v>3529800</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.4</v>
+        <v>0.16</v>
       </c>
       <c r="H50" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.16</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.166</v>
+        <v>4.726</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.156</v>
+        <v>4.811</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2769,19 +2769,19 @@
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>1.15</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3113900</v>
+        <v>3485500</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="H51" t="n">
-        <v>32.43</v>
+        <v>33.75</v>
       </c>
       <c r="I51" s="17" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.203</v>
+        <v>1.204</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>1.29</v>
@@ -2805,39 +2805,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>-0.0105</v>
+        <v>0.17</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3060500</v>
+        <v>3454500</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.14</v>
+        <v>1.55</v>
       </c>
       <c r="H52" t="n">
-        <v>46.16</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.01</v>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>4.726</v>
+        <v>0.166</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>4.811</v>
+        <v>0.156</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2850,39 +2850,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.0276</v>
+        <v>4.17</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2996300</v>
+        <v>3435300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="H53" t="n">
-        <v>44.82</v>
-      </c>
-      <c r="I53" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.16</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.821</v>
+        <v>3.799</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.627</v>
+        <v>3.248</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2895,39 +2895,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>0</v>
+        <v>3.4</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2691800</v>
+        <v>3411100</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.38</v>
+        <v>1.09</v>
       </c>
       <c r="H54" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.48</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.282</v>
+        <v>3.043</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.282</v>
+        <v>2.578</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2940,39 +2940,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.0062</v>
+        <v>0.265</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2667400</v>
+        <v>3231500</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="H55" t="n">
-        <v>49.41</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.25</v>
+      </c>
+      <c r="I55" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.625</v>
+        <v>0.282</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>1.675</v>
+        <v>0.282</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2985,39 +2985,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PCCS</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0.05</v>
+        <v>0.7</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2613000</v>
+        <v>3143900</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>20.72</v>
+        <v>0.66</v>
       </c>
       <c r="H56" t="n">
-        <v>75.47</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.54</v>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.285</v>
+        <v>0.821</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.282</v>
+        <v>0.627</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3030,28 +3030,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>0</v>
+        <v>1.63</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2579300</v>
+        <v>2760900</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="H57" t="n">
-        <v>36.35</v>
+        <v>49.41</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.314</v>
+        <v>1.625</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.359</v>
+        <v>1.675</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3075,28 +3075,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>3.46</v>
+        <v>1.42</v>
       </c>
       <c r="E58" s="15" t="n">
-        <v>0.0117</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2278900</v>
+        <v>2658500</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.73</v>
+        <v>1.56</v>
       </c>
       <c r="H58" t="n">
-        <v>89.7</v>
+        <v>54.47</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>3.049</v>
+        <v>1.37</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>2.579</v>
+        <v>1.44</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3120,28 +3120,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>PCCS</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0</v>
+        <v>0.315</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0.05</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2269300</v>
+        <v>2615900</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.25</v>
+        <v>20.75</v>
       </c>
       <c r="H59" t="n">
-        <v>59.07</v>
+        <v>75.47</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.093</v>
+        <v>0.285</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.056</v>
+        <v>0.282</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3165,39 +3165,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.0682</v>
+        <v>2.65</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1925200</v>
+        <v>2614700</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1.13</v>
+        <v>0.25</v>
       </c>
       <c r="H60" t="n">
-        <v>53.26</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.85</v>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.369</v>
+        <v>2.731</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1.44</v>
+        <v>2.746</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3210,39 +3210,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.0238</v>
+        <v>0.295</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1893200</v>
+        <v>2609900</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H61" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="I61" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.35</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.83</v>
+        <v>0.314</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.799</v>
+        <v>0.359</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3255,39 +3255,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>-0.0149</v>
+        <v>1.15</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1796400</v>
+        <v>2360700</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="H62" t="n">
-        <v>43.09</v>
-      </c>
-      <c r="I62" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.07</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.348</v>
+        <v>1.093</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.33</v>
+        <v>1.056</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3300,28 +3300,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>7.1</v>
+        <v>4.82</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.0062</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1748200</v>
+        <v>2237500</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="H63" t="n">
-        <v>31.47</v>
+        <v>47.76</v>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>7.359</v>
+        <v>4.87</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>7.625</v>
+        <v>4.764</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3345,28 +3345,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>7.1</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1658000</v>
+        <v>2168300</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="H64" t="n">
-        <v>35.3</v>
+        <v>31.47</v>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.656</v>
+        <v>7.359</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1.741</v>
+        <v>7.625</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3390,28 +3390,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2.67</v>
+        <v>0.33</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>-0.0037</v>
+        <v>-0.0149</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1642600</v>
+        <v>2138200</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H65" t="n">
-        <v>44.27</v>
+        <v>43.09</v>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.733</v>
+        <v>0.348</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.747</v>
+        <v>0.33</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3435,39 +3435,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>0.0049</v>
+        <v>0.23</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1640700</v>
+        <v>2136900</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.41</v>
+        <v>1.53</v>
       </c>
       <c r="H66" t="n">
-        <v>48.91</v>
-      </c>
-      <c r="I66" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.039</v>
+        <v>0.23</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.064</v>
+        <v>0.238</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3480,28 +3480,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.435</v>
+        <v>0.865</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>0.0116</v>
+        <v>0.0298</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1623200</v>
+        <v>2065500</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.1</v>
+        <v>0.54</v>
       </c>
       <c r="H67" t="n">
-        <v>27.55</v>
+        <v>58.16</v>
       </c>
       <c r="I67" s="17" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.479</v>
+        <v>0.83</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.619</v>
+        <v>0.799</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3525,28 +3525,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>0.0184</v>
+        <v>0.865</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1622800</v>
+        <v>1993000</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.26</v>
+        <v>0.67</v>
       </c>
       <c r="H68" t="n">
-        <v>42.31</v>
+        <v>50.44</v>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.885</v>
+        <v>0.866</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.859</v>
+        <v>0.861</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3579,19 +3579,19 @@
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="E69" s="16" t="n">
-        <v>0</v>
+        <v>5.72</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1604400</v>
+        <v>1992200</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H69" t="n">
-        <v>40.39</v>
+        <v>38.83</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>5.829</v>
+        <v>5.826</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>6.087</v>
+        <v>6.086</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3615,39 +3615,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.225</v>
+        <v>0.755</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>-0.0217</v>
+        <v>-0.0066</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1584300</v>
+        <v>1963200</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1.13</v>
+        <v>0.25</v>
       </c>
       <c r="H70" t="n">
-        <v>43.32</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.8</v>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.23</v>
+        <v>0.767</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.237</v>
+        <v>0.771</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3660,28 +3660,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>-0.0042</v>
+        <v>2.04</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1529800</v>
+        <v>1938600</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.13</v>
+        <v>0.48</v>
       </c>
       <c r="H71" t="n">
-        <v>42.66</v>
+        <v>48.91</v>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.433</v>
+        <v>2.039</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.412</v>
+        <v>2.064</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3705,38 +3705,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.37</v>
+        <v>0.835</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>0.0423</v>
+        <v>0.0245</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1522900</v>
+        <v>1936100</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="H72" t="n">
-        <v>61.24</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.04</v>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="K72" s="9" t="n"/>
+        <v>0.885</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>0.859</v>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
     </row>
@@ -3748,28 +3750,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>KEYFIELD</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2.54</v>
+        <v>1.39</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0071</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1454300</v>
+        <v>1807000</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.26</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>44.96</v>
+        <v>50.67</v>
       </c>
       <c r="I73" s="17" t="inlineStr">
         <is>
@@ -3777,10 +3779,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>2.594</v>
+        <v>1.389</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>2.604</v>
+        <v>1.372</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3793,39 +3795,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.225</v>
+        <v>1.56</v>
       </c>
       <c r="E74" s="15" t="n">
-        <v>0.0227</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1447000</v>
+        <v>1753600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>1.46</v>
+        <v>0.29</v>
       </c>
       <c r="H74" t="n">
-        <v>50.21</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.3</v>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.223</v>
+        <v>1.656</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.23</v>
+        <v>1.741</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3838,28 +3840,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4.81</v>
+        <v>2.55</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0039</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1425300</v>
+        <v>1725400</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
       <c r="H75" t="n">
-        <v>47.19</v>
+        <v>45.76</v>
       </c>
       <c r="I75" s="17" t="inlineStr">
         <is>
@@ -3867,10 +3869,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>4.869</v>
+        <v>2.594</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>4.763</v>
+        <v>2.604</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3883,40 +3885,38 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>-0.0066</v>
+        <v>0.37</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.0423</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1376100</v>
+        <v>1720600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="H76" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="I76" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.24</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="K76" s="9" t="n">
-        <v>0.771</v>
-      </c>
+        <v>0.337</v>
+      </c>
+      <c r="K76" s="9" t="n"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
     </row>
@@ -3928,39 +3928,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>0.0147</v>
+        <v>6.29</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1367600</v>
+        <v>1716200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H77" t="n">
-        <v>57.71</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.09</v>
+      </c>
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.337</v>
+        <v>6.342</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.343</v>
+        <v>6.646</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3973,28 +3973,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>0</v>
+        <v>0.435</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.0116</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1311800</v>
+        <v>1661400</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="H78" t="n">
-        <v>35.41</v>
+        <v>27.55</v>
       </c>
       <c r="I78" s="17" t="inlineStr">
         <is>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.646</v>
+        <v>0.479</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.619</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4018,28 +4018,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>6.3</v>
+        <v>2.38</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0042</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1311800</v>
+        <v>1589500</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="H79" t="n">
-        <v>44.57</v>
+        <v>42.66</v>
       </c>
       <c r="I79" s="17" t="inlineStr">
         <is>
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>6.343</v>
+        <v>2.433</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>6.647</v>
+        <v>2.412</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4063,39 +4063,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>2.41</v>
+        <v>4.2</v>
       </c>
       <c r="E80" s="15" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1307800</v>
+        <v>1584100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.38</v>
+        <v>0.17</v>
       </c>
       <c r="H80" t="n">
-        <v>62.27</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.31</v>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>2.288</v>
+        <v>3.983</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>2.207</v>
+        <v>3.644</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4117,19 +4117,19 @@
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>0.0036</v>
+        <v>0.0072</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1293300</v>
+        <v>1554100</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="H81" t="n">
-        <v>51.42</v>
+        <v>52</v>
       </c>
       <c r="I81" s="17" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>2.787</v>
+        <v>2.788</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>2.69</v>
@@ -4153,39 +4153,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>0.0205</v>
+        <v>6.88</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>-0.0101</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1286800</v>
+        <v>1531100</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="H82" t="n">
-        <v>52.58</v>
-      </c>
-      <c r="I82" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.4</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.739</v>
+        <v>6.806</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>6.822</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4198,39 +4198,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>-0.0115</v>
+        <v>0.545</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1280600</v>
+        <v>1511100</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="H83" t="n">
-        <v>51.18</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37</v>
+      </c>
+      <c r="I83" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.429</v>
+        <v>0.608</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.418</v>
+        <v>0.616</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4243,39 +4243,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.45</v>
+        <v>0.225</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0112</v>
+        <v>0.0227</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1266300</v>
+        <v>1462000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.13</v>
+        <v>1.48</v>
       </c>
       <c r="H84" t="n">
-        <v>42.42</v>
-      </c>
-      <c r="I84" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.21</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.492</v>
+        <v>0.223</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.469</v>
+        <v>0.23</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4288,28 +4288,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.895</v>
+        <v>0.755</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.0342</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1256000</v>
+        <v>1407900</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.72</v>
+        <v>0.26</v>
       </c>
       <c r="H85" t="n">
-        <v>48.61</v>
+        <v>54.07</v>
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.905</v>
+        <v>0.74</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.892</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4333,28 +4333,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>-0.006</v>
+        <v>0.345</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1184700</v>
+        <v>1400400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.09</v>
+        <v>0.31</v>
       </c>
       <c r="H86" t="n">
-        <v>48.61</v>
+        <v>57.71</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>9.997</v>
+        <v>0.337</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>10.112</v>
+        <v>0.343</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4378,39 +4378,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>-0.0174</v>
+        <v>2.42</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1152600</v>
+        <v>1392200</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="H87" t="n">
-        <v>29.22</v>
-      </c>
-      <c r="I87" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.86</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.198</v>
+        <v>2.289</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.303</v>
+        <v>2.208</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4423,39 +4423,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1.06</v>
+        <v>0.435</v>
       </c>
       <c r="E88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1146100</v>
+        <v>1377500</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H88" t="n">
-        <v>40.12</v>
-      </c>
-      <c r="I88" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.42</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>1.123</v>
+        <v>0.429</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>1.112</v>
+        <v>0.418</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4468,28 +4468,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.59</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1121000</v>
+        <v>1369800</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.38</v>
+        <v>0.17</v>
       </c>
       <c r="H89" t="n">
-        <v>50.44</v>
+        <v>36.66</v>
       </c>
       <c r="I89" s="17" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.866</v>
+        <v>0.646</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.861</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4513,39 +4513,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.3</v>
+        <v>0.985</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>-0.0323</v>
+        <v>-0.015</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1114600</v>
+        <v>1334400</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.85</v>
+        <v>0.37</v>
       </c>
       <c r="H90" t="n">
-        <v>49.39</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.83</v>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.296</v>
+        <v>1.024</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.327</v>
+        <v>0.973</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4558,28 +4558,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>4.17</v>
+        <v>1.2</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>0.0425</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1087600</v>
+        <v>1274600</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="H91" t="n">
-        <v>59.46</v>
+        <v>54.86</v>
       </c>
       <c r="I91" s="17" t="inlineStr">
         <is>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>3.98</v>
+        <v>1.176</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>3.643</v>
+        <v>1.149</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4603,28 +4603,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2.38</v>
+        <v>0.445</v>
       </c>
       <c r="E92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1085900</v>
+        <v>1274500</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="H92" t="n">
-        <v>33.86</v>
+        <v>41.39</v>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>2.481</v>
+        <v>0.491</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.646</v>
+        <v>0.469</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4648,39 +4648,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>-0.0122</v>
+        <v>-0.008</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1019900</v>
+        <v>1273100</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>0.36</v>
       </c>
       <c r="H93" t="n">
-        <v>28.52</v>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.1</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.867</v>
+        <v>0.62</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.931</v>
+        <v>0.61</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4693,28 +4693,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.605</v>
+        <v>0.555</v>
       </c>
       <c r="E94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1018200</v>
+        <v>1264000</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="H94" t="n">
-        <v>32.83</v>
+        <v>45.18</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.679</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.734</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4738,39 +4738,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>0</v>
+        <v>1.09</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>0.0283</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1013500</v>
+        <v>1259100</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.88</v>
+        <v>0.34</v>
       </c>
       <c r="H95" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.05</v>
+      </c>
+      <c r="I95" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.441</v>
+        <v>1.098</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.44</v>
+        <v>0.927</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4783,39 +4783,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.535</v>
+        <v>9.99</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>-0.0183</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>984000</v>
+        <v>1258400</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H96" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="I96" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.607</v>
+        <v>9.996</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.616</v>
+        <v>10.112</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4828,28 +4828,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.2</v>
+        <v>0.895</v>
       </c>
       <c r="E97" s="15" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>974000</v>
+        <v>1256000</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.15</v>
+        <v>0.72</v>
       </c>
       <c r="H97" t="n">
-        <v>54.86</v>
+        <v>48.61</v>
       </c>
       <c r="I97" s="17" t="inlineStr">
         <is>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.176</v>
+        <v>0.905</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.149</v>
+        <v>0.892</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4873,28 +4873,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>-0.0086</v>
+        <v>1.06</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>956600</v>
+        <v>1164500</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="H98" t="n">
-        <v>60.29</v>
+        <v>40.12</v>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.539</v>
+        <v>1.123</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.485</v>
+        <v>1.112</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4918,39 +4918,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>-0.0052</v>
+        <v>-0.0174</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>902700</v>
+        <v>1159100</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="H99" t="n">
-        <v>60.51</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.22</v>
+      </c>
+      <c r="I99" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.198</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.892</v>
+        <v>1.303</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4963,39 +4963,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>-0.0179</v>
+        <v>-0.0323</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>870500</v>
+        <v>1114800</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.04</v>
+        <v>0.85</v>
       </c>
       <c r="H100" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I100" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.39</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.296</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.546</v>
+        <v>0.327</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5008,39 +5008,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>0.0027</v>
+        <v>2.37</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>861300</v>
+        <v>1112000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
       <c r="H101" t="n">
-        <v>41.43</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.15</v>
+      </c>
+      <c r="I101" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>7.411</v>
+        <v>2.48</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>7.819</v>
+        <v>2.645</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5053,28 +5053,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.965</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>854300</v>
+        <v>1111000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="H102" t="n">
-        <v>53.67</v>
+        <v>62.7</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.245</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.115</v>
+        <v>0.892</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5098,39 +5098,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>6.76</v>
+        <v>7.34</v>
       </c>
       <c r="E103" s="15" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0027</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>830400</v>
+        <v>1081500</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H103" t="n">
-        <v>36.25</v>
-      </c>
-      <c r="I103" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.43</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>7.05</v>
+        <v>7.411</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>7.494</v>
+        <v>7.819</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5143,28 +5143,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E104" s="16" t="n">
-        <v>0</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>809100</v>
+        <v>1058600</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="H104" t="n">
-        <v>29.83</v>
+        <v>29.37</v>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.529</v>
+        <v>0.867</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.931</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5188,28 +5188,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>-0.02</v>
+        <v>0.615</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>0.0165</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>802400</v>
+        <v>1041700</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.23</v>
+        <v>0.34</v>
       </c>
       <c r="H105" t="n">
-        <v>44.11</v>
+        <v>35.18</v>
       </c>
       <c r="I105" s="17" t="inlineStr">
         <is>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.023</v>
+        <v>0.68</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.973</v>
+        <v>0.734</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5233,28 +5233,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.23</v>
+        <v>0.55</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.0179</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>800300</v>
+        <v>1033100</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.39</v>
+        <v>0.05</v>
       </c>
       <c r="H106" t="n">
-        <v>42.11</v>
+        <v>47.42</v>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
@@ -5262,10 +5262,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.289</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.3</v>
+        <v>0.546</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5278,28 +5278,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.625</v>
+        <v>0.445</v>
       </c>
       <c r="E107" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>760000</v>
+        <v>1015500</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.22</v>
+        <v>0.88</v>
       </c>
       <c r="H107" t="n">
-        <v>63.67</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.62</v>
+        <v>0.441</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.61</v>
+        <v>0.44</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5323,39 +5323,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E108" s="16" t="n">
-        <v>0</v>
+        <v>0.585</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>759500</v>
+        <v>1014500</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="H108" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.18</v>
+      </c>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>1.226</v>
+        <v>0.54</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1.205</v>
+        <v>0.485</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5368,28 +5368,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.705</v>
+        <v>6.78</v>
       </c>
       <c r="E109" s="15" t="n">
-        <v>0.0071</v>
+        <v>0.0074</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>750700</v>
+        <v>1011400</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.32</v>
+        <v>0.09</v>
       </c>
       <c r="H109" t="n">
-        <v>38.96</v>
+        <v>37.07</v>
       </c>
       <c r="I109" s="17" t="inlineStr">
         <is>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.756</v>
+        <v>7.052</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.769</v>
+        <v>7.494</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5413,28 +5413,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E110" s="16" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>749000</v>
+        <v>1007400</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="H110" t="n">
-        <v>48.88</v>
+        <v>14</v>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
@@ -5442,11 +5442,9 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>1.096</v>
-      </c>
-      <c r="K110" s="9" t="n">
-        <v>0.926</v>
-      </c>
+        <v>0.257</v>
+      </c>
+      <c r="K110" s="9" t="n"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
     </row>
@@ -5458,39 +5456,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E111" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.505</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>724000</v>
+        <v>942600</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="H111" t="n">
-        <v>51.65</v>
-      </c>
-      <c r="I111" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.83</v>
+      </c>
+      <c r="I111" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.64</v>
+        <v>0.529</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.628</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5503,28 +5501,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v>0.0189</v>
+        <v>1.23</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>705900</v>
+        <v>908200</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.14</v>
+        <v>0.45</v>
       </c>
       <c r="H112" t="n">
-        <v>49.05</v>
+        <v>42.11</v>
       </c>
       <c r="I112" s="17" t="inlineStr">
         <is>
@@ -5532,10 +5530,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.549</v>
+        <v>1.289</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.525</v>
+        <v>1.3</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5548,39 +5546,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E113" s="15" t="n">
-        <v>0.0273</v>
+        <v>1.26</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>692800</v>
+        <v>883500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.68</v>
+        <v>0.25</v>
       </c>
       <c r="H113" t="n">
-        <v>50.04</v>
-      </c>
-      <c r="I113" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.67</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.925</v>
+        <v>1.245</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.011</v>
+        <v>1.115</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5593,28 +5591,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.54</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>649100</v>
+        <v>828600</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H114" t="n">
-        <v>51.19</v>
+        <v>49.05</v>
       </c>
       <c r="I114" s="17" t="inlineStr">
         <is>
@@ -5622,10 +5620,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.265</v>
+        <v>0.549</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1.186</v>
+        <v>0.525</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5638,39 +5636,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E115" s="16" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0.0219</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>640000</v>
+        <v>823700</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="H115" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.29</v>
+      </c>
+      <c r="I115" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.633</v>
+        <v>0.925</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.632</v>
+        <v>1.011</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5683,39 +5681,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>-0.0147</v>
+        <v>1.25</v>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>629400</v>
+        <v>821600</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="H116" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="I116" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.64</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>2.831</v>
+        <v>1.226</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>2.97</v>
+        <v>1.205</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5728,28 +5726,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>-0.0299</v>
+        <v>2.42</v>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>0.0342</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>628100</v>
+        <v>820800</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="H117" t="n">
-        <v>51.71</v>
+        <v>37.34</v>
       </c>
       <c r="I117" s="17" t="inlineStr">
         <is>
@@ -5757,10 +5755,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>1.288</v>
+        <v>2.633</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>1.242</v>
+        <v>2.828</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5773,28 +5771,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>-0.0072</v>
+        <v>1.28</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>613000</v>
+        <v>816800</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>1</v>
+        <v>0.31</v>
       </c>
       <c r="H118" t="n">
-        <v>56.44</v>
+        <v>52.99</v>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
@@ -5802,10 +5800,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>1.267</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.663</v>
+        <v>1.186</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5818,28 +5816,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.28</v>
+        <v>0.635</v>
       </c>
       <c r="E119" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>602800</v>
+        <v>805000</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.16</v>
+        <v>0.77</v>
       </c>
       <c r="H119" t="n">
-        <v>53.94</v>
+        <v>55.02</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5847,10 +5845,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.266</v>
+        <v>0.633</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.271</v>
+        <v>0.632</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5863,28 +5861,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v>0.0171</v>
+        <v>2.68</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>589500</v>
+        <v>784500</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="H120" t="n">
-        <v>35.01</v>
+        <v>35.99</v>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
@@ -5892,10 +5890,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>2.629</v>
+        <v>2.831</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>2.828</v>
+        <v>2.97</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5908,28 +5906,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>-0.0408</v>
+        <v>0.7</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>583500</v>
+        <v>752400</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.57</v>
+        <v>0.32</v>
       </c>
       <c r="H121" t="n">
-        <v>26.97</v>
+        <v>37.78</v>
       </c>
       <c r="I121" s="17" t="inlineStr">
         <is>
@@ -5937,10 +5935,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.557</v>
+        <v>0.756</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.622</v>
+        <v>0.768</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5953,28 +5951,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.74</v>
+        <v>0.59</v>
       </c>
       <c r="E122" s="15" t="n">
-        <v>0.0116</v>
+        <v>0.0172</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>582000</v>
+        <v>738600</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="H122" t="n">
-        <v>43.72</v>
+        <v>54.77</v>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
@@ -5982,10 +5980,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.753</v>
+        <v>0.576</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.854</v>
+        <v>0.485</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5998,39 +5996,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.805</v>
+        <v>0.64</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>-0.0123</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>554100</v>
+        <v>724000</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="H123" t="n">
-        <v>29.03</v>
-      </c>
-      <c r="I123" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.65</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.832</v>
+        <v>0.64</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.856</v>
+        <v>0.628</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6043,28 +6041,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v>0</v>
+        <v>4.46</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>537200</v>
+        <v>722000</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H124" t="n">
-        <v>42.28</v>
+        <v>37.41</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6072,10 +6070,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.713</v>
+        <v>4.559</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.77</v>
+        <v>4.64</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6088,28 +6086,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>-0.0072</v>
+        <v>1.28</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>537100</v>
+        <v>720200</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="H125" t="n">
-        <v>56.76</v>
+        <v>53.94</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6117,10 +6115,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>6.807</v>
+        <v>1.266</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>6.822</v>
+        <v>1.271</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6142,19 +6140,19 @@
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>-0.0169</v>
+        <v>6.52</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0.0015</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>534200</v>
+        <v>718100</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H126" t="n">
-        <v>53.57</v>
+        <v>55.76</v>
       </c>
       <c r="I126" s="17" t="inlineStr">
         <is>
@@ -6162,10 +6160,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>6.288</v>
+        <v>6.299</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>5.997</v>
+        <v>5.999</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6178,28 +6176,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>-0.0203</v>
+        <v>0.93</v>
+      </c>
+      <c r="E127" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>520300</v>
+        <v>688000</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H127" t="n">
-        <v>48.66</v>
+        <v>34.33</v>
       </c>
       <c r="I127" s="17" t="inlineStr">
         <is>
@@ -6207,10 +6205,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.741</v>
+        <v>0.952</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.707</v>
+        <v>1.033</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6223,45 +6221,990 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="E128" s="15" t="n">
-        <v>0.128</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>506700</v>
+        <v>676300</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>1.86</v>
+        <v>0.09</v>
       </c>
       <c r="H128" t="n">
-        <v>78.51000000000001</v>
-      </c>
-      <c r="I128" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.01</v>
+      </c>
+      <c r="I128" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.168</v>
+        <v>1.273</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.193</v>
+        <v>1.316</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>669700</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H129" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>4.437</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>4.441</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>656700</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H130" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>-0.0299</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>650300</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H131" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="I131" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>620000</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>42.28</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E133" s="15" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>618700</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H133" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="I133" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>613000</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>608600</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H135" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>10.462</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>9.872</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>606700</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H136" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="I136" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>-0.0135</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>604700</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>LWSABAH</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>589100</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H138" t="n">
+        <v>26.97</v>
+      </c>
+      <c r="I138" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>582100</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H139" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="I139" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>569300</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H140" t="n">
+        <v>48.19</v>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>3.801</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>3.741</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>563200</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H141" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>-0.004699999999999999</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>557500</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H142" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>2.105</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>555200</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H143" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="I143" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>1.716</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>528800</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H144" t="n">
+        <v>59.43</v>
+      </c>
+      <c r="I144" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>2.817</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7197</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>GESHEN</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E145" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>526900</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H145" t="n">
+        <v>78.02</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>525500</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H146" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="I146" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E147" s="15" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>520500</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H147" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="I147" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>MAXIS</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>513600</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H148" t="n">
+        <v>58.39</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>3.537</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>3.578</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>511900</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H149" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="I149" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M128"/>
+  <autoFilter ref="A1:M149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
+++ b/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,28 +557,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.505</v>
+        <v>0.74</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0412</v>
+        <v>0.0571</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5298300</v>
+        <v>1284200</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>56.25</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.49</v>
+        <v>0.644</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.485</v>
+        <v>0.615</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,62 +598,54 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.505高于50日均线0.485，RSI 56.25处中性区间，未超买，信号技术面较可靠。</t>
+          <t>RSI 80.1 已处超买区，现价高于50日均线约20%，SAR转多信号可靠性受超买制约。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>5073</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>NAIM</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0.0571</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>1218200</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>-0.0667</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>101589700</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H3" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>🎯 SAR 转多</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>RSI 80.1 已处超买区，现价高于50日均线约20%，SAR转多信号可靠性受超买制约。</t>
-        </is>
-      </c>
+      <c r="J3" s="9" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -663,28 +655,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>-0.0667</v>
+        <v>0.19</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0.3571</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>95587000</v>
+        <v>59938800</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.26</v>
+        <v>64.84</v>
       </c>
       <c r="H4" t="n">
-        <v>32.63</v>
+        <v>86.39</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -692,10 +684,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.099</v>
+        <v>0.12</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.259</v>
+        <v>0.116</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -708,28 +700,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>0.3929</v>
+        <v>0.47</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>58876200</v>
+        <v>44134100</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>63.69</v>
+        <v>1.21</v>
       </c>
       <c r="H5" t="n">
-        <v>87.01000000000001</v>
+        <v>70.62</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -737,10 +729,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.12</v>
+        <v>0.419</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.117</v>
+        <v>0.318</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -753,28 +745,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.475</v>
+        <v>0.15</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>-0.0306</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>37498600</v>
+        <v>40561300</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.03</v>
+        <v>0.65</v>
       </c>
       <c r="H6" t="n">
-        <v>72.55</v>
+        <v>46.87</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -782,10 +774,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.42</v>
+        <v>0.159</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.318</v>
+        <v>0.147</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -798,28 +790,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>-0.1212</v>
+        <v>0.09</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>36639200</v>
+        <v>22323200</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.59</v>
+        <v>9.16</v>
       </c>
       <c r="H7" t="n">
-        <v>44.98</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -827,10 +819,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.159</v>
+        <v>0.078</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.147</v>
+        <v>0.076</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -843,28 +835,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>0069</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>VINVEST</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.03</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>22273200</v>
+        <v>20532200</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>9.140000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="H8" t="n">
-        <v>78.40000000000001</v>
+        <v>70.62</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -872,10 +864,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.078</v>
+        <v>0.019</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.076</v>
+        <v>0.018</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -888,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0069</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VINVEST</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.1667</v>
+        <v>0.055</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>20342100</v>
+        <v>16177300</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>7.81</v>
+        <v>1.97</v>
       </c>
       <c r="H9" t="n">
-        <v>74.81</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.63</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.019</v>
+        <v>0.049</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.018</v>
+        <v>0.047</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -933,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.055</v>
+        <v>0.74</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>16157300</v>
+        <v>15535300</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.97</v>
+        <v>0.64</v>
       </c>
       <c r="H10" t="n">
-        <v>58.63</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.92</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.049</v>
+        <v>0.66</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.047</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -978,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.305</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>13049200</v>
+        <v>14740700</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="H11" t="n">
-        <v>84.41</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.66</v>
+        <v>0.307</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.302</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1023,28 +1015,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
+        <v>0.155</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>12402600</v>
+        <v>14097100</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.77</v>
+        <v>0.39</v>
       </c>
       <c r="H12" t="n">
-        <v>54.27</v>
+        <v>47.73</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1052,10 +1044,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1068,39 +1060,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.305</v>
+        <v>0.82</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>11902700</v>
+        <v>13745000</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="H13" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.307</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.302</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1113,28 +1105,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>-0.0185</v>
+        <v>0.38</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>11799000</v>
+        <v>11991900</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="H14" t="n">
-        <v>41.24</v>
+        <v>31.76</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -1142,10 +1134,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.286</v>
+        <v>0.39</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.279</v>
+        <v>0.403</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1158,28 +1150,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.265</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>11685800</v>
+        <v>11856700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="H15" t="n">
-        <v>31.76</v>
+        <v>41.24</v>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
@@ -1187,10 +1179,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.39</v>
+        <v>0.286</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.403</v>
+        <v>0.279</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1203,28 +1195,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.022</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>10459200</v>
+        <v>11197900</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>60.52</v>
+        <v>61.85</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1232,10 +1224,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.316</v>
+        <v>0.433</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.266</v>
+        <v>0.385</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1248,39 +1240,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.0054</v>
+        <v>0.33</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>9609000</v>
+        <v>10743700</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0.13</v>
       </c>
       <c r="H17" t="n">
-        <v>65.45</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.52</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.86</v>
+        <v>0.316</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.763</v>
+        <v>0.266</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1293,39 +1285,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0</v>
+        <v>0.27</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>9370000</v>
+        <v>10527800</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.6</v>
+        <v>2.05</v>
       </c>
       <c r="H18" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.73</v>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.775</v>
+        <v>0.267</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.776</v>
+        <v>0.27</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1338,28 +1330,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>-0.0313</v>
+        <v>0.925</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.0054</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>9361100</v>
+        <v>10483800</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="H19" t="n">
-        <v>47.73</v>
+        <v>65.45</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -1367,10 +1359,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.156</v>
+        <v>0.86</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.156</v>
+        <v>0.763</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1383,39 +1375,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.0392</v>
+        <v>0.775</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>9294300</v>
+        <v>10285300</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.81</v>
+        <v>0.66</v>
       </c>
       <c r="H20" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.44</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.267</v>
+        <v>0.775</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.269</v>
+        <v>0.776</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1428,28 +1420,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.022</v>
+        <v>5.03</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.0545</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9264500</v>
+        <v>9688400</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="H21" t="n">
-        <v>61.85</v>
+        <v>34.46</v>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
@@ -1457,10 +1449,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.433</v>
+        <v>5.404</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.385</v>
+        <v>5.51</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1473,40 +1465,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>-0.0526</v>
+        <v>0.19</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>8474300</v>
+        <v>9397100</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H22" t="n">
-        <v>34.72</v>
+        <v>0.27</v>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J22" s="9" t="n">
-        <v>5.405</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>5.511</v>
-      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1518,33 +1503,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.185</v>
+        <v>0.865</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>-0.0263</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8434500</v>
+        <v>8322200</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
+        <v>0.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.869</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1556,28 +1548,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>0</v>
+        <v>1.99</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>-0.0386</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7775000</v>
+        <v>8296800</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>8.51</v>
+        <v>0.74</v>
       </c>
       <c r="H24" t="n">
-        <v>47.02</v>
+        <v>33.25</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
@@ -1585,10 +1577,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.005</v>
+        <v>2.106</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.006</v>
+        <v>2.23</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1601,28 +1593,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>-0.0386</v>
+        <v>0.005</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7339700</v>
+        <v>8075000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.66</v>
+        <v>8.84</v>
       </c>
       <c r="H25" t="n">
-        <v>33.25</v>
+        <v>47.02</v>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
@@ -1630,10 +1622,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>2.106</v>
+        <v>0.005</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>2.23</v>
+        <v>0.006</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1655,16 +1647,16 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>-0.0493</v>
+        <v>-0.0352</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6979300</v>
+        <v>7473500</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
@@ -1684,28 +1676,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>0.04</v>
+        <v>0.0244</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6450600</v>
+        <v>7181300</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1.73</v>
+        <v>0.61</v>
       </c>
       <c r="H27" t="n">
-        <v>49.54</v>
+        <v>57.53</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1713,10 +1705,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.898</v>
+        <v>0.402</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.958</v>
+        <v>0.383</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1729,39 +1721,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.905</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.0343</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6240300</v>
+        <v>6862700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.82</v>
+        <v>1.84</v>
       </c>
       <c r="H28" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.12</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.423</v>
+        <v>0.897</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.439</v>
+        <v>0.958</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1774,39 +1766,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.055</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6155100</v>
+        <v>6503600</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.3</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.43</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.868</v>
+        <v>0.062</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.869</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1819,39 +1811,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.9350000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.0331</v>
+        <v>0.029</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5899500</v>
+        <v>6350700</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="H30" t="n">
-        <v>40.62</v>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.38</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>1.005</v>
+        <v>1.969</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.981</v>
+        <v>1.961</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1864,39 +1856,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.415</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>0.0122</v>
+        <v>0.0331</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5882300</v>
+        <v>6252200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="H31" t="n">
-        <v>56.17</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.62</v>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.401</v>
+        <v>1.005</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.383</v>
+        <v>0.981</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1909,28 +1901,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.05</v>
+        <v>0.385</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.04940000000000001</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5843500</v>
+        <v>6243000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="H32" t="n">
-        <v>34.17</v>
+        <v>37.96</v>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
@@ -1938,10 +1930,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.061</v>
+        <v>0.423</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.439</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1954,28 +1946,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.635</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5778400</v>
+        <v>6132700</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.3</v>
+        <v>0.58</v>
       </c>
       <c r="H33" t="n">
-        <v>66.55</v>
+        <v>60.81</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1983,10 +1975,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.099</v>
+        <v>0.624</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.618</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1999,39 +1991,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2.13</v>
+        <v>0.195</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.029</v>
+        <v>0.0263</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5760400</v>
+        <v>5926400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="H34" t="n">
-        <v>70.38</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.92</v>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>1.969</v>
+        <v>0.209</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.961</v>
+        <v>0.229</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2044,39 +2036,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>0.0526</v>
+        <v>0.0476</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5687000</v>
+        <v>5778400</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="H35" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.55</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.209</v>
+        <v>0.099</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.229</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2089,28 +2081,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0309</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5608300</v>
+        <v>5463000</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.53</v>
+        <v>2.35</v>
       </c>
       <c r="H36" t="n">
-        <v>60.81</v>
+        <v>54.66</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2118,10 +2110,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.624</v>
+        <v>0.49</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.618</v>
+        <v>0.485</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2134,39 +2126,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>0.0267</v>
+        <v>0.415</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4806200</v>
+        <v>5338500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.44</v>
+        <v>0.15</v>
       </c>
       <c r="H37" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.3</v>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.469</v>
+        <v>0.455</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.583</v>
+        <v>0.474</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2179,39 +2171,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>0.0196</v>
+        <v>0.725</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>-0.0136</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4699600</v>
+        <v>5294200</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1.39</v>
+        <v>0.46</v>
       </c>
       <c r="H38" t="n">
-        <v>80.93000000000001</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.45</v>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.451</v>
+        <v>0.735</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.437</v>
+        <v>0.725</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2224,28 +2216,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>-0.0133</v>
+        <v>0.38</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4563400</v>
+        <v>5281700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.67</v>
+        <v>0.48</v>
       </c>
       <c r="H39" t="n">
-        <v>48.14</v>
+        <v>28.85</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2253,10 +2245,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.372</v>
+        <v>0.469</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.37</v>
+        <v>0.583</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2269,28 +2261,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>1.41</v>
+        <v>2.02</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.0292</v>
+        <v>0.0151</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4514300</v>
+        <v>5181500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="H40" t="n">
-        <v>27.3</v>
+        <v>56.35</v>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
@@ -2298,10 +2290,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>1.576</v>
+        <v>1.968</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1.867</v>
+        <v>1.795</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2314,28 +2306,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.73</v>
+        <v>2.49</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>-0.0068</v>
+        <v>-0.008</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4243500</v>
+        <v>5175900</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.37</v>
+        <v>0.27</v>
       </c>
       <c r="H41" t="n">
-        <v>49.17</v>
+        <v>43.45</v>
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
@@ -2343,10 +2335,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.735</v>
+        <v>2.593</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.725</v>
+        <v>2.559</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2359,40 +2351,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.295</v>
+        <v>0.005</v>
       </c>
       <c r="E42" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4143400</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H42" t="n">
-        <v>49.06</v>
-      </c>
+        <v>5138100</v>
+      </c>
+      <c r="G42" s="12" t="n"/>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J42" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="K42" s="9" t="n">
-        <v>0.295</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
     </row>
@@ -2404,39 +2387,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>-0.0118</v>
+        <v>0.52</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4075400</v>
+        <v>4832900</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.11</v>
+        <v>1.43</v>
       </c>
       <c r="H43" t="n">
-        <v>37.37</v>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.93000000000001</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.455</v>
+        <v>0.451</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.475</v>
+        <v>0.437</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2449,28 +2432,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>-0.004</v>
+        <v>1.4</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0219</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4047300</v>
+        <v>4662700</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="H44" t="n">
-        <v>43.98</v>
+        <v>25.96</v>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
@@ -2478,10 +2461,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>2.594</v>
+        <v>1.575</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>2.56</v>
+        <v>1.867</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2494,39 +2477,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.0101</v>
+        <v>0.37</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4003900</v>
+        <v>4566800</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.14</v>
+        <v>0.67</v>
       </c>
       <c r="H45" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="I45" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.14</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.967</v>
+        <v>0.372</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.795</v>
+        <v>0.37</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2554,10 +2537,10 @@
         <v>-0.0217</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3999700</v>
+        <v>4421700</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H46" t="n">
         <v>51.42</v>
@@ -2580,39 +2563,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>0.019</v>
+        <v>2.64</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3911100</v>
+        <v>4318600</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>1.87</v>
+        <v>0.41</v>
       </c>
       <c r="H47" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.17</v>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>2.114</v>
+        <v>2.73</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>2.078</v>
+        <v>2.746</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2625,39 +2608,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0</v>
+        <v>1.14</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3687100</v>
+        <v>4316200</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="H48" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.43</v>
+      </c>
+      <c r="I48" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.805</v>
+        <v>1.203</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.779</v>
+        <v>1.29</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2670,39 +2653,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0.0179</v>
+        <v>0.625</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3670700</v>
+        <v>4180700</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.59</v>
+        <v>1.19</v>
       </c>
       <c r="H49" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I49" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.67</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>1.3</v>
+        <v>0.62</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>1.502</v>
+        <v>0.61</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2715,39 +2698,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>-0.0105</v>
+        <v>0.295</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3529800</v>
+        <v>4143400</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.16</v>
+        <v>1.22</v>
       </c>
       <c r="H50" t="n">
-        <v>46.16</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.06</v>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>4.726</v>
+        <v>0.295</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>4.811</v>
+        <v>0.295</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2760,39 +2743,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>0</v>
+        <v>3.39</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3485500</v>
+        <v>3955000</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.46</v>
+        <v>1.27</v>
       </c>
       <c r="H51" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.23999999999999</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.204</v>
+        <v>3.042</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.29</v>
+        <v>2.577</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2805,39 +2788,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.17</v>
+        <v>2.14</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.019</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3454500</v>
+        <v>3928900</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="H52" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="I52" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.64</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.166</v>
+        <v>2.114</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.156</v>
+        <v>2.078</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2850,28 +2833,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>0.0097</v>
+        <v>4.7</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3435300</v>
+        <v>3903200</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.45</v>
+        <v>0.18</v>
       </c>
       <c r="H53" t="n">
-        <v>65.16</v>
+        <v>46.16</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2879,10 +2862,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>3.799</v>
+        <v>4.726</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>3.248</v>
+        <v>4.811</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2895,39 +2878,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.0058</v>
+        <v>1.14</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3411100</v>
+        <v>3814600</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1.09</v>
+        <v>0.62</v>
       </c>
       <c r="H54" t="n">
-        <v>86.48</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.3</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>3.043</v>
+        <v>1.3</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>2.578</v>
+        <v>1.502</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2940,39 +2923,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.265</v>
+        <v>0.825</v>
       </c>
       <c r="E55" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3231500</v>
+        <v>3775500</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="H55" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="I55" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.73</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.282</v>
+        <v>0.805</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.282</v>
+        <v>0.779</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2985,39 +2968,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.0345</v>
+        <v>4.2</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3143900</v>
+        <v>3699600</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
       <c r="H56" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.76000000000001</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.821</v>
+        <v>3.802</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.627</v>
+        <v>3.249</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3030,39 +3013,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.63</v>
+        <v>0.17</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>0.0062</v>
+        <v>0.0303</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2760900</v>
+        <v>3514500</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.34</v>
+        <v>1.57</v>
       </c>
       <c r="H57" t="n">
-        <v>49.41</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.01</v>
+      </c>
+      <c r="I57" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.625</v>
+        <v>0.166</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1.675</v>
+        <v>0.156</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3075,39 +3058,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.7</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2658500</v>
+        <v>3487700</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>1.56</v>
+        <v>0.73</v>
       </c>
       <c r="H58" t="n">
-        <v>54.47</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.54</v>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>1.37</v>
+        <v>0.821</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1.44</v>
+        <v>0.627</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3120,36 +3103,36 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PCCS</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>0.05</v>
+        <v>0.265</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2615900</v>
+        <v>3336100</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>20.75</v>
+        <v>0.47</v>
       </c>
       <c r="H59" t="n">
-        <v>75.47</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.25</v>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.285</v>
+        <v>0.282</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0.282</v>
@@ -3165,39 +3148,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>-0.0112</v>
+        <v>1.63</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2614700</v>
+        <v>3274700</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="H60" t="n">
-        <v>42.85</v>
-      </c>
-      <c r="I60" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.41</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.731</v>
+        <v>1.625</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.746</v>
+        <v>1.675</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3210,39 +3193,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2609900</v>
+        <v>3243700</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="H61" t="n">
-        <v>36.35</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.66</v>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.314</v>
+        <v>0.186</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.359</v>
+        <v>0.186</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3255,28 +3238,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>0</v>
+        <v>1.39</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0.053</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2360700</v>
+        <v>3029400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.26</v>
+        <v>1.77</v>
       </c>
       <c r="H62" t="n">
-        <v>59.07</v>
+        <v>50.62</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3284,10 +3267,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.093</v>
+        <v>1.367</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.056</v>
+        <v>1.439</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3300,39 +3283,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>PCCS</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>-0.0062</v>
+        <v>0.315</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.05</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2237500</v>
+        <v>2820900</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.09</v>
+        <v>22.37</v>
       </c>
       <c r="H63" t="n">
-        <v>47.76</v>
-      </c>
-      <c r="I63" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.47</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>4.87</v>
+        <v>0.285</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>4.764</v>
+        <v>0.282</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3345,39 +3328,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.295</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2168300</v>
+        <v>2786200</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.13</v>
+        <v>0.42</v>
       </c>
       <c r="H64" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="I64" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.35</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>7.359</v>
+        <v>0.314</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>7.625</v>
+        <v>0.359</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3390,28 +3373,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.33</v>
+        <v>7.09</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>-0.0149</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2138200</v>
+        <v>2711700</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H65" t="n">
-        <v>43.09</v>
+        <v>31.13</v>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
@@ -3419,10 +3402,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.348</v>
+        <v>7.359</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.33</v>
+        <v>7.624</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3435,28 +3418,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.23</v>
+        <v>1.15</v>
       </c>
       <c r="E66" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2136900</v>
+        <v>2698900</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>1.53</v>
+        <v>0.29</v>
       </c>
       <c r="H66" t="n">
-        <v>48.11</v>
+        <v>59.07</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3464,10 +3447,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.23</v>
+        <v>1.093</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.238</v>
+        <v>1.056</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3480,28 +3463,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>0.0298</v>
+        <v>0.555</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2065500</v>
+        <v>2605000</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.54</v>
+        <v>1.33</v>
       </c>
       <c r="H67" t="n">
-        <v>58.16</v>
+        <v>45.18</v>
       </c>
       <c r="I67" s="17" t="inlineStr">
         <is>
@@ -3509,10 +3492,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.83</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.799</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3540,10 +3523,10 @@
         <v>-0.005699999999999999</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1993000</v>
+        <v>2565000</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="H68" t="n">
         <v>50.44</v>
@@ -3570,39 +3553,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>5.72</v>
+        <v>0.755</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>-0.0052</v>
+        <v>-0.0066</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1992200</v>
+        <v>2483200</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="H69" t="n">
-        <v>38.83</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.8</v>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>5.826</v>
+        <v>0.767</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>6.086</v>
+        <v>0.771</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3615,39 +3598,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.755</v>
+        <v>5.73</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>-0.0066</v>
+        <v>-0.0035</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1963200</v>
+        <v>2447400</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="H70" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="I70" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.34</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.767</v>
+        <v>5.827</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.771</v>
+        <v>6.087</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3660,28 +3643,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>0.0049</v>
+        <v>4.82</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1938600</v>
+        <v>2370500</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.48</v>
+        <v>0.1</v>
       </c>
       <c r="H71" t="n">
-        <v>48.91</v>
+        <v>47.76</v>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
@@ -3689,10 +3672,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.039</v>
+        <v>4.87</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.064</v>
+        <v>4.764</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3705,28 +3688,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.835</v>
+        <v>0.855</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>0.0245</v>
+        <v>0.0179</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1936100</v>
+        <v>2286900</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.31</v>
+        <v>0.6</v>
       </c>
       <c r="H72" t="n">
-        <v>43.04</v>
+        <v>56.61</v>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
@@ -3734,10 +3717,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.885</v>
+        <v>0.829</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.859</v>
+        <v>0.799</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3750,28 +3733,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KEYFIELD</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>-0.0071</v>
+        <v>2.04</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1807000</v>
+        <v>2267600</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>9.109999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>50.67</v>
+        <v>48.91</v>
       </c>
       <c r="I73" s="17" t="inlineStr">
         <is>
@@ -3779,10 +3762,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>1.389</v>
+        <v>2.039</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1.372</v>
+        <v>2.064</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3795,28 +3778,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.325</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1753600</v>
+        <v>2242000</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="H74" t="n">
-        <v>35.3</v>
+        <v>41.45</v>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
@@ -3824,10 +3807,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.656</v>
+        <v>0.348</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.741</v>
+        <v>0.33</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3840,28 +3823,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>-0.0039</v>
+        <v>-0.0042</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1725400</v>
+        <v>2231800</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H75" t="n">
-        <v>45.76</v>
+        <v>42.66</v>
       </c>
       <c r="I75" s="17" t="inlineStr">
         <is>
@@ -3869,10 +3852,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.594</v>
+        <v>2.433</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.604</v>
+        <v>2.412</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3885,38 +3868,40 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.37</v>
+        <v>4.21</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.0423</v>
+        <v>0.0525</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1720600</v>
+        <v>2223600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H76" t="n">
-        <v>61.24</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.59</v>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="K76" s="9" t="n"/>
+        <v>3.984</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>3.644</v>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
     </row>
@@ -3928,28 +3913,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>0.435</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0116</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1716200</v>
+        <v>2176400</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="H77" t="n">
-        <v>44.09</v>
+        <v>27.55</v>
       </c>
       <c r="I77" s="17" t="inlineStr">
         <is>
@@ -3957,10 +3942,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>6.342</v>
+        <v>0.479</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>6.646</v>
+        <v>0.619</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3973,39 +3958,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0.0116</v>
+        <v>0.225</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1661400</v>
+        <v>2147000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.1</v>
+        <v>1.53</v>
       </c>
       <c r="H78" t="n">
-        <v>27.55</v>
-      </c>
-      <c r="I78" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.32</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.479</v>
+        <v>0.23</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.619</v>
+        <v>0.237</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4018,28 +4003,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>-0.0042</v>
+        <v>0.835</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>0.0245</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1589500</v>
+        <v>2083000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.14</v>
+        <v>0.34</v>
       </c>
       <c r="H79" t="n">
-        <v>42.66</v>
+        <v>43.04</v>
       </c>
       <c r="I79" s="17" t="inlineStr">
         <is>
@@ -4047,10 +4032,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>2.433</v>
+        <v>0.885</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>2.412</v>
+        <v>0.859</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4063,40 +4048,38 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>4.2</v>
+        <v>0.365</v>
       </c>
       <c r="E80" s="15" t="n">
-        <v>0.05</v>
+        <v>0.0282</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1584100</v>
+        <v>2069100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="H80" t="n">
-        <v>60.31</v>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.1</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>3.983</v>
-      </c>
-      <c r="K80" s="9" t="n">
-        <v>3.644</v>
-      </c>
+        <v>0.337</v>
+      </c>
+      <c r="K80" s="9" t="n"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
     </row>
@@ -4108,28 +4091,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.0072</v>
+        <v>0.755</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1554100</v>
+        <v>2034100</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.19</v>
+        <v>1.44</v>
       </c>
       <c r="H81" t="n">
-        <v>52</v>
+        <v>55.46</v>
       </c>
       <c r="I81" s="17" t="inlineStr">
         <is>
@@ -4137,10 +4120,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>2.788</v>
+        <v>0.75</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>2.69</v>
+        <v>0.723</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4153,39 +4136,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>6.88</v>
+        <v>6.27</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>-0.0101</v>
+        <v>-0.0126</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1531100</v>
+        <v>2026300</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="H82" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.17</v>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>6.806</v>
+        <v>6.34</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>6.822</v>
+        <v>6.646</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4198,28 +4181,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>0</v>
+        <v>1.57</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0.0129</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1511100</v>
+        <v>1951400</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.17</v>
+        <v>0.32</v>
       </c>
       <c r="H83" t="n">
-        <v>37</v>
+        <v>36.76</v>
       </c>
       <c r="I83" s="17" t="inlineStr">
         <is>
@@ -4227,10 +4210,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.608</v>
+        <v>1.657</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.616</v>
+        <v>1.741</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4243,39 +4226,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>KEYFIELD</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>0.0227</v>
+        <v>1.38</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1462000</v>
+        <v>1822000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>1.48</v>
+        <v>9.19</v>
       </c>
       <c r="H84" t="n">
-        <v>50.21</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.48</v>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.223</v>
+        <v>1.388</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.23</v>
+        <v>1.372</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4288,28 +4271,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.755</v>
+        <v>1.21</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>0.0342</v>
+        <v>0.0168</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1407900</v>
+        <v>1773700</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H85" t="n">
-        <v>54.07</v>
+        <v>56.17</v>
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
@@ -4317,10 +4300,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.74</v>
+        <v>1.177</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.149</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4333,39 +4316,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>0.0147</v>
+        <v>2.55</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>-0.0039</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1400400</v>
+        <v>1772900</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>0.31</v>
       </c>
       <c r="H86" t="n">
-        <v>57.71</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.76</v>
+      </c>
+      <c r="I86" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.337</v>
+        <v>2.594</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.343</v>
+        <v>2.604</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4378,39 +4361,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0.0126</v>
+        <v>0.545</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1392200</v>
+        <v>1702400</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.4</v>
+        <v>0.19</v>
       </c>
       <c r="H87" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37</v>
+      </c>
+      <c r="I87" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.289</v>
+        <v>0.608</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>2.208</v>
+        <v>0.616</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4423,39 +4406,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>0</v>
+        <v>2.81</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1377500</v>
+        <v>1674600</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="H88" t="n">
-        <v>52.42</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.55</v>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.429</v>
+        <v>2.789</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.418</v>
+        <v>2.69</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4468,28 +4451,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0112</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1369800</v>
+        <v>1631200</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0.17</v>
       </c>
       <c r="H89" t="n">
-        <v>36.66</v>
+        <v>42.42</v>
       </c>
       <c r="I89" s="17" t="inlineStr">
         <is>
@@ -4497,10 +4480,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.646</v>
+        <v>0.492</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.469</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4513,28 +4496,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>-0.015</v>
+        <v>0.75</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0.0274</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1334400</v>
+        <v>1610700</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
       <c r="H90" t="n">
-        <v>44.83</v>
+        <v>53.34</v>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
@@ -4542,10 +4525,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>1.024</v>
+        <v>0.74</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.973</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4558,28 +4541,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E91" s="15" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.585</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1274600</v>
+        <v>1581900</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H91" t="n">
-        <v>54.86</v>
+        <v>35.41</v>
       </c>
       <c r="I91" s="17" t="inlineStr">
         <is>
@@ -4587,10 +4570,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.176</v>
+        <v>0.646</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.149</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4603,39 +4586,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>0</v>
+        <v>6.87</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1274500</v>
+        <v>1576700</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="H92" t="n">
-        <v>41.39</v>
-      </c>
-      <c r="I92" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.75</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.491</v>
+        <v>6.805</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.469</v>
+        <v>6.822</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4648,28 +4631,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>-0.008</v>
+        <v>2.42</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>0.0126</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1273100</v>
+        <v>1569900</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="H93" t="n">
-        <v>54.1</v>
+        <v>62.86</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4677,10 +4660,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.62</v>
+        <v>2.289</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.61</v>
+        <v>2.208</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4693,28 +4676,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>0</v>
+        <v>1.07</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1264000</v>
+        <v>1548500</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.64</v>
+        <v>0.41</v>
       </c>
       <c r="H94" t="n">
-        <v>45.18</v>
+        <v>49.98</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -4722,10 +4705,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.096</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.926</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4738,39 +4721,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>0.0283</v>
+        <v>0.024</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1259100</v>
+        <v>1466200</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="H95" t="n">
-        <v>52.05</v>
-      </c>
-      <c r="I95" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.18</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.098</v>
+        <v>1.228</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.927</v>
+        <v>1.206</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4783,28 +4766,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.225</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1258400</v>
+        <v>1462000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.1</v>
+        <v>1.48</v>
       </c>
       <c r="H96" t="n">
-        <v>48</v>
+        <v>50.21</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4812,10 +4795,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>9.996</v>
+        <v>0.223</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>10.112</v>
+        <v>0.23</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4828,28 +4811,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.985</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.015</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1256000</v>
+        <v>1437900</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.72</v>
+        <v>0.4</v>
       </c>
       <c r="H97" t="n">
-        <v>48.61</v>
+        <v>44.83</v>
       </c>
       <c r="I97" s="17" t="inlineStr">
         <is>
@@ -4857,10 +4840,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.905</v>
+        <v>1.024</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.892</v>
+        <v>0.973</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4873,39 +4856,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v>0</v>
+        <v>0.345</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1164500</v>
+        <v>1410000</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H98" t="n">
-        <v>40.12</v>
-      </c>
-      <c r="I98" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.71</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.123</v>
+        <v>0.337</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.112</v>
+        <v>0.343</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4918,39 +4901,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>-0.0174</v>
+        <v>0.435</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1159100</v>
+        <v>1401100</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="H99" t="n">
-        <v>29.22</v>
-      </c>
-      <c r="I99" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.42</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.198</v>
+        <v>0.429</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.303</v>
+        <v>0.418</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4963,40 +4946,38 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.3</v>
+        <v>0.225</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>-0.0323</v>
+        <v>-0.0217</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1114800</v>
+        <v>1338200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="H100" t="n">
-        <v>49.39</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>14</v>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="K100" s="9" t="n">
-        <v>0.327</v>
-      </c>
+        <v>0.257</v>
+      </c>
+      <c r="K100" s="9" t="n"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
     </row>
@@ -5008,39 +4989,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>2.37</v>
+        <v>9.99</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>-0.0042</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1112000</v>
+        <v>1335800</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.27</v>
+        <v>0.11</v>
       </c>
       <c r="H101" t="n">
-        <v>33.15</v>
-      </c>
-      <c r="I101" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>2.48</v>
+        <v>9.996</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2.645</v>
+        <v>10.112</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5053,39 +5034,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.965</v>
+        <v>2.38</v>
       </c>
       <c r="E102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1111000</v>
+        <v>1315500</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="H102" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.86</v>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.9429999999999999</v>
+        <v>2.481</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.892</v>
+        <v>2.646</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5098,39 +5079,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>0.0027</v>
+        <v>0.55</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1081500</v>
+        <v>1282600</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H103" t="n">
-        <v>41.43</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I103" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>7.411</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>7.819</v>
+        <v>0.546</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5143,28 +5124,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>-0.0061</v>
+        <v>0.895</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1058600</v>
+        <v>1256000</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.37</v>
+        <v>0.72</v>
       </c>
       <c r="H104" t="n">
-        <v>29.37</v>
+        <v>48.61</v>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
@@ -5172,10 +5153,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.867</v>
+        <v>0.905</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.931</v>
+        <v>0.892</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5188,28 +5169,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.615</v>
+        <v>0.225</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>0.0165</v>
+        <v>0.0227</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1041700</v>
+        <v>1255500</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.34</v>
+        <v>2.91</v>
       </c>
       <c r="H105" t="n">
-        <v>35.18</v>
+        <v>51.18</v>
       </c>
       <c r="I105" s="17" t="inlineStr">
         <is>
@@ -5217,10 +5198,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.68</v>
+        <v>0.225</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.734</v>
+        <v>0.224</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5233,28 +5214,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>-0.0179</v>
+        <v>0.31</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1033100</v>
+        <v>1222600</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.05</v>
+        <v>0.96</v>
       </c>
       <c r="H106" t="n">
-        <v>47.42</v>
+        <v>43.1</v>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
@@ -5262,10 +5243,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.315</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.546</v>
+        <v>0.328</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5278,39 +5259,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>0</v>
+        <v>6.77</v>
+      </c>
+      <c r="E107" s="15" t="n">
+        <v>0.0059</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1015500</v>
+        <v>1218200</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.88</v>
+        <v>0.11</v>
       </c>
       <c r="H107" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.66</v>
+      </c>
+      <c r="I107" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.441</v>
+        <v>7.051</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.44</v>
+        <v>7.494</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5323,39 +5304,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.585</v>
+        <v>7.34</v>
       </c>
       <c r="E108" s="15" t="n">
-        <v>0.0086</v>
+        <v>0.0027</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1014500</v>
+        <v>1202200</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="H108" t="n">
-        <v>62.18</v>
-      </c>
-      <c r="I108" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.43</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.54</v>
+        <v>7.411</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.485</v>
+        <v>7.819</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5368,28 +5349,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>0.0074</v>
+        <v>1.06</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1011400</v>
+        <v>1201400</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.09</v>
+        <v>0.36</v>
       </c>
       <c r="H109" t="n">
-        <v>37.07</v>
+        <v>40.12</v>
       </c>
       <c r="I109" s="17" t="inlineStr">
         <is>
@@ -5397,10 +5378,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>7.052</v>
+        <v>1.123</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>7.494</v>
+        <v>1.112</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5413,28 +5394,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>-0.0217</v>
+        <v>2.42</v>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>0.0342</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1007400</v>
+        <v>1200400</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.38</v>
+        <v>0.21</v>
       </c>
       <c r="H110" t="n">
-        <v>14</v>
+        <v>37.34</v>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
@@ -5442,9 +5423,11 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="K110" s="9" t="n"/>
+        <v>2.633</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>2.828</v>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
     </row>
@@ -5456,28 +5439,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.505</v>
+        <v>0.605</v>
       </c>
       <c r="E111" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>942600</v>
+        <v>1186700</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="H111" t="n">
-        <v>29.83</v>
+        <v>32.83</v>
       </c>
       <c r="I111" s="17" t="inlineStr">
         <is>
@@ -5485,10 +5468,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.529</v>
+        <v>0.679</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.734</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5501,39 +5484,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.965</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>908200</v>
+        <v>1169800</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="H112" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="I112" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.7</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.289</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.3</v>
+        <v>0.892</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5546,39 +5529,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0174</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>883500</v>
+        <v>1168500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="H113" t="n">
-        <v>53.67</v>
-      </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.22</v>
+      </c>
+      <c r="I113" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>1.245</v>
+        <v>1.198</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.115</v>
+        <v>1.303</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5591,39 +5574,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>0.0189</v>
+        <v>0.3</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>828600</v>
+        <v>1153800</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.16</v>
+        <v>0.88</v>
       </c>
       <c r="H114" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="I114" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.39</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.549</v>
+        <v>0.296</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.525</v>
+        <v>0.327</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5636,28 +5619,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E115" s="15" t="n">
-        <v>0.0219</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>823700</v>
+        <v>1144700</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H115" t="n">
-        <v>49.29</v>
+        <v>28.52</v>
       </c>
       <c r="I115" s="17" t="inlineStr">
         <is>
@@ -5665,10 +5648,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.925</v>
+        <v>0.867</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>1.011</v>
+        <v>0.931</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5681,39 +5664,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E116" s="16" t="n">
-        <v>0</v>
+        <v>0.585</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>821600</v>
+        <v>1061700</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="H116" t="n">
-        <v>55.64</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.18</v>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>1.226</v>
+        <v>0.54</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>1.205</v>
+        <v>0.485</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5726,39 +5709,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E117" s="15" t="n">
-        <v>0.0342</v>
+        <v>0.445</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>820800</v>
+        <v>1045500</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.15</v>
+        <v>0.91</v>
       </c>
       <c r="H117" t="n">
-        <v>37.34</v>
-      </c>
-      <c r="I117" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.98999999999999</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>2.633</v>
+        <v>0.441</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>2.828</v>
+        <v>0.44</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5771,28 +5754,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.24</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>816800</v>
+        <v>1012400</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="H118" t="n">
-        <v>52.99</v>
+        <v>43.14</v>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
@@ -5800,10 +5783,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.267</v>
+        <v>1.29</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1.186</v>
+        <v>1.3</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5816,39 +5799,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>805000</v>
+        <v>958300</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.77</v>
+        <v>0.37</v>
       </c>
       <c r="H119" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.28</v>
+      </c>
+      <c r="I119" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.633</v>
+        <v>1.264</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.632</v>
+        <v>1.186</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5861,39 +5844,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>2.68</v>
+        <v>1.26</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>-0.0147</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>784500</v>
+        <v>935200</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="H120" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="I120" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.67</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>2.831</v>
+        <v>1.245</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>2.97</v>
+        <v>1.115</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5906,39 +5889,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.7</v>
+        <v>1.28</v>
       </c>
       <c r="E121" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>752400</v>
+        <v>918900</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="H121" t="n">
-        <v>37.78</v>
-      </c>
-      <c r="I121" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.94</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.756</v>
+        <v>1.266</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.768</v>
+        <v>1.271</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5951,28 +5934,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v>0.0172</v>
+        <v>2.67</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0184</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>738600</v>
+        <v>902500</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H122" t="n">
-        <v>54.77</v>
+        <v>35.48</v>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
@@ -5980,10 +5963,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.576</v>
+        <v>2.83</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.485</v>
+        <v>2.97</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5996,28 +5979,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.7</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>724000</v>
+        <v>902100</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.34</v>
+        <v>0.15</v>
       </c>
       <c r="H123" t="n">
-        <v>51.65</v>
+        <v>42.28</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6025,10 +6008,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.64</v>
+        <v>0.713</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.628</v>
+        <v>0.77</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6041,39 +6024,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>-0.004500000000000001</v>
+        <v>0.93</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0.0164</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>722000</v>
+        <v>894600</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.08</v>
+        <v>0.87</v>
       </c>
       <c r="H124" t="n">
-        <v>37.41</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.51</v>
+      </c>
+      <c r="I124" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>4.559</v>
+        <v>0.925</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>4.64</v>
+        <v>1.011</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6086,39 +6069,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E125" s="16" t="n">
-        <v>0</v>
+        <v>6.5</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>-0.0015</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>720200</v>
+        <v>881100</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="H125" t="n">
-        <v>53.94</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.41</v>
+      </c>
+      <c r="I125" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>1.266</v>
+        <v>6.297</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>1.271</v>
+        <v>5.999</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6131,28 +6114,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>0.0015</v>
+        <v>1.3</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>718100</v>
+        <v>874300</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="H126" t="n">
-        <v>55.76</v>
+        <v>51.71</v>
       </c>
       <c r="I126" s="17" t="inlineStr">
         <is>
@@ -6160,10 +6143,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>6.299</v>
+        <v>1.288</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>5.999</v>
+        <v>1.242</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6176,28 +6159,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E127" s="16" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>688000</v>
+        <v>865900</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H127" t="n">
-        <v>34.33</v>
+        <v>47.92</v>
       </c>
       <c r="I127" s="17" t="inlineStr">
         <is>
@@ -6205,10 +6188,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.952</v>
+        <v>0.548</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1.033</v>
+        <v>0.525</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6221,28 +6204,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.23</v>
+        <v>0.705</v>
       </c>
       <c r="E128" s="15" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0071</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>676300</v>
+        <v>838200</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
       <c r="H128" t="n">
-        <v>41.01</v>
+        <v>38.96</v>
       </c>
       <c r="I128" s="17" t="inlineStr">
         <is>
@@ -6250,10 +6233,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.273</v>
+        <v>0.756</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.316</v>
+        <v>0.769</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6275,19 +6258,19 @@
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="E129" s="15" t="n">
-        <v>0.0129</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>669700</v>
+        <v>821600</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H129" t="n">
-        <v>61.08</v>
+        <v>60.19</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6295,7 +6278,7 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>4.437</v>
+        <v>4.434</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>4.441</v>
@@ -6311,39 +6294,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.46</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>-0.0061</v>
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>656700</v>
+        <v>816300</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="H130" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="I130" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.41</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.832</v>
+        <v>4.559</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.856</v>
+        <v>4.64</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6356,39 +6339,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>-0.0299</v>
+        <v>0.635</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>650300</v>
+        <v>805000</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.22</v>
+        <v>0.77</v>
       </c>
       <c r="H131" t="n">
-        <v>51.71</v>
-      </c>
-      <c r="I131" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.02</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>1.288</v>
+        <v>0.633</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.242</v>
+        <v>0.632</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6401,39 +6384,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>0</v>
+        <v>0.585</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>620000</v>
+        <v>796600</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="H132" t="n">
-        <v>42.28</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.15</v>
+      </c>
+      <c r="I132" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.713</v>
+        <v>0.575</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.77</v>
+        <v>0.485</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6461,10 +6444,10 @@
         <v>0.0172</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>618700</v>
+        <v>764000</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H133" t="n">
         <v>49.88</v>
@@ -6491,39 +6474,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>-0.0072</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>613000</v>
+        <v>729900</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>1</v>
+        <v>0.34</v>
       </c>
       <c r="H134" t="n">
-        <v>56.44</v>
-      </c>
-      <c r="I134" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.65</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.663</v>
+        <v>0.628</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6536,28 +6519,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="E135" s="15" t="n">
-        <v>0.0153</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>608600</v>
+        <v>716800</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="H135" t="n">
-        <v>55.7</v>
+        <v>30.9</v>
       </c>
       <c r="I135" s="17" t="inlineStr">
         <is>
@@ -6565,10 +6548,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>10.462</v>
+        <v>0.832</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>9.872</v>
+        <v>0.856</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6581,39 +6564,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E136" s="16" t="n">
-        <v>0</v>
+        <v>3.59</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>606700</v>
+        <v>705500</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.12</v>
+        <v>0.51</v>
       </c>
       <c r="H136" t="n">
-        <v>39.59</v>
-      </c>
-      <c r="I136" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.45</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.715</v>
+        <v>3.535</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>3.577</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6626,39 +6609,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>-0.0135</v>
+        <v>1.38</v>
+      </c>
+      <c r="E137" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>604700</v>
+        <v>704000</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="H137" t="n">
-        <v>49.48</v>
-      </c>
-      <c r="I137" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.09</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.741</v>
+        <v>1.367</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.707</v>
+        <v>1.346</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6671,28 +6654,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>-0.0408</v>
+        <v>1.23</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>589100</v>
+        <v>701300</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.58</v>
+        <v>0.09</v>
       </c>
       <c r="H138" t="n">
-        <v>26.97</v>
+        <v>41.01</v>
       </c>
       <c r="I138" s="17" t="inlineStr">
         <is>
@@ -6700,10 +6683,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>1.557</v>
+        <v>1.273</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>1.622</v>
+        <v>1.316</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6716,28 +6699,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E139" s="15" t="n">
-        <v>0.0116</v>
+        <v>0.93</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>582100</v>
+        <v>697100</v>
       </c>
       <c r="G139" s="12" t="n">
         <v>0.16</v>
       </c>
       <c r="H139" t="n">
-        <v>43.72</v>
+        <v>34.33</v>
       </c>
       <c r="I139" s="17" t="inlineStr">
         <is>
@@ -6745,10 +6728,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.753</v>
+        <v>0.952</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.854</v>
+        <v>1.033</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6761,28 +6744,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>TROP</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E140" s="15" t="n">
-        <v>0.0054</v>
+        <v>1.17</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>569300</v>
+        <v>694400</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.17</v>
+        <v>0.71</v>
       </c>
       <c r="H140" t="n">
-        <v>48.19</v>
+        <v>46.26</v>
       </c>
       <c r="I140" s="17" t="inlineStr">
         <is>
@@ -6790,10 +6773,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>3.801</v>
+        <v>1.182</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>3.741</v>
+        <v>1.187</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6806,39 +6789,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>0</v>
+        <v>1.14</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>563200</v>
+        <v>678600</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.28</v>
+        <v>0.14</v>
       </c>
       <c r="H141" t="n">
-        <v>56.09</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.53</v>
+      </c>
+      <c r="I141" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>1.367</v>
+        <v>1.088</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.346</v>
+        <v>0.962</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6851,39 +6834,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E142" s="10" t="n">
-        <v>-0.004699999999999999</v>
+        <v>10.6</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>0.0134</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>557500</v>
+        <v>675900</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="H142" t="n">
-        <v>49.24</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.37</v>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>2.105</v>
+        <v>10.461</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>2.109</v>
+        <v>9.872</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6896,28 +6879,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>0.0124</v>
+        <v>0.635</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>555200</v>
+        <v>658700</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.8</v>
+        <v>0.13</v>
       </c>
       <c r="H143" t="n">
-        <v>32.56</v>
+        <v>39.08</v>
       </c>
       <c r="I143" s="17" t="inlineStr">
         <is>
@@ -6925,10 +6908,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>1.716</v>
+        <v>0.714</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>1.77</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6941,28 +6924,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E144" s="15" t="n">
-        <v>0.0355</v>
+        <v>0.73</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>528800</v>
+        <v>644300</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="H144" t="n">
-        <v>59.43</v>
+        <v>49.48</v>
       </c>
       <c r="I144" s="17" t="inlineStr">
         <is>
@@ -6970,10 +6953,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>2.817</v>
+        <v>0.741</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>2.347</v>
+        <v>0.707</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6986,28 +6969,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E145" s="15" t="n">
-        <v>0.12</v>
+        <v>2.1</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>526900</v>
+        <v>637300</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>1.94</v>
+        <v>0.06</v>
       </c>
       <c r="H145" t="n">
-        <v>78.02</v>
+        <v>49.24</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -7015,10 +6998,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>1.167</v>
+        <v>2.105</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>1.193</v>
+        <v>2.109</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7031,28 +7014,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E146" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>2.88</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>525500</v>
+        <v>626400</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="H146" t="n">
-        <v>41.17</v>
+        <v>57.86</v>
       </c>
       <c r="I146" s="17" t="inlineStr">
         <is>
@@ -7060,10 +7043,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.721</v>
+        <v>2.813</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.739</v>
+        <v>2.346</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7076,39 +7059,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>GESHEN</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.76</v>
+        <v>1.4</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>0.0066</v>
+        <v>0.12</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>520500</v>
+        <v>626000</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.37</v>
+        <v>2.3</v>
       </c>
       <c r="H147" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="I147" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.02</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.751</v>
+        <v>1.167</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.724</v>
+        <v>1.193</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7121,39 +7104,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>0326</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>SORENTO</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="E148" s="15" t="n">
-        <v>0.0198</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>513600</v>
+        <v>613000</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.37</v>
+        <v>1</v>
       </c>
       <c r="H148" t="n">
-        <v>58.39</v>
-      </c>
-      <c r="I148" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.44</v>
+      </c>
+      <c r="I148" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>3.537</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>3.578</v>
+        <v>0.663</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7166,28 +7149,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E149" s="16" t="n">
-        <v>0</v>
+        <v>3.75</v>
+      </c>
+      <c r="E149" s="15" t="n">
+        <v>0.0054</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>511900</v>
+        <v>611200</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="H149" t="n">
-        <v>59.7</v>
+        <v>48.19</v>
       </c>
       <c r="I149" s="17" t="inlineStr">
         <is>
@@ -7195,16 +7178,376 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>1.089</v>
+        <v>3.801</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.962</v>
+        <v>3.741</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>LWSABAH</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>605400</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H150" t="n">
+        <v>26.97</v>
+      </c>
+      <c r="I150" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>588200</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H151" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="I151" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>576200</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H152" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="I152" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>1.716</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>575700</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H153" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="I153" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>553700</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H154" t="n">
+        <v>39.17</v>
+      </c>
+      <c r="I154" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>1.256</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>543400</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H155" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="E156" s="15" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>527500</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H156" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>5.038</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>522200</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H157" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="I157" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>2.984</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>2.861</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M149"/>
+  <autoFilter ref="A1:M157"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
+++ b/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0571</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1284200</v>
+        <v>1298900</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>80.09999999999999</v>
@@ -625,7 +625,7 @@
         <v>-0.0667</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>101589700</v>
+        <v>103292400</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>0.28</v>
@@ -670,10 +670,10 @@
         <v>0.3571</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>59938800</v>
+        <v>60951300</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>64.84</v>
+        <v>65.94</v>
       </c>
       <c r="H4" t="n">
         <v>86.39</v>
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-0.0408</v>
+        <v>-0.0306</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>44134100</v>
+        <v>45714100</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="H5" t="n">
-        <v>70.62</v>
+        <v>72.55</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.419</v>
+        <v>0.42</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0.318</v>
@@ -760,7 +760,7 @@
         <v>-0.09089999999999999</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>40561300</v>
+        <v>40854300</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>0.65</v>
@@ -850,10 +850,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>20532200</v>
+        <v>20665200</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>7.88</v>
+        <v>7.93</v>
       </c>
       <c r="H8" t="n">
         <v>70.62</v>
@@ -895,10 +895,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>16177300</v>
+        <v>17277300</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="H9" t="n">
         <v>58.63</v>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
+        <v>0.745</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>15535300</v>
+        <v>15643500</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H10" t="n">
-        <v>83.92</v>
+        <v>84.41</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -1105,28 +1105,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.045</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.1818</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>11991900</v>
+        <v>13223400</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>31.76</v>
+        <v>30.77</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.39</v>
+        <v>0.061</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.403</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,28 +1150,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>-0.0185</v>
+        <v>0.38</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>11856700</v>
+        <v>11991900</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="H15" t="n">
-        <v>41.24</v>
+        <v>31.76</v>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.286</v>
+        <v>0.39</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.279</v>
+        <v>0.403</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,28 +1195,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0.022</v>
+        <v>0.265</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>11197900</v>
+        <v>11967800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="H16" t="n">
-        <v>61.85</v>
+        <v>41.24</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.433</v>
+        <v>0.286</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.385</v>
+        <v>0.279</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1240,39 +1240,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0</v>
+        <v>0.93</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10743700</v>
+        <v>11745400</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H17" t="n">
-        <v>60.52</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.02</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.316</v>
+        <v>0.86</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.266</v>
+        <v>0.763</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1285,28 +1285,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.27</v>
+        <v>0.46</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.011</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>10527800</v>
+        <v>11198900</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>56.73</v>
+        <v>60.81</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.267</v>
+        <v>0.433</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.27</v>
+        <v>0.385</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1330,39 +1330,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.0054</v>
+        <v>0.33</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10483800</v>
+        <v>10786500</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H19" t="n">
-        <v>65.45</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.52</v>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.86</v>
+        <v>0.316</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.763</v>
+        <v>0.266</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1375,39 +1375,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0</v>
+        <v>0.27</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>10285300</v>
+        <v>10578000</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.66</v>
+        <v>2.06</v>
       </c>
       <c r="H20" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.73</v>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.775</v>
+        <v>0.267</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.776</v>
+        <v>0.27</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1420,39 +1420,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>-0.0545</v>
+        <v>0.775</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9688400</v>
+        <v>10285300</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="H21" t="n">
-        <v>34.46</v>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.44</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>5.404</v>
+        <v>0.775</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>5.51</v>
+        <v>0.776</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1465,33 +1465,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>0</v>
+        <v>5.01</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0583</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>9397100</v>
+        <v>10131200</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.27</v>
+        <v>0.76</v>
+      </c>
+      <c r="H22" t="n">
+        <v>33.96</v>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="J22" s="9" t="n">
+        <v>5.402</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>5.51</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1503,40 +1510,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.865</v>
+        <v>0.185</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0263</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8322200</v>
+        <v>9461900</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H23" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>0.869</v>
-      </c>
+        <v>0.27</v>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1548,39 +1548,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.99</v>
+        <v>0.865</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>-0.0386</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>8296800</v>
+        <v>8592200</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.74</v>
+        <v>0.42</v>
       </c>
       <c r="H24" t="n">
-        <v>33.25</v>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>2.106</v>
+        <v>0.868</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2.23</v>
+        <v>0.869</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1593,28 +1593,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0</v>
+        <v>1.98</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>8075000</v>
+        <v>8535400</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>8.84</v>
+        <v>0.76</v>
       </c>
       <c r="H25" t="n">
-        <v>47.02</v>
+        <v>32.51</v>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.005</v>
+        <v>2.105</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.006</v>
+        <v>2.23</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1638,33 +1638,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>-0.0352</v>
+        <v>0.005</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7473500</v>
+        <v>8075000</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.22</v>
+        <v>8.84</v>
+      </c>
+      <c r="H26" t="n">
+        <v>47.02</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
+      <c r="J26" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.006</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
     </row>
@@ -1676,40 +1683,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.0244</v>
+        <v>0.68</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.0423</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7181300</v>
+        <v>7846300</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H27" t="n">
-        <v>57.53</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>0.383</v>
-      </c>
+        <v>0.23</v>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
     </row>
@@ -1721,28 +1721,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.905</v>
+        <v>0.415</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.0343</v>
+        <v>0.0122</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6862700</v>
+        <v>7193300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.84</v>
+        <v>0.61</v>
       </c>
       <c r="H28" t="n">
-        <v>48.12</v>
+        <v>56.17</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.897</v>
+        <v>0.401</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.958</v>
+        <v>0.383</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1766,39 +1766,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>0</v>
+        <v>0.915</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.0457</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6503600</v>
+        <v>6951600</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.86</v>
       </c>
       <c r="H29" t="n">
-        <v>38.43</v>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.89</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.062</v>
+        <v>0.898</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.958</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         <v>0.029</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6350700</v>
+        <v>6454300</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H30" t="n">
         <v>70.38</v>
@@ -1856,28 +1856,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.0331</v>
+        <v>0.385</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>-0.04940000000000001</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6252200</v>
+        <v>6254500</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="H31" t="n">
-        <v>40.62</v>
+        <v>37.96</v>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.005</v>
+        <v>0.423</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.981</v>
+        <v>0.439</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1901,28 +1901,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>-0.04940000000000001</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0387</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6243000</v>
+        <v>6253500</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="H32" t="n">
-        <v>37.96</v>
+        <v>41.35</v>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.423</v>
+        <v>1.006</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.439</v>
+        <v>0.981</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -2000,19 +2000,19 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.195</v>
+        <v>0.2</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.0263</v>
+        <v>0.0526</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5926400</v>
+        <v>6106000</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H34" t="n">
-        <v>37.92</v>
+        <v>41.57</v>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
@@ -2045,19 +2045,19 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.105</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5778400</v>
+        <v>5784400</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>1.3</v>
       </c>
       <c r="H35" t="n">
-        <v>66.55</v>
+        <v>62.33</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2081,39 +2081,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.0309</v>
+        <v>0.715</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.0272</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5463000</v>
+        <v>5668800</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>2.35</v>
+        <v>0.49</v>
       </c>
       <c r="H36" t="n">
-        <v>54.66</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.06</v>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.49</v>
+        <v>0.734</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.485</v>
+        <v>0.724</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2126,39 +2126,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>-0.0235</v>
+        <v>0.495</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.0206</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5338500</v>
+        <v>5503900</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.15</v>
+        <v>2.36</v>
       </c>
       <c r="H37" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.94</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.455</v>
+        <v>0.489</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.474</v>
+        <v>0.484</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2171,28 +2171,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.725</v>
+        <v>0.42</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>-0.0136</v>
+        <v>-0.0118</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5294200</v>
+        <v>5393800</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.46</v>
+        <v>0.15</v>
       </c>
       <c r="H38" t="n">
-        <v>48.45</v>
+        <v>37.37</v>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.735</v>
+        <v>0.455</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.725</v>
+        <v>0.475</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2216,39 +2216,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.0133</v>
+        <v>2.49</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5281700</v>
+        <v>5343000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.48</v>
+        <v>0.28</v>
       </c>
       <c r="H39" t="n">
-        <v>28.85</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.45</v>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.469</v>
+        <v>2.593</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.583</v>
+        <v>2.559</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2261,39 +2261,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.02</v>
+        <v>0.38</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.0151</v>
+        <v>0.0133</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5181500</v>
+        <v>5296100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.19</v>
+        <v>0.49</v>
       </c>
       <c r="H40" t="n">
-        <v>56.35</v>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>28.85</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>1.968</v>
+        <v>0.469</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1.795</v>
+        <v>0.583</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2306,28 +2306,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>-0.008</v>
+        <v>2.01</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.0101</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5175900</v>
+        <v>5234300</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="H41" t="n">
-        <v>43.45</v>
+        <v>55.8</v>
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2.593</v>
+        <v>1.967</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.559</v>
+        <v>1.795</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2396,19 +2396,19 @@
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.52</v>
+        <v>0.515</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>0.0196</v>
+        <v>0.0098</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4832900</v>
+        <v>4835900</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>1.43</v>
       </c>
       <c r="H43" t="n">
-        <v>80.93000000000001</v>
+        <v>80.16</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>0.437</v>
@@ -2447,10 +2447,10 @@
         <v>0.0219</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4662700</v>
+        <v>4774900</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="H44" t="n">
         <v>25.96</v>
@@ -2522,36 +2522,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>-0.0217</v>
+        <v>1.15</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4421700</v>
+        <v>4548100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.21</v>
+        <v>0.6</v>
       </c>
       <c r="H46" t="n">
-        <v>51.42</v>
+        <v>33.75</v>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J46" s="9" t="n"/>
-      <c r="K46" s="9" t="n"/>
+      <c r="J46" s="9" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>1.29</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
     </row>
@@ -2563,40 +2567,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>2.64</v>
+        <v>0.225</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>-0.0149</v>
+        <v>-0.0217</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4318600</v>
+        <v>4421700</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="H47" t="n">
-        <v>42.17</v>
+        <v>51.42</v>
       </c>
       <c r="I47" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J47" s="9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="K47" s="9" t="n">
-        <v>2.746</v>
-      </c>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="9" t="n"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
     </row>
@@ -2608,28 +2608,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.14</v>
+        <v>2.63</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0187</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4316200</v>
+        <v>4387000</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.57</v>
+        <v>0.42</v>
       </c>
       <c r="H48" t="n">
-        <v>32.43</v>
+        <v>41.52</v>
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.203</v>
+        <v>2.729</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.29</v>
+        <v>2.746</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2653,28 +2653,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0</v>
+        <v>4.7</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4180700</v>
+        <v>4290100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1.19</v>
+        <v>0.2</v>
       </c>
       <c r="H49" t="n">
-        <v>63.67</v>
+        <v>46.16</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.62</v>
+        <v>4.726</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.61</v>
+        <v>4.811</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2698,39 +2698,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.295</v>
+        <v>0.625</v>
       </c>
       <c r="E50" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4143400</v>
+        <v>4180700</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="H50" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.67</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.295</v>
+        <v>0.62</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.295</v>
+        <v>0.61</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2743,39 +2743,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3955000</v>
+        <v>4143400</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="H51" t="n">
-        <v>85.23999999999999</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.06</v>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>3.042</v>
+        <v>0.295</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.577</v>
+        <v>0.295</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2788,28 +2788,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>0.019</v>
+        <v>3.4</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3928900</v>
+        <v>4078800</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="H52" t="n">
-        <v>55.64</v>
+        <v>86.48</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>2.114</v>
+        <v>3.043</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2.078</v>
+        <v>2.578</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2833,28 +2833,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.0105</v>
+        <v>2.14</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.019</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3903200</v>
+        <v>3940400</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.18</v>
+        <v>1.88</v>
       </c>
       <c r="H53" t="n">
-        <v>46.16</v>
+        <v>55.64</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>4.726</v>
+        <v>2.114</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>4.811</v>
+        <v>2.078</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>0.0179</v>
+        <v>0.0268</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3814600</v>
+        <v>3884900</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H54" t="n">
-        <v>22.3</v>
+        <v>24.18</v>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.3</v>
+        <v>1.301</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>1.502</v>
@@ -2983,7 +2983,7 @@
         <v>0.0169</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3699600</v>
+        <v>3739700</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>0.49</v>
@@ -3028,10 +3028,10 @@
         <v>0.0303</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3514500</v>
+        <v>3534500</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H57" t="n">
         <v>55.01</v>
@@ -3073,7 +3073,7 @@
         <v>-0.0345</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3487700</v>
+        <v>3493000</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>0.73</v>
@@ -3103,39 +3103,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0</v>
+        <v>1.63</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3336100</v>
+        <v>3353400</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="H59" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.41</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.282</v>
+        <v>1.625</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.282</v>
+        <v>1.675</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3148,39 +3148,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.0062</v>
+        <v>0.265</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3274700</v>
+        <v>3336100</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="H60" t="n">
-        <v>49.41</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.25</v>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.625</v>
+        <v>0.282</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1.675</v>
+        <v>0.282</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3202,19 +3202,19 @@
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.0278</v>
+        <v>0.18</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3243700</v>
+        <v>3260200</v>
       </c>
       <c r="G61" s="12" t="n">
         <v>0.16</v>
       </c>
       <c r="H61" t="n">
-        <v>48.66</v>
+        <v>44.11</v>
       </c>
       <c r="I61" s="17" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.186</v>
+        <v>0.185</v>
       </c>
       <c r="K61" s="9" t="n">
         <v>0.186</v>
@@ -3253,10 +3253,10 @@
         <v>0.053</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3029400</v>
+        <v>3043400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H62" t="n">
         <v>50.62</v>
@@ -3283,28 +3283,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PCCS</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.315</v>
+        <v>1.16</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.05</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2820900</v>
+        <v>2971900</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>22.37</v>
+        <v>0.32</v>
       </c>
       <c r="H63" t="n">
-        <v>75.47</v>
+        <v>60.13</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.285</v>
+        <v>1.094</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.282</v>
+        <v>1.056</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3328,39 +3328,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.295</v>
+        <v>0.43</v>
       </c>
       <c r="E64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2786200</v>
+        <v>2926400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.42</v>
+        <v>0.18</v>
       </c>
       <c r="H64" t="n">
-        <v>36.35</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.46</v>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.314</v>
+        <v>0.479</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.359</v>
+        <v>0.618</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3373,39 +3373,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>PCCS</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.31</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2711700</v>
+        <v>2854500</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.16</v>
+        <v>22.64</v>
       </c>
       <c r="H65" t="n">
-        <v>31.13</v>
-      </c>
-      <c r="I65" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.39</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>7.359</v>
+        <v>0.285</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>7.624</v>
+        <v>0.282</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3418,28 +3418,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.15</v>
+        <v>0.295</v>
       </c>
       <c r="E66" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2698900</v>
+        <v>2786300</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.29</v>
+        <v>0.42</v>
       </c>
       <c r="H66" t="n">
-        <v>59.07</v>
+        <v>36.35</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.093</v>
+        <v>0.314</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.056</v>
+        <v>0.359</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3463,28 +3463,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>0</v>
+        <v>7.09</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2605000</v>
+        <v>2750800</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1.33</v>
+        <v>0.17</v>
       </c>
       <c r="H67" t="n">
-        <v>45.18</v>
+        <v>31.13</v>
       </c>
       <c r="I67" s="17" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.359</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>7.624</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3508,39 +3508,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.865</v>
+        <v>0.225</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0217</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2565000</v>
+        <v>2748500</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.86</v>
+        <v>1.96</v>
       </c>
       <c r="H68" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I68" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.32</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.866</v>
+        <v>0.23</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.861</v>
+        <v>0.237</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3553,28 +3553,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>-0.0066</v>
+        <v>0.555</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2483200</v>
+        <v>2605000</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.32</v>
+        <v>1.33</v>
       </c>
       <c r="H69" t="n">
-        <v>45.8</v>
+        <v>45.18</v>
       </c>
       <c r="I69" s="17" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.767</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.771</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3598,39 +3598,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>5.73</v>
+        <v>0.865</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>-0.0035</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2447400</v>
+        <v>2565000</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.31</v>
+        <v>0.86</v>
       </c>
       <c r="H70" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.44</v>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>5.827</v>
+        <v>0.866</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>6.087</v>
+        <v>0.861</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3643,28 +3643,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>4.82</v>
+        <v>0.755</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>-0.0062</v>
+        <v>-0.0066</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2370500</v>
+        <v>2483200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="H71" t="n">
-        <v>47.76</v>
+        <v>45.8</v>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>4.87</v>
+        <v>0.767</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>4.764</v>
+        <v>0.771</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3688,39 +3688,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>0.0179</v>
+        <v>5.73</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2286900</v>
+        <v>2482200</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="H72" t="n">
-        <v>56.61</v>
-      </c>
-      <c r="I72" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.34</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.829</v>
+        <v>5.827</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.799</v>
+        <v>6.087</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         <v>0.0049</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2267600</v>
+        <v>2412300</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H73" t="n">
         <v>48.91</v>
@@ -3778,28 +3778,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.325</v>
+        <v>4.83</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>-0.0299</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2242000</v>
+        <v>2388300</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="H74" t="n">
-        <v>41.45</v>
+        <v>48.35</v>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.348</v>
+        <v>4.871</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.33</v>
+        <v>4.764</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3823,28 +3823,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>-0.0042</v>
+        <v>0.835</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0.0245</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2231800</v>
+        <v>2292700</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="H75" t="n">
-        <v>42.66</v>
+        <v>43.04</v>
       </c>
       <c r="I75" s="17" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.433</v>
+        <v>0.885</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.412</v>
+        <v>0.859</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3868,28 +3868,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>4.21</v>
+        <v>0.855</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.0525</v>
+        <v>0.0179</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2223600</v>
+        <v>2286900</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="H76" t="n">
-        <v>60.59</v>
+        <v>56.61</v>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>3.984</v>
+        <v>0.829</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>3.644</v>
+        <v>0.799</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3913,28 +3913,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>0.0116</v>
+        <v>0.325</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2176400</v>
+        <v>2263400</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="H77" t="n">
-        <v>27.55</v>
+        <v>41.45</v>
       </c>
       <c r="I77" s="17" t="inlineStr">
         <is>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.479</v>
+        <v>0.348</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.619</v>
+        <v>0.33</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3958,39 +3958,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>-0.0217</v>
+        <v>4.19</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.0475</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2147000</v>
+        <v>2262600</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>1.53</v>
+        <v>0.24</v>
       </c>
       <c r="H78" t="n">
-        <v>43.32</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.03</v>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.23</v>
+        <v>3.982</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.237</v>
+        <v>3.644</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4003,28 +4003,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0.0245</v>
+        <v>2.38</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2083000</v>
+        <v>2262000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H79" t="n">
-        <v>43.04</v>
+        <v>42.66</v>
       </c>
       <c r="I79" s="17" t="inlineStr">
         <is>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.885</v>
+        <v>2.433</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.859</v>
+        <v>2.412</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4063,10 +4063,10 @@
         <v>0.0282</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2069100</v>
+        <v>2157100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="H80" t="n">
         <v>60.1</v>
@@ -4091,28 +4091,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>0</v>
+        <v>6.29</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2034100</v>
+        <v>2039100</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>1.44</v>
+        <v>0.29</v>
       </c>
       <c r="H81" t="n">
-        <v>55.46</v>
+        <v>44.09</v>
       </c>
       <c r="I81" s="17" t="inlineStr">
         <is>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.75</v>
+        <v>6.342</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.723</v>
+        <v>6.646</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4136,28 +4136,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>-0.0126</v>
+        <v>0.755</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2026300</v>
+        <v>2034100</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.28</v>
+        <v>1.44</v>
       </c>
       <c r="H82" t="n">
-        <v>43.17</v>
+        <v>55.46</v>
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>6.34</v>
+        <v>0.75</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>6.646</v>
+        <v>0.723</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4190,19 +4190,19 @@
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>0.0129</v>
+        <v>0.0194</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1951400</v>
+        <v>2023200</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H83" t="n">
-        <v>36.76</v>
+        <v>38.17</v>
       </c>
       <c r="I83" s="17" t="inlineStr">
         <is>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.657</v>
+        <v>1.658</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.741</v>
+        <v>1.742</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4286,7 +4286,7 @@
         <v>0.0168</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1773700</v>
+        <v>1775000</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>0.27</v>
@@ -4331,7 +4331,7 @@
         <v>-0.0039</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1772900</v>
+        <v>1774600</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>0.31</v>
@@ -4376,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1702400</v>
+        <v>1707400</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>0.19</v>
@@ -4421,7 +4421,7 @@
         <v>0.0108</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1674600</v>
+        <v>1686500</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>0.2</v>
@@ -4466,7 +4466,7 @@
         <v>0.0112</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1631200</v>
+        <v>1641400</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0.17</v>
@@ -4496,28 +4496,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.0274</v>
+        <v>0.0283</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1610700</v>
+        <v>1630500</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
       <c r="H90" t="n">
-        <v>53.34</v>
+        <v>52.05</v>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.74</v>
+        <v>1.098</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.927</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4541,28 +4541,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.0274</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1581900</v>
+        <v>1611700</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="H91" t="n">
-        <v>35.41</v>
+        <v>53.34</v>
       </c>
       <c r="I91" s="17" t="inlineStr">
         <is>
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.646</v>
+        <v>0.74</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4595,19 +4595,19 @@
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>6.87</v>
+        <v>6.86</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>-0.0115</v>
+        <v>-0.0129</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1576700</v>
+        <v>1596100</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>0.31</v>
       </c>
       <c r="H92" t="n">
-        <v>54.75</v>
+        <v>54.11</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>6.805</v>
+        <v>6.804</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>6.822</v>
+        <v>6.821</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4640,19 +4640,19 @@
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="E93" s="15" t="n">
-        <v>0.0126</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1569900</v>
+        <v>1593900</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="H93" t="n">
-        <v>62.86</v>
+        <v>62.27</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.289</v>
+        <v>2.288</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>2.208</v>
+        <v>2.207</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4676,39 +4676,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.07</v>
+        <v>0.23</v>
       </c>
       <c r="E94" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0455</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1548500</v>
+        <v>1587000</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.41</v>
+        <v>1.61</v>
       </c>
       <c r="H94" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="I94" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.4</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.096</v>
+        <v>0.223</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.926</v>
+        <v>0.23</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4721,39 +4721,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E95" s="15" t="n">
-        <v>0.024</v>
+        <v>0.58</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1466200</v>
+        <v>1586400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H95" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.72</v>
+      </c>
+      <c r="I95" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.228</v>
+        <v>0.645</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.206</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4766,28 +4766,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v>0.0227</v>
+        <v>0.43</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1462000</v>
+        <v>1506100</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>1.48</v>
+        <v>0.22</v>
       </c>
       <c r="H96" t="n">
-        <v>50.21</v>
+        <v>51.18</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.223</v>
+        <v>0.429</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.23</v>
+        <v>0.418</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4811,39 +4811,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>-0.015</v>
+        <v>1.27</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>0.016</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1437900</v>
+        <v>1491900</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.4</v>
+        <v>0.21</v>
       </c>
       <c r="H97" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="I97" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.06</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.024</v>
+        <v>1.228</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.973</v>
+        <v>1.206</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4856,39 +4856,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>0.0147</v>
+        <v>0.985</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>-0.015</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1410000</v>
+        <v>1437900</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="H98" t="n">
-        <v>57.71</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.83</v>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.337</v>
+        <v>1.024</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.343</v>
+        <v>0.973</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4901,28 +4901,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.435</v>
+        <v>0.34</v>
       </c>
       <c r="E99" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1401100</v>
+        <v>1410600</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="H99" t="n">
-        <v>52.42</v>
+        <v>52.96</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.429</v>
+        <v>0.336</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.418</v>
+        <v>0.343</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4946,38 +4946,40 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.225</v>
+        <v>9.99</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>-0.0217</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1338200</v>
+        <v>1396900</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
       <c r="H100" t="n">
-        <v>14</v>
-      </c>
-      <c r="I100" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="K100" s="9" t="n"/>
+        <v>9.996</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>10.112</v>
+      </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
     </row>
@@ -4989,39 +4991,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>9.99</v>
+        <v>0.55</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.0179</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1335800</v>
+        <v>1360000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H101" t="n">
-        <v>48</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I101" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>9.996</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>10.112</v>
+        <v>0.546</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5034,28 +5036,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1315500</v>
+        <v>1338200</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="H102" t="n">
-        <v>33.86</v>
+        <v>14</v>
       </c>
       <c r="I102" s="17" t="inlineStr">
         <is>
@@ -5063,11 +5065,9 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="K102" s="9" t="n">
-        <v>2.646</v>
-      </c>
+        <v>0.257</v>
+      </c>
+      <c r="K102" s="9" t="n"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
     </row>
@@ -5079,28 +5079,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>-0.0179</v>
+        <v>2.38</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1282600</v>
+        <v>1325700</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.06</v>
+        <v>0.33</v>
       </c>
       <c r="H103" t="n">
-        <v>47.42</v>
+        <v>33.86</v>
       </c>
       <c r="I103" s="17" t="inlineStr">
         <is>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>2.481</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.546</v>
+        <v>2.646</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5124,28 +5124,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.605</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1256000</v>
+        <v>1283300</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="H104" t="n">
-        <v>48.61</v>
+        <v>32.83</v>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.905</v>
+        <v>0.679</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.892</v>
+        <v>0.734</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5169,28 +5169,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.225</v>
+        <v>0.895</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>0.0227</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1255500</v>
+        <v>1256000</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>2.91</v>
+        <v>0.72</v>
       </c>
       <c r="H105" t="n">
-        <v>51.18</v>
+        <v>48.61</v>
       </c>
       <c r="I105" s="17" t="inlineStr">
         <is>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.225</v>
+        <v>0.905</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.224</v>
+        <v>0.892</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5214,28 +5214,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.31</v>
+        <v>0.225</v>
       </c>
       <c r="E106" s="15" t="n">
-        <v>0.0164</v>
+        <v>0.0227</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1222600</v>
+        <v>1255500</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.96</v>
+        <v>2.91</v>
       </c>
       <c r="H106" t="n">
-        <v>43.1</v>
+        <v>51.18</v>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.315</v>
+        <v>0.225</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.328</v>
+        <v>0.224</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5268,19 +5268,19 @@
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>6.77</v>
+        <v>6.79</v>
       </c>
       <c r="E107" s="15" t="n">
-        <v>0.0059</v>
+        <v>0.0089</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1218200</v>
+        <v>1245400</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>0.11</v>
       </c>
       <c r="H107" t="n">
-        <v>36.66</v>
+        <v>37.48</v>
       </c>
       <c r="I107" s="17" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>7.051</v>
+        <v>7.053</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>7.494</v>
@@ -5319,7 +5319,7 @@
         <v>0.0027</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1202200</v>
+        <v>1236800</v>
       </c>
       <c r="G108" s="12" t="n">
         <v>0.11</v>
@@ -5349,28 +5349,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E109" s="16" t="n">
-        <v>0</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1201400</v>
+        <v>1231700</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="H109" t="n">
-        <v>40.12</v>
+        <v>29.37</v>
       </c>
       <c r="I109" s="17" t="inlineStr">
         <is>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.123</v>
+        <v>0.867</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.112</v>
+        <v>0.931</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5394,28 +5394,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>2.42</v>
+        <v>0.31</v>
       </c>
       <c r="E110" s="15" t="n">
-        <v>0.0342</v>
+        <v>0.0164</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1200400</v>
+        <v>1222600</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.21</v>
+        <v>0.96</v>
       </c>
       <c r="H110" t="n">
-        <v>37.34</v>
+        <v>43.1</v>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>2.633</v>
+        <v>0.315</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>2.828</v>
+        <v>0.328</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5439,28 +5439,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.605</v>
+        <v>1.06</v>
       </c>
       <c r="E111" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1186700</v>
+        <v>1208000</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="H111" t="n">
-        <v>32.83</v>
+        <v>40.12</v>
       </c>
       <c r="I111" s="17" t="inlineStr">
         <is>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.679</v>
+        <v>1.123</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.734</v>
+        <v>1.112</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5484,39 +5484,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E112" s="16" t="n">
-        <v>0</v>
+        <v>2.42</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0.0342</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1169800</v>
+        <v>1206000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="H112" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.34</v>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.9429999999999999</v>
+        <v>2.633</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.892</v>
+        <v>2.828</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         <v>-0.0174</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1168500</v>
+        <v>1204200</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H113" t="n">
         <v>29.22</v>
@@ -5574,28 +5574,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>-0.0323</v>
+        <v>0.965</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1153800</v>
+        <v>1169800</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.88</v>
+        <v>0.25</v>
       </c>
       <c r="H114" t="n">
-        <v>49.39</v>
+        <v>62.7</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.296</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.327</v>
+        <v>0.892</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5619,39 +5619,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>-0.0122</v>
+        <v>-0.0323</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1144700</v>
+        <v>1162000</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.4</v>
+        <v>0.88</v>
       </c>
       <c r="H115" t="n">
-        <v>28.52</v>
-      </c>
-      <c r="I115" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.39</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.867</v>
+        <v>0.296</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.931</v>
+        <v>0.327</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5664,28 +5664,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v>0.0086</v>
+        <v>0.205</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1061700</v>
+        <v>1118200</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="H116" t="n">
-        <v>62.18</v>
+        <v>30.88</v>
       </c>
       <c r="I116" s="17" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.54</v>
+        <v>0.223</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.485</v>
+        <v>0.269</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5709,39 +5709,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E117" s="16" t="n">
-        <v>0</v>
+        <v>0.585</v>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1045500</v>
+        <v>1107000</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.91</v>
+        <v>0.23</v>
       </c>
       <c r="H117" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.18</v>
+      </c>
+      <c r="I117" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.441</v>
+        <v>0.54</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.44</v>
+        <v>0.485</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5754,39 +5754,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.24</v>
+        <v>0.445</v>
       </c>
       <c r="E118" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1012400</v>
+        <v>1045500</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="H118" t="n">
-        <v>43.14</v>
-      </c>
-      <c r="I118" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.98999999999999</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.29</v>
+        <v>0.441</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1.3</v>
+        <v>0.44</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5799,28 +5799,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>-0.0157</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>958300</v>
+        <v>1015200</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="H119" t="n">
-        <v>50.28</v>
+        <v>28.13</v>
       </c>
       <c r="I119" s="17" t="inlineStr">
         <is>
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.264</v>
+        <v>0.528</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.186</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5844,39 +5844,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>935200</v>
+        <v>1013400</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="H120" t="n">
-        <v>53.67</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.11</v>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.245</v>
+        <v>1.289</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.115</v>
+        <v>1.3</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5889,39 +5889,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E121" s="16" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>918900</v>
+        <v>976300</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="H121" t="n">
-        <v>53.94</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.28</v>
+      </c>
+      <c r="I121" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.266</v>
+        <v>1.264</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.271</v>
+        <v>1.186</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5934,28 +5934,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>2.67</v>
+        <v>1.3</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>-0.0184</v>
+        <v>-0.0299</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>902500</v>
+        <v>964700</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="H122" t="n">
-        <v>35.48</v>
+        <v>51.71</v>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>2.83</v>
+        <v>1.288</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>2.97</v>
+        <v>1.242</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5994,7 +5994,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>902100</v>
+        <v>940800</v>
       </c>
       <c r="G123" s="12" t="n">
         <v>0.15</v>
@@ -6024,39 +6024,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v>0.0164</v>
+        <v>1.25</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>894600</v>
+        <v>937900</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.87</v>
+        <v>0.26</v>
       </c>
       <c r="H124" t="n">
-        <v>48.51</v>
-      </c>
-      <c r="I124" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.78</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.925</v>
+        <v>1.244</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.011</v>
+        <v>1.115</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6069,39 +6069,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>-0.0015</v>
+        <v>1.28</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>881100</v>
+        <v>936900</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="H125" t="n">
-        <v>55.41</v>
-      </c>
-      <c r="I125" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.94</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>6.297</v>
+        <v>1.266</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>5.999</v>
+        <v>1.271</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6114,28 +6114,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>1.3</v>
+        <v>2.67</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>-0.0299</v>
+        <v>-0.0184</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>874300</v>
+        <v>917600</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="H126" t="n">
-        <v>51.71</v>
+        <v>35.48</v>
       </c>
       <c r="I126" s="17" t="inlineStr">
         <is>
@@ -6143,10 +6143,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>1.288</v>
+        <v>2.83</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>1.242</v>
+        <v>2.97</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6159,28 +6159,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.535</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0273</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>865900</v>
+        <v>911400</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.17</v>
+        <v>0.89</v>
       </c>
       <c r="H127" t="n">
-        <v>47.92</v>
+        <v>50.04</v>
       </c>
       <c r="I127" s="17" t="inlineStr">
         <is>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.548</v>
+        <v>0.925</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.525</v>
+        <v>1.011</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6204,28 +6204,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>0.0071</v>
+        <v>6.5</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>-0.0015</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>838200</v>
+        <v>909600</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="H128" t="n">
-        <v>38.96</v>
+        <v>55.41</v>
       </c>
       <c r="I128" s="17" t="inlineStr">
         <is>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.756</v>
+        <v>6.297</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.769</v>
+        <v>5.999</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6249,39 +6249,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>4.68</v>
+        <v>0.535</v>
       </c>
       <c r="E129" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>821600</v>
+        <v>880300</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H129" t="n">
-        <v>60.19</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.92</v>
+      </c>
+      <c r="I129" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>4.434</v>
+        <v>0.548</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>4.441</v>
+        <v>0.525</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6294,39 +6294,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>-0.004500000000000001</v>
+        <v>0.585</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>816300</v>
+        <v>876600</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="H130" t="n">
-        <v>37.41</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.15</v>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>4.559</v>
+        <v>0.575</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>4.64</v>
+        <v>0.485</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6339,28 +6339,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.635</v>
+        <v>1.38</v>
       </c>
       <c r="E131" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>805000</v>
+        <v>870200</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.77</v>
+        <v>0.43</v>
       </c>
       <c r="H131" t="n">
-        <v>55.02</v>
+        <v>56.09</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.633</v>
+        <v>1.367</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.632</v>
+        <v>1.346</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6384,28 +6384,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0.0086</v>
+        <v>1.4</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>-0.0476</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>796600</v>
+        <v>840900</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.13</v>
+        <v>0.83</v>
       </c>
       <c r="H132" t="n">
-        <v>54.15</v>
+        <v>26.29</v>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.575</v>
+        <v>1.556</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.485</v>
+        <v>1.622</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6429,28 +6429,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.59</v>
+        <v>0.705</v>
       </c>
       <c r="E133" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.0071</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>764000</v>
+        <v>838200</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="H133" t="n">
-        <v>49.88</v>
+        <v>38.96</v>
       </c>
       <c r="I133" s="17" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.592</v>
+        <v>0.756</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.584</v>
+        <v>0.769</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6474,28 +6474,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>4.66</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0.0022</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>729900</v>
+        <v>835300</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="H134" t="n">
-        <v>51.65</v>
+        <v>59.57</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.64</v>
+        <v>4.432</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.628</v>
+        <v>4.44</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6519,39 +6519,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.47</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>-0.0061</v>
+        <v>-0.0022</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>716800</v>
+        <v>817300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.29</v>
+        <v>0.09</v>
       </c>
       <c r="H135" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="I135" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.17</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.832</v>
+        <v>4.56</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.856</v>
+        <v>4.641</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6564,28 +6564,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="E136" s="15" t="n">
-        <v>0.0141</v>
+        <v>0.635</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>705500</v>
+        <v>805000</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.51</v>
+        <v>0.77</v>
       </c>
       <c r="H136" t="n">
-        <v>56.45</v>
+        <v>55.02</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>3.535</v>
+        <v>0.633</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>3.577</v>
+        <v>0.632</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6609,39 +6609,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E137" s="16" t="n">
-        <v>0</v>
+        <v>1.63</v>
+      </c>
+      <c r="E137" s="15" t="n">
+        <v>0.0124</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>704000</v>
+        <v>790200</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.35</v>
+        <v>1.14</v>
       </c>
       <c r="H137" t="n">
-        <v>56.09</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.56</v>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.367</v>
+        <v>1.716</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.346</v>
+        <v>1.77</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6654,28 +6654,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>1.23</v>
+        <v>0.59</v>
       </c>
       <c r="E138" s="15" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0172</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>701300</v>
+        <v>774200</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="H138" t="n">
-        <v>41.01</v>
+        <v>49.88</v>
       </c>
       <c r="I138" s="17" t="inlineStr">
         <is>
@@ -6683,10 +6683,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>1.273</v>
+        <v>0.592</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>1.316</v>
+        <v>0.584</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6699,28 +6699,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>TROP</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="E139" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>697100</v>
+        <v>764800</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.16</v>
+        <v>0.78</v>
       </c>
       <c r="H139" t="n">
-        <v>34.33</v>
+        <v>46.26</v>
       </c>
       <c r="I139" s="17" t="inlineStr">
         <is>
@@ -6728,10 +6728,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.952</v>
+        <v>1.182</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.033</v>
+        <v>1.187</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6744,28 +6744,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TROP</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>0</v>
+        <v>0.805</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>694400</v>
+        <v>748400</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.71</v>
+        <v>0.3</v>
       </c>
       <c r="H140" t="n">
-        <v>46.26</v>
+        <v>29.03</v>
       </c>
       <c r="I140" s="17" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.182</v>
+        <v>0.832</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.187</v>
+        <v>0.856</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6789,28 +6789,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.93</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>678600</v>
+        <v>734500</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H141" t="n">
-        <v>58.53</v>
+        <v>34.33</v>
       </c>
       <c r="I141" s="17" t="inlineStr">
         <is>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>1.088</v>
+        <v>0.952</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.962</v>
+        <v>1.033</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6834,39 +6834,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>0.0134</v>
+        <v>0.64</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>675900</v>
+        <v>730100</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="H142" t="n">
-        <v>55.37</v>
-      </c>
-      <c r="I142" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.65</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>10.461</v>
+        <v>0.64</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>9.872</v>
+        <v>0.628</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6879,28 +6879,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E143" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.22</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>658700</v>
+        <v>718600</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="H143" t="n">
-        <v>39.08</v>
+        <v>39.04</v>
       </c>
       <c r="I143" s="17" t="inlineStr">
         <is>
@@ -6908,10 +6908,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.714</v>
+        <v>1.272</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.316</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6924,39 +6924,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E144" s="10" t="n">
-        <v>-0.0135</v>
+        <v>3.59</v>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>644300</v>
+        <v>705900</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.21</v>
+        <v>0.51</v>
       </c>
       <c r="H144" t="n">
-        <v>49.48</v>
-      </c>
-      <c r="I144" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.45</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.741</v>
+        <v>3.535</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.707</v>
+        <v>3.577</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6969,39 +6969,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>-0.004699999999999999</v>
+        <v>3.73</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>637300</v>
+        <v>688000</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="H145" t="n">
-        <v>49.24</v>
-      </c>
-      <c r="I145" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.23</v>
+      </c>
+      <c r="I145" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>2.105</v>
+        <v>3.799</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>2.109</v>
+        <v>3.741</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7014,28 +7014,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>2.88</v>
+        <v>10.6</v>
       </c>
       <c r="E146" s="15" t="n">
-        <v>0.0213</v>
+        <v>0.0134</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>626400</v>
+        <v>686600</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H146" t="n">
-        <v>57.86</v>
+        <v>55.37</v>
       </c>
       <c r="I146" s="17" t="inlineStr">
         <is>
@@ -7043,10 +7043,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>2.813</v>
+        <v>10.461</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>2.346</v>
+        <v>9.872</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E147" s="15" t="n">
-        <v>0.12</v>
+        <v>1.14</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>626000</v>
+        <v>678700</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>2.3</v>
+        <v>0.14</v>
       </c>
       <c r="H147" t="n">
-        <v>78.02</v>
-      </c>
-      <c r="I147" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.53</v>
+      </c>
+      <c r="I147" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.167</v>
+        <v>1.088</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>1.193</v>
+        <v>0.962</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7104,28 +7104,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>-0.0072</v>
+        <v>2.9</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0.0284</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>613000</v>
+        <v>667100</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>1</v>
+        <v>0.16</v>
       </c>
       <c r="H148" t="n">
-        <v>56.44</v>
+        <v>58.66</v>
       </c>
       <c r="I148" s="17" t="inlineStr">
         <is>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>2.815</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.663</v>
+        <v>2.347</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7149,28 +7149,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E149" s="15" t="n">
-        <v>0.0054</v>
+        <v>0.635</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>611200</v>
+        <v>658800</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="H149" t="n">
-        <v>48.19</v>
+        <v>39.08</v>
       </c>
       <c r="I149" s="17" t="inlineStr">
         <is>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>3.801</v>
+        <v>0.714</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>3.741</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7194,39 +7194,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>-0.0408</v>
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>605400</v>
+        <v>645000</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="H150" t="n">
-        <v>26.97</v>
-      </c>
-      <c r="I150" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.24</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.557</v>
+        <v>2.105</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.622</v>
+        <v>2.109</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7239,28 +7239,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E151" s="15" t="n">
-        <v>0.0058</v>
+        <v>0.73</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>588200</v>
+        <v>644300</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H151" t="n">
-        <v>41.67</v>
+        <v>49.48</v>
       </c>
       <c r="I151" s="17" t="inlineStr">
         <is>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>1.752</v>
+        <v>0.741</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>1.854</v>
+        <v>0.707</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7284,28 +7284,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>0326</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>SORENTO</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E152" s="15" t="n">
-        <v>0.0124</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>576200</v>
+        <v>637000</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.83</v>
+        <v>1.04</v>
       </c>
       <c r="H152" t="n">
-        <v>32.56</v>
+        <v>56.44</v>
       </c>
       <c r="I152" s="17" t="inlineStr">
         <is>
@@ -7313,10 +7313,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>1.716</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>1.77</v>
+        <v>0.663</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7329,39 +7329,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>GESHEN</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E153" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>1.39</v>
+      </c>
+      <c r="E153" s="15" t="n">
+        <v>0.112</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>575700</v>
+        <v>627500</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.33</v>
+        <v>2.31</v>
       </c>
       <c r="H153" t="n">
-        <v>41.17</v>
-      </c>
-      <c r="I153" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.52</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.721</v>
+        <v>1.166</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.739</v>
+        <v>1.192</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7374,28 +7374,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>1.06</v>
+        <v>1.74</v>
       </c>
       <c r="E154" s="15" t="n">
-        <v>0.0495</v>
+        <v>0.0116</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>553700</v>
+        <v>588700</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="H154" t="n">
-        <v>39.17</v>
+        <v>43.72</v>
       </c>
       <c r="I154" s="17" t="inlineStr">
         <is>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>1.129</v>
+        <v>1.753</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.256</v>
+        <v>1.854</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7419,39 +7419,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E155" s="16" t="n">
-        <v>0</v>
+        <v>0.705</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>543400</v>
+        <v>575700</v>
       </c>
       <c r="G155" s="12" t="n">
         <v>0.33</v>
       </c>
       <c r="H155" t="n">
-        <v>48.29</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.17</v>
+      </c>
+      <c r="I155" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>0.891</v>
+        <v>0.721</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>0.903</v>
+        <v>0.739</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7464,39 +7464,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>5.11</v>
+        <v>1.06</v>
       </c>
       <c r="E156" s="15" t="n">
-        <v>0.024</v>
+        <v>0.0495</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>527500</v>
+        <v>573700</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H156" t="n">
-        <v>52.87</v>
-      </c>
-      <c r="I156" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.17</v>
+      </c>
+      <c r="I156" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>5.06</v>
+        <v>1.129</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>5.038</v>
+        <v>1.256</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7509,45 +7509,135 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E157" s="10" t="n">
-        <v>-0.0102</v>
+        <v>0.9</v>
+      </c>
+      <c r="E157" s="15" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>522200</v>
+        <v>564400</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="H157" t="n">
-        <v>46.64</v>
-      </c>
-      <c r="I157" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.84</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>2.984</v>
+        <v>0.892</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>2.861</v>
+        <v>0.903</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>-0.0137</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>538700</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H158" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="I158" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>2.983</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>2.861</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="E159" s="15" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>527600</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H159" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>5.038</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M157"/>
+  <autoFilter ref="A1:M159"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
+++ b/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,95 +557,103 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>COMFORT</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.08109999999999999</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>2908500</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>68.59</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 68.59接近超买区，现价高于50日均线约23%，信号偏强但需留意RSI高位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>5073</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>NAIM</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.0571</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>1298900</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="D3" s="3" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1495200</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>0.644</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>0.615</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>🎯 SAR 转多</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>RSI 80.1 已处超买区，现价高于50日均线约20%，SAR转多信号可靠性受超买制约。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>-0.0667</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>103292400</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H3" t="n">
-        <v>32.63</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>RSI 79.54 已超买，现价高于50日均线约19.5%，SAR转多信号可靠性偏弱。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,28 +663,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>0.3571</v>
+        <v>0.065</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>-0.1333</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>60951300</v>
+        <v>105412400</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>65.94</v>
+        <v>0.29</v>
       </c>
       <c r="H4" t="n">
-        <v>86.39</v>
+        <v>31.79</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -684,10 +692,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.12</v>
+        <v>0.098</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.116</v>
+        <v>0.259</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -700,28 +708,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>-0.0306</v>
+        <v>0.19</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.3571</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>45714100</v>
+        <v>70399600</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>1.26</v>
+        <v>76.16</v>
       </c>
       <c r="H5" t="n">
-        <v>72.55</v>
+        <v>86.39</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -729,10 +737,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.42</v>
+        <v>0.12</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.318</v>
+        <v>0.116</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -745,28 +753,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.15</v>
+        <v>0.475</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.0306</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>40854300</v>
+        <v>51404400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.65</v>
+        <v>1.41</v>
       </c>
       <c r="H6" t="n">
-        <v>46.87</v>
+        <v>72.55</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -774,10 +782,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.159</v>
+        <v>0.42</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.147</v>
+        <v>0.318</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,28 +798,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.155</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-0.06059999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>22323200</v>
+        <v>41289500</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>9.16</v>
+        <v>0.66</v>
       </c>
       <c r="H7" t="n">
-        <v>78.40000000000001</v>
+        <v>48.93</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -819,10 +827,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.078</v>
+        <v>0.159</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.076</v>
+        <v>0.147</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,39 +843,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0069</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VINVEST</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.03</v>
+        <v>0.055</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>20665200</v>
+        <v>36327700</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>7.93</v>
+        <v>4.43</v>
       </c>
       <c r="H8" t="n">
-        <v>70.62</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.63</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.019</v>
+        <v>0.049</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.018</v>
+        <v>0.047</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,39 +888,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0</v>
+        <v>0.09</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>17277300</v>
+        <v>26231400</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>2.11</v>
+        <v>10.77</v>
       </c>
       <c r="H9" t="n">
-        <v>58.63</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.049</v>
+        <v>0.078</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.047</v>
+        <v>0.076</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,28 +933,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.155</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>15643500</v>
+        <v>24179100</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H10" t="n">
-        <v>84.41</v>
+        <v>47.73</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -954,10 +962,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.66</v>
+        <v>0.156</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,39 +978,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0069</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>VINVEST</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0</v>
+        <v>0.035</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.1667</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>14740700</v>
+        <v>20774100</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.76</v>
+        <v>7.97</v>
       </c>
       <c r="H11" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.81</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.307</v>
+        <v>0.019</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.302</v>
+        <v>0.018</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,28 +1023,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0313</v>
+        <v>0.93</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14097100</v>
+        <v>18351300</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="H12" t="n">
-        <v>47.73</v>
+        <v>66.02</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1044,10 +1052,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.156</v>
+        <v>0.86</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.156</v>
+        <v>0.763</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,39 +1068,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13745000</v>
+        <v>18002600</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.86</v>
+        <v>1.91</v>
       </c>
       <c r="H13" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.17</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,28 +1113,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>-0.1818</v>
+        <v>0.305</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>13223400</v>
+        <v>15831500</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.4</v>
+        <v>0.82</v>
       </c>
       <c r="H14" t="n">
-        <v>30.77</v>
+        <v>47.42</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -1134,10 +1142,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.061</v>
+        <v>0.307</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.302</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,39 +1158,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.74</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>11991900</v>
+        <v>15818300</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.24</v>
+        <v>0.66</v>
       </c>
       <c r="H15" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.92</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.39</v>
+        <v>0.66</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.403</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,28 +1203,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.265</v>
+        <v>4.93</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>-0.0185</v>
+        <v>-0.0733</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>11967800</v>
+        <v>14679100</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H16" t="n">
-        <v>41.24</v>
+        <v>32.11</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1224,10 +1232,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.286</v>
+        <v>5.395</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.279</v>
+        <v>5.508</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1240,28 +1248,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.82</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>11745400</v>
+        <v>14476000</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.16</v>
+        <v>0.9</v>
       </c>
       <c r="H17" t="n">
-        <v>66.02</v>
+        <v>54.27</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
@@ -1269,10 +1277,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.86</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.763</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1285,28 +1293,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0.011</v>
+        <v>0.0133</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11198900</v>
+        <v>13821500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="H18" t="n">
-        <v>60.81</v>
+        <v>31.76</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -1314,10 +1322,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.433</v>
+        <v>0.39</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.385</v>
+        <v>0.403</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1330,28 +1338,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.022</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10786500</v>
+        <v>13708700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.13</v>
+        <v>0.68</v>
       </c>
       <c r="H19" t="n">
-        <v>60.52</v>
+        <v>61.85</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
@@ -1359,10 +1367,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.316</v>
+        <v>0.433</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.266</v>
+        <v>0.385</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1375,28 +1383,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.265</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>10578000</v>
+        <v>12415700</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2.06</v>
+        <v>1.17</v>
       </c>
       <c r="H20" t="n">
-        <v>56.73</v>
+        <v>41.24</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -1404,10 +1412,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.267</v>
+        <v>0.286</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.27</v>
+        <v>0.279</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1420,28 +1428,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10285300</v>
+        <v>12326500</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H21" t="n">
-        <v>50.44</v>
+        <v>46.13</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1449,10 +1457,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.775</v>
+        <v>0.868</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.776</v>
+        <v>0.869</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1465,28 +1473,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>5.01</v>
+        <v>1.96</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>-0.0583</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>10131200</v>
+        <v>12234000</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.76</v>
+        <v>1.09</v>
       </c>
       <c r="H22" t="n">
-        <v>33.96</v>
+        <v>31.14</v>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
@@ -1494,10 +1502,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>5.402</v>
+        <v>2.103</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>5.51</v>
+        <v>2.23</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1510,33 +1518,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>-0.0263</v>
+        <v>0.775</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9461900</v>
+        <v>11455300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
+        <v>0.74</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.776</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1548,39 +1563,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.33</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>8592200</v>
+        <v>11002900</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.42</v>
+        <v>0.13</v>
       </c>
       <c r="H24" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.52</v>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.868</v>
+        <v>0.316</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.869</v>
+        <v>0.266</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1593,28 +1608,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>-0.0435</v>
+        <v>0.27</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>8535400</v>
+        <v>10662300</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.76</v>
+        <v>2.08</v>
       </c>
       <c r="H25" t="n">
-        <v>32.51</v>
+        <v>56.73</v>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
@@ -1622,10 +1637,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>2.105</v>
+        <v>0.267</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>2.23</v>
+        <v>0.27</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1638,40 +1653,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>8075000</v>
+        <v>9487100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>8.84</v>
-      </c>
-      <c r="H26" t="n">
-        <v>47.02</v>
+        <v>0.27</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J26" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
     </row>
@@ -1683,25 +1691,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.68</v>
+        <v>0.225</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>-0.0423</v>
+        <v>-0.0217</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7846300</v>
+        <v>9206700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
+      </c>
+      <c r="H27" t="n">
+        <v>51.42</v>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
@@ -1721,40 +1732,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.0122</v>
+        <v>0.675</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>-0.0493</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>7193300</v>
+        <v>8912700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H28" t="n">
-        <v>56.17</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="K28" s="9" t="n">
-        <v>0.383</v>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1766,28 +1770,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.0457</v>
+        <v>0.41</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6951600</v>
+        <v>8780600</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1.86</v>
+        <v>0.74</v>
       </c>
       <c r="H29" t="n">
-        <v>50.89</v>
+        <v>54.71</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1795,10 +1799,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.898</v>
+        <v>0.401</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.958</v>
+        <v>0.383</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1811,39 +1815,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>0.029</v>
+        <v>0.005</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6454300</v>
+        <v>8270000</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.05</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>70.38</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>1.969</v>
+        <v>0.005</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1.961</v>
+        <v>0.006</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1856,39 +1860,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>-0.04940000000000001</v>
+        <v>0.905</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0343</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6254500</v>
+        <v>7279000</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.82</v>
+        <v>1.95</v>
       </c>
       <c r="H31" t="n">
-        <v>37.96</v>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.12</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.423</v>
+        <v>0.897</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.439</v>
+        <v>0.958</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1901,28 +1905,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>0.0387</v>
+        <v>0.715</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.0272</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6253500</v>
+        <v>7162300</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H32" t="n">
-        <v>41.35</v>
+        <v>47.06</v>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
@@ -1930,10 +1934,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1.006</v>
+        <v>0.734</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.981</v>
+        <v>0.724</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1946,28 +1950,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>0</v>
+        <v>2.13</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.029</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6132700</v>
+        <v>7067800</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.58</v>
+        <v>1.15</v>
       </c>
       <c r="H33" t="n">
-        <v>60.81</v>
+        <v>70.38</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1975,10 +1979,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.624</v>
+        <v>1.969</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.618</v>
+        <v>1.961</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1991,39 +1995,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>0.0526</v>
+        <v>0.635</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>6106000</v>
+        <v>6956700</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="H34" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.81</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.209</v>
+        <v>0.624</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.229</v>
+        <v>0.618</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2036,39 +2040,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.0331</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5784400</v>
+        <v>6713100</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1.3</v>
+        <v>0.64</v>
       </c>
       <c r="H35" t="n">
-        <v>62.33</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.62</v>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.099</v>
+        <v>1.005</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.981</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2081,28 +2085,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.715</v>
+        <v>0.39</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>-0.0272</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5668800</v>
+        <v>6685900</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H36" t="n">
-        <v>47.06</v>
+        <v>39.02</v>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
@@ -2110,10 +2114,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.734</v>
+        <v>0.423</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.724</v>
+        <v>0.439</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2126,28 +2130,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>0.0206</v>
+        <v>4.7</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5503900</v>
+        <v>6615400</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>2.36</v>
+        <v>0.3</v>
       </c>
       <c r="H37" t="n">
-        <v>52.94</v>
+        <v>46.16</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2155,10 +2159,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.489</v>
+        <v>4.726</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.484</v>
+        <v>4.811</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2171,39 +2175,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>-0.0118</v>
+        <v>0.38</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5393800</v>
+        <v>6391900</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.15</v>
+        <v>0.59</v>
       </c>
       <c r="H38" t="n">
-        <v>37.37</v>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>28.85</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.455</v>
+        <v>0.469</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.475</v>
+        <v>0.583</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2216,28 +2220,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>-0.008</v>
+        <v>0.195</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5343000</v>
+        <v>6257600</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="H39" t="n">
-        <v>43.45</v>
+        <v>37.92</v>
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
@@ -2245,10 +2249,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>2.593</v>
+        <v>0.209</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>2.559</v>
+        <v>0.229</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2261,39 +2265,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.38</v>
+        <v>2.01</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.0101</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5296100</v>
+        <v>5896500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.49</v>
+        <v>0.21</v>
       </c>
       <c r="H40" t="n">
-        <v>28.85</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.8</v>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.469</v>
+        <v>1.967</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.583</v>
+        <v>1.795</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2306,39 +2310,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.01</v>
+        <v>0.11</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>0.0101</v>
+        <v>0.0476</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5234300</v>
+        <v>5883400</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.19</v>
+        <v>1.32</v>
       </c>
       <c r="H41" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="I41" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.55</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.967</v>
+        <v>0.099</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1.795</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2351,31 +2355,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>0</v>
+        <v>2.49</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5138100</v>
-      </c>
-      <c r="G42" s="12" t="n"/>
+        <v>5867500</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H42" t="n">
+        <v>43.45</v>
+      </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>2.593</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>2.559</v>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
     </row>
@@ -2387,39 +2400,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0098</v>
+        <v>1.14</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4835900</v>
+        <v>5866800</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1.43</v>
+        <v>0.77</v>
       </c>
       <c r="H43" t="n">
-        <v>80.16</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.43</v>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.45</v>
+        <v>1.203</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.437</v>
+        <v>1.29</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2441,19 +2454,19 @@
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>0.0219</v>
+        <v>0.0292</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4774900</v>
+        <v>5640700</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="H44" t="n">
-        <v>25.96</v>
+        <v>27.3</v>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
@@ -2461,7 +2474,7 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>1.575</v>
+        <v>1.576</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>1.867</v>
@@ -2477,28 +2490,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>-0.0133</v>
+        <v>0.5</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.0309</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4566800</v>
+        <v>5600300</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.67</v>
+        <v>2.41</v>
       </c>
       <c r="H45" t="n">
-        <v>48.14</v>
+        <v>54.66</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2506,10 +2519,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.372</v>
+        <v>0.49</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.37</v>
+        <v>0.485</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,28 +2535,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.0235</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4548100</v>
+        <v>5543100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="H46" t="n">
-        <v>33.75</v>
+        <v>36.3</v>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
@@ -2551,10 +2564,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.204</v>
+        <v>0.455</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1.29</v>
+        <v>0.474</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,36 +2580,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.225</v>
+        <v>0.37</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>-0.0217</v>
+        <v>-0.0133</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4421700</v>
+        <v>5474800</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.21</v>
+        <v>0.8</v>
       </c>
       <c r="H47" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="I47" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="9" t="n"/>
+        <v>48.14</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.37</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
     </row>
@@ -2608,39 +2625,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>-0.0187</v>
+        <v>0.52</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4387000</v>
+        <v>5191800</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.42</v>
+        <v>1.54</v>
       </c>
       <c r="H48" t="n">
-        <v>41.52</v>
-      </c>
-      <c r="I48" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.93000000000001</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.729</v>
+        <v>0.451</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2.746</v>
+        <v>0.437</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2653,40 +2670,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>-0.0105</v>
+        <v>0.005</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4290100</v>
-      </c>
-      <c r="G49" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46.16</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="n">
-        <v>4.726</v>
-      </c>
-      <c r="K49" s="9" t="n">
-        <v>4.811</v>
-      </c>
+        <v>5141100</v>
+      </c>
+      <c r="G49" s="12" t="n"/>
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n"/>
+      <c r="K49" s="9" t="n"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
     </row>
@@ -2698,39 +2706,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>0</v>
+        <v>2.63</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>-0.0187</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4180700</v>
+        <v>5069600</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.19</v>
+        <v>0.48</v>
       </c>
       <c r="H50" t="n">
-        <v>63.67</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.52</v>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.62</v>
+        <v>2.729</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.61</v>
+        <v>2.746</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2743,28 +2751,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0.0268</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4143400</v>
+        <v>4861200</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>1.22</v>
+        <v>0.79</v>
       </c>
       <c r="H51" t="n">
-        <v>49.06</v>
+        <v>24.18</v>
       </c>
       <c r="I51" s="17" t="inlineStr">
         <is>
@@ -2772,10 +2780,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.295</v>
+        <v>1.301</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.295</v>
+        <v>1.502</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2797,19 +2805,19 @@
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>-0.0058</v>
+        <v>3.42</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4078800</v>
+        <v>4586100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="H52" t="n">
-        <v>86.48</v>
+        <v>89.08</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2817,7 +2825,7 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>3.043</v>
+        <v>3.045</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>2.578</v>
@@ -2833,28 +2841,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>2.14</v>
+        <v>0.83</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>0.019</v>
+        <v>0.0061</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3940400</v>
+        <v>4554700</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.88</v>
+        <v>0.89</v>
       </c>
       <c r="H53" t="n">
-        <v>55.64</v>
+        <v>70.69</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2862,10 +2870,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>2.114</v>
+        <v>0.806</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.078</v>
+        <v>0.779</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2878,28 +2886,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>0.0268</v>
+        <v>0.105</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3884900</v>
+        <v>4534300</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.63</v>
+        <v>0.25</v>
       </c>
       <c r="H54" t="n">
-        <v>24.18</v>
+        <v>30.51</v>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
@@ -2907,10 +2915,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.301</v>
+        <v>0.131</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.502</v>
+        <v>0.146</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2923,28 +2931,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>0</v>
+        <v>1.65</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3775500</v>
+        <v>4288500</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="H55" t="n">
-        <v>68.73</v>
+        <v>52.12</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2952,10 +2960,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.805</v>
+        <v>1.626</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.779</v>
+        <v>1.676</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2968,28 +2976,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>4.2</v>
+        <v>2.14</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>0.0169</v>
+        <v>0.019</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3739700</v>
+        <v>4214700</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.49</v>
+        <v>2.02</v>
       </c>
       <c r="H56" t="n">
-        <v>65.76000000000001</v>
+        <v>55.64</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -2997,10 +3005,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>3.802</v>
+        <v>2.114</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>3.249</v>
+        <v>2.078</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3013,39 +3021,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.17</v>
+        <v>1.16</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3534500</v>
+        <v>4182200</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.58</v>
+        <v>0.45</v>
       </c>
       <c r="H57" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="I57" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.13</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.166</v>
+        <v>1.094</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.156</v>
+        <v>1.056</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3058,39 +3066,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>-0.0345</v>
+        <v>0.625</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3493000</v>
+        <v>4180700</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.73</v>
+        <v>1.19</v>
       </c>
       <c r="H58" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="I58" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.67</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.821</v>
+        <v>0.62</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.627</v>
+        <v>0.61</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3103,39 +3111,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>0.0062</v>
+        <v>0.295</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3353400</v>
+        <v>4143400</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.42</v>
+        <v>1.22</v>
       </c>
       <c r="H59" t="n">
-        <v>49.41</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.06</v>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.625</v>
+        <v>0.295</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.675</v>
+        <v>0.295</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3148,28 +3156,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3336100</v>
+        <v>4125100</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="H60" t="n">
-        <v>41.25</v>
+        <v>41.45</v>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
@@ -3177,10 +3185,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.282</v>
+        <v>0.348</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.282</v>
+        <v>0.33</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3193,28 +3201,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.18</v>
+        <v>0.755</v>
       </c>
       <c r="E61" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3260200</v>
+        <v>4104700</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.16</v>
+        <v>2.91</v>
       </c>
       <c r="H61" t="n">
-        <v>44.11</v>
+        <v>55.46</v>
       </c>
       <c r="I61" s="17" t="inlineStr">
         <is>
@@ -3222,10 +3230,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.185</v>
+        <v>0.75</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.186</v>
+        <v>0.723</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3238,39 +3246,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>0.053</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0552</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3043400</v>
+        <v>4027700</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1.78</v>
+        <v>0.85</v>
       </c>
       <c r="H62" t="n">
-        <v>50.62</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.71</v>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.367</v>
+        <v>0.819</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.439</v>
+        <v>0.627</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3283,28 +3291,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.16</v>
+        <v>4.19</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0145</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2971900</v>
+        <v>4022300</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.32</v>
+        <v>0.53</v>
       </c>
       <c r="H63" t="n">
-        <v>60.13</v>
+        <v>65.56</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3312,10 +3320,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.094</v>
+        <v>3.801</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.056</v>
+        <v>3.249</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3328,39 +3336,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>0</v>
+        <v>4.24</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0.06</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2926400</v>
+        <v>3769700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H64" t="n">
-        <v>25.46</v>
-      </c>
-      <c r="I64" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.39</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.479</v>
+        <v>3.986</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.618</v>
+        <v>3.645</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3373,39 +3381,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PCCS</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>0.0333</v>
+        <v>0.0303</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2854500</v>
+        <v>3544500</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>22.64</v>
+        <v>1.59</v>
       </c>
       <c r="H65" t="n">
-        <v>73.39</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.01</v>
+      </c>
+      <c r="I65" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.285</v>
+        <v>0.166</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.282</v>
+        <v>0.156</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3418,28 +3426,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E66" s="16" t="n">
-        <v>0</v>
+        <v>1.41</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0.0682</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2786300</v>
+        <v>3515000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.42</v>
+        <v>2.06</v>
       </c>
       <c r="H66" t="n">
-        <v>36.35</v>
+        <v>53.26</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3447,10 +3455,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.314</v>
+        <v>1.369</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.359</v>
+        <v>1.44</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3463,28 +3471,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>7.09</v>
+        <v>0.26</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0189</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2750800</v>
+        <v>3437400</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.17</v>
+        <v>0.49</v>
       </c>
       <c r="H67" t="n">
-        <v>31.13</v>
+        <v>39.48</v>
       </c>
       <c r="I67" s="17" t="inlineStr">
         <is>
@@ -3492,10 +3500,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>7.359</v>
+        <v>0.282</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>7.624</v>
+        <v>0.282</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3508,39 +3516,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>-0.0217</v>
+        <v>0.435</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.0116</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2748500</v>
+        <v>3350500</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>1.96</v>
+        <v>0.2</v>
       </c>
       <c r="H68" t="n">
-        <v>43.32</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.55</v>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.23</v>
+        <v>0.479</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.237</v>
+        <v>0.619</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3553,28 +3561,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E69" s="16" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2605000</v>
+        <v>3290200</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1.33</v>
+        <v>0.16</v>
       </c>
       <c r="H69" t="n">
-        <v>45.18</v>
+        <v>48.66</v>
       </c>
       <c r="I69" s="17" t="inlineStr">
         <is>
@@ -3582,10 +3590,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.186</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.186</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3598,28 +3606,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.865</v>
+        <v>4.8</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0103</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2565000</v>
+        <v>3278500</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="H70" t="n">
-        <v>50.44</v>
+        <v>46.64</v>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
@@ -3627,10 +3635,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.866</v>
+        <v>4.868</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.861</v>
+        <v>4.763</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3643,28 +3651,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>-0.0066</v>
+        <v>0.46</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2483200</v>
+        <v>3126600</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.32</v>
+        <v>1.57</v>
       </c>
       <c r="H71" t="n">
-        <v>45.8</v>
+        <v>47.46</v>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
@@ -3672,10 +3680,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.767</v>
+        <v>0.462</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.771</v>
+        <v>0.462</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3688,28 +3696,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>PCCS</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>-0.0035</v>
+        <v>0.305</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2482200</v>
+        <v>3043100</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.31</v>
+        <v>24.13</v>
       </c>
       <c r="H72" t="n">
-        <v>39.34</v>
+        <v>70.92</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3717,10 +3725,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>5.827</v>
+        <v>0.284</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>6.087</v>
+        <v>0.282</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3733,39 +3741,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E73" s="15" t="n">
-        <v>0.0049</v>
+        <v>5.73</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2412300</v>
+        <v>2981500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="H73" t="n">
-        <v>48.91</v>
-      </c>
-      <c r="I73" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.34</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>2.039</v>
+        <v>5.827</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>2.064</v>
+        <v>6.087</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3778,39 +3786,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.3</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2388300</v>
+        <v>2970700</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="H74" t="n">
-        <v>48.35</v>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.96</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>4.871</v>
+        <v>0.315</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>4.764</v>
+        <v>0.359</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3823,28 +3831,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>0.0245</v>
+        <v>7.09</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2292700</v>
+        <v>2967700</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.37</v>
+        <v>0.18</v>
       </c>
       <c r="H75" t="n">
-        <v>43.04</v>
+        <v>31.13</v>
       </c>
       <c r="I75" s="17" t="inlineStr">
         <is>
@@ -3852,10 +3860,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.885</v>
+        <v>7.359</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.859</v>
+        <v>7.624</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3868,28 +3876,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0.0179</v>
+        <v>0.865</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2286900</v>
+        <v>2880000</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.6</v>
+        <v>0.97</v>
       </c>
       <c r="H76" t="n">
-        <v>56.61</v>
+        <v>50.44</v>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
@@ -3897,10 +3905,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.829</v>
+        <v>0.866</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.799</v>
+        <v>0.861</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3913,39 +3921,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.325</v>
+        <v>0.225</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>-0.0299</v>
+        <v>-0.0217</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2263400</v>
+        <v>2878500</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.28</v>
+        <v>2.06</v>
       </c>
       <c r="H77" t="n">
-        <v>41.45</v>
-      </c>
-      <c r="I77" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.32</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.348</v>
+        <v>0.23</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.33</v>
+        <v>0.237</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3958,28 +3966,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>4.19</v>
+        <v>1.58</v>
       </c>
       <c r="E78" s="15" t="n">
-        <v>0.0475</v>
+        <v>0.0194</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2262600</v>
+        <v>2827700</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.24</v>
+        <v>0.46</v>
       </c>
       <c r="H78" t="n">
-        <v>60.03</v>
+        <v>38.17</v>
       </c>
       <c r="I78" s="17" t="inlineStr">
         <is>
@@ -3987,10 +3995,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>3.982</v>
+        <v>1.658</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>3.644</v>
+        <v>1.742</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4003,28 +4011,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>-0.0042</v>
+        <v>0.555</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2262000</v>
+        <v>2785000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.2</v>
+        <v>1.42</v>
       </c>
       <c r="H79" t="n">
-        <v>42.66</v>
+        <v>45.18</v>
       </c>
       <c r="I79" s="17" t="inlineStr">
         <is>
@@ -4032,10 +4040,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>2.433</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>2.412</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4048,38 +4056,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.0282</v>
+        <v>0.755</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2157100</v>
+        <v>2752700</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="H80" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.8</v>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="K80" s="9" t="n"/>
+        <v>0.767</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>0.771</v>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
     </row>
@@ -4091,28 +4101,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>2.04</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2039100</v>
+        <v>2645700</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.29</v>
+        <v>0.66</v>
       </c>
       <c r="H81" t="n">
-        <v>44.09</v>
+        <v>48.91</v>
       </c>
       <c r="I81" s="17" t="inlineStr">
         <is>
@@ -4120,10 +4130,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>6.342</v>
+        <v>2.039</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>6.646</v>
+        <v>2.064</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4136,39 +4146,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>0</v>
+        <v>0.975</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.0104</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2034100</v>
+        <v>2615300</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1.44</v>
+        <v>0.55</v>
       </c>
       <c r="H82" t="n">
-        <v>55.46</v>
-      </c>
-      <c r="I82" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.22</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.75</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.723</v>
+        <v>0.892</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4181,28 +4191,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.58</v>
+        <v>0.835</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>0.0194</v>
+        <v>0.0245</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2023200</v>
+        <v>2469700</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="H83" t="n">
-        <v>38.17</v>
+        <v>43.04</v>
       </c>
       <c r="I83" s="17" t="inlineStr">
         <is>
@@ -4210,10 +4220,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.658</v>
+        <v>0.885</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.742</v>
+        <v>0.859</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4226,28 +4236,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KEYFIELD</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1.38</v>
+        <v>2.38</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>-0.0143</v>
+        <v>-0.0042</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1822000</v>
+        <v>2455900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>9.19</v>
+        <v>0.22</v>
       </c>
       <c r="H84" t="n">
-        <v>48.48</v>
+        <v>42.66</v>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
@@ -4255,10 +4265,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>1.388</v>
+        <v>2.433</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.372</v>
+        <v>2.412</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4271,28 +4281,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>0.0168</v>
+        <v>6.3</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1775000</v>
+        <v>2431000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="H85" t="n">
-        <v>56.17</v>
+        <v>44.57</v>
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
@@ -4300,10 +4310,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.177</v>
+        <v>6.343</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.149</v>
+        <v>6.647</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4316,28 +4326,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>-0.0039</v>
+        <v>0.865</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0.0298</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1774600</v>
+        <v>2422800</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.31</v>
+        <v>0.63</v>
       </c>
       <c r="H86" t="n">
-        <v>45.76</v>
+        <v>58.16</v>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
@@ -4345,10 +4355,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>2.594</v>
+        <v>0.83</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2.604</v>
+        <v>0.799</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4361,28 +4371,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.0472</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1707400</v>
+        <v>2380600</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.19</v>
+        <v>0.64</v>
       </c>
       <c r="H87" t="n">
-        <v>37</v>
+        <v>53.95</v>
       </c>
       <c r="I87" s="17" t="inlineStr">
         <is>
@@ -4390,10 +4400,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.608</v>
+        <v>1.1</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.616</v>
+        <v>0.927</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4406,28 +4416,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>0.0108</v>
+        <v>0.555</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>-0.0089</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1686500</v>
+        <v>2324300</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="H88" t="n">
-        <v>52.55</v>
+        <v>48.36</v>
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
@@ -4435,10 +4445,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.789</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>2.69</v>
+        <v>0.546</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4451,40 +4461,38 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.45</v>
+        <v>0.365</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>0.0112</v>
+        <v>0.0282</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1641400</v>
+        <v>2284200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="H89" t="n">
-        <v>42.42</v>
-      </c>
-      <c r="I89" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.1</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="K89" s="9" t="n">
-        <v>0.469</v>
-      </c>
+        <v>0.337</v>
+      </c>
+      <c r="K89" s="9" t="n"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
     </row>
@@ -4496,28 +4504,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v>0.0283</v>
+        <v>2.55</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>-0.0039</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1630500</v>
+        <v>2150800</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="H90" t="n">
-        <v>52.05</v>
+        <v>45.76</v>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
@@ -4525,10 +4533,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>1.098</v>
+        <v>2.594</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.927</v>
+        <v>2.604</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4541,28 +4549,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.75</v>
+        <v>0.895</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>0.0274</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1611700</v>
+        <v>2118500</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.29</v>
+        <v>1.22</v>
       </c>
       <c r="H91" t="n">
-        <v>53.34</v>
+        <v>48.61</v>
       </c>
       <c r="I91" s="17" t="inlineStr">
         <is>
@@ -4570,10 +4578,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.74</v>
+        <v>0.905</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.892</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4586,39 +4594,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>-0.0129</v>
+        <v>0.755</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>0.0342</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1596100</v>
+        <v>2095600</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="H92" t="n">
-        <v>54.11</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.07</v>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>6.804</v>
+        <v>0.74</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>6.821</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4631,39 +4639,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="E93" s="15" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0556</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1593900</v>
+        <v>2027700</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="H93" t="n">
-        <v>62.27</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.03</v>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.288</v>
+        <v>2.637</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>2.207</v>
+        <v>2.829</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4676,39 +4684,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.23</v>
+        <v>1.2</v>
       </c>
       <c r="E94" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1587000</v>
+        <v>2016700</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>1.61</v>
+        <v>0.31</v>
       </c>
       <c r="H94" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.86</v>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.223</v>
+        <v>1.176</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.23</v>
+        <v>1.149</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4721,28 +4729,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.455</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>0.0225</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1586400</v>
+        <v>1991900</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H95" t="n">
-        <v>34.72</v>
+        <v>43.41</v>
       </c>
       <c r="I95" s="17" t="inlineStr">
         <is>
@@ -4750,10 +4758,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.645</v>
+        <v>0.492</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.469</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4766,39 +4774,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>-0.0115</v>
+        <v>0.615</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>0.0165</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1506100</v>
+        <v>1880200</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.22</v>
+        <v>0.62</v>
       </c>
       <c r="H96" t="n">
-        <v>51.18</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.18</v>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.429</v>
+        <v>0.68</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.418</v>
+        <v>0.734</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4811,39 +4819,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.27</v>
+        <v>2.8</v>
       </c>
       <c r="E97" s="15" t="n">
-        <v>0.016</v>
+        <v>0.0072</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1491900</v>
+        <v>1853900</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H97" t="n">
-        <v>58.06</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52</v>
+      </c>
+      <c r="I97" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.228</v>
+        <v>2.788</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.206</v>
+        <v>2.69</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4856,28 +4864,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>KEYFIELD</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.985</v>
+        <v>1.37</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.0214</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1437900</v>
+        <v>1852000</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.4</v>
+        <v>9.34</v>
       </c>
       <c r="H98" t="n">
-        <v>44.83</v>
+        <v>46.47</v>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
@@ -4885,10 +4893,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.024</v>
+        <v>1.387</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.973</v>
+        <v>1.372</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4901,39 +4909,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E99" s="16" t="n">
-        <v>0</v>
+        <v>0.54</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>-0.0092</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1410600</v>
+        <v>1851900</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="H99" t="n">
-        <v>52.96</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.36</v>
+      </c>
+      <c r="I99" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.336</v>
+        <v>0.607</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.343</v>
+        <v>0.616</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4946,39 +4954,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>9.99</v>
+        <v>0.205</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.0238</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1396900</v>
+        <v>1827700</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="H100" t="n">
-        <v>48</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.88</v>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>9.996</v>
+        <v>0.223</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>10.112</v>
+        <v>0.269</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4991,39 +4999,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>-0.0179</v>
+        <v>2.4</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0.0042</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1360000</v>
+        <v>1758600</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H101" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I101" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.67</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>2.287</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.546</v>
+        <v>2.207</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5045,19 +5053,19 @@
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.225</v>
+        <v>0.22</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>-0.0217</v>
+        <v>-0.0435</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1338200</v>
+        <v>1743500</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="H102" t="n">
-        <v>14</v>
+        <v>13.39</v>
       </c>
       <c r="I102" s="17" t="inlineStr">
         <is>
@@ -5065,7 +5073,7 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="K102" s="9" t="n"/>
       <c r="L102" t="inlineStr"/>
@@ -5079,28 +5087,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>2.38</v>
+        <v>0.82</v>
       </c>
       <c r="E103" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1325700</v>
+        <v>1709500</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="H103" t="n">
-        <v>33.86</v>
+        <v>30.27</v>
       </c>
       <c r="I103" s="17" t="inlineStr">
         <is>
@@ -5108,10 +5116,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>2.481</v>
+        <v>0.868</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>2.646</v>
+        <v>0.931</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5124,39 +5132,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E104" s="16" t="n">
-        <v>0</v>
+        <v>6.87</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1283300</v>
+        <v>1705500</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.42</v>
+        <v>0.34</v>
       </c>
       <c r="H104" t="n">
-        <v>32.83</v>
-      </c>
-      <c r="I104" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.75</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.679</v>
+        <v>6.805</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.734</v>
+        <v>6.822</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5169,39 +5177,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.895</v>
+        <v>1.28</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.024</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1256000</v>
+        <v>1695200</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.72</v>
+        <v>0.24</v>
       </c>
       <c r="H105" t="n">
-        <v>48.61</v>
-      </c>
-      <c r="I105" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.18</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.905</v>
+        <v>1.228</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.892</v>
+        <v>1.206</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5214,28 +5222,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E106" s="15" t="n">
-        <v>0.0227</v>
+        <v>0.585</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1255500</v>
+        <v>1694600</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>2.91</v>
+        <v>0.21</v>
       </c>
       <c r="H106" t="n">
-        <v>51.18</v>
+        <v>35.41</v>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
@@ -5243,10 +5251,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.225</v>
+        <v>0.646</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.224</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5259,28 +5267,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>6.79</v>
+        <v>0.23</v>
       </c>
       <c r="E107" s="15" t="n">
-        <v>0.0089</v>
+        <v>0.0455</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1245400</v>
+        <v>1683800</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.11</v>
+        <v>3.9</v>
       </c>
       <c r="H107" t="n">
-        <v>37.48</v>
+        <v>61.36</v>
       </c>
       <c r="I107" s="17" t="inlineStr">
         <is>
@@ -5288,10 +5296,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>7.053</v>
+        <v>0.225</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>7.494</v>
+        <v>0.224</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5304,28 +5312,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0.0027</v>
+        <v>9.99</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1236800</v>
+        <v>1655100</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="H108" t="n">
-        <v>41.43</v>
+        <v>48</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5333,10 +5341,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>7.411</v>
+        <v>9.996</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>7.819</v>
+        <v>10.112</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5349,39 +5357,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>-0.0061</v>
+        <v>0.23</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1231700</v>
+        <v>1587000</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.43</v>
+        <v>1.61</v>
       </c>
       <c r="H109" t="n">
-        <v>29.37</v>
-      </c>
-      <c r="I109" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.4</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.867</v>
+        <v>0.223</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.931</v>
+        <v>0.23</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5394,39 +5402,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.31</v>
+        <v>7.35</v>
       </c>
       <c r="E110" s="15" t="n">
-        <v>0.0164</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1222600</v>
+        <v>1582200</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.96</v>
+        <v>0.14</v>
       </c>
       <c r="H110" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="I110" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.06</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.315</v>
+        <v>7.412</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.328</v>
+        <v>7.819</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5439,28 +5447,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E111" s="16" t="n">
-        <v>0</v>
+        <v>6.8</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>0.0104</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1208000</v>
+        <v>1575600</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.36</v>
+        <v>0.14</v>
       </c>
       <c r="H111" t="n">
-        <v>40.12</v>
+        <v>37.88</v>
       </c>
       <c r="I111" s="17" t="inlineStr">
         <is>
@@ -5468,10 +5476,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.123</v>
+        <v>7.054</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.112</v>
+        <v>7.495</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5484,39 +5492,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v>0.0342</v>
+        <v>0.43</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1206000</v>
+        <v>1561700</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H112" t="n">
-        <v>37.34</v>
-      </c>
-      <c r="I112" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.18</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>2.633</v>
+        <v>0.429</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.828</v>
+        <v>0.418</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5529,28 +5537,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>1.13</v>
+        <v>2.37</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>-0.0174</v>
+        <v>-0.0042</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1204200</v>
+        <v>1514800</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.55</v>
+        <v>0.37</v>
       </c>
       <c r="H113" t="n">
-        <v>29.22</v>
+        <v>33.15</v>
       </c>
       <c r="I113" s="17" t="inlineStr">
         <is>
@@ -5558,10 +5566,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>1.198</v>
+        <v>2.48</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.303</v>
+        <v>2.645</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5574,28 +5582,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>YNHPROP</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0.0526</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1169800</v>
+        <v>1511100</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.25</v>
+        <v>4.07</v>
       </c>
       <c r="H114" t="n">
-        <v>62.7</v>
+        <v>51.46</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5603,10 +5611,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.294</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.892</v>
+        <v>0.31</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5619,39 +5627,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.3</v>
+        <v>0.98</v>
       </c>
       <c r="E115" s="10" t="n">
-        <v>-0.0323</v>
+        <v>-0.02</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1162000</v>
+        <v>1474800</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.88</v>
+        <v>0.41</v>
       </c>
       <c r="H115" t="n">
-        <v>49.39</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.11</v>
+      </c>
+      <c r="I115" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.296</v>
+        <v>1.023</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.327</v>
+        <v>0.973</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5664,28 +5672,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.205</v>
+        <v>0.42</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>-0.0238</v>
+        <v>-0.0233</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1118200</v>
+        <v>1439300</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.1</v>
+        <v>0.82</v>
       </c>
       <c r="H116" t="n">
-        <v>30.88</v>
+        <v>38.84</v>
       </c>
       <c r="I116" s="17" t="inlineStr">
         <is>
@@ -5693,10 +5701,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.223</v>
+        <v>0.445</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.269</v>
+        <v>0.457</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5709,39 +5717,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E117" s="15" t="n">
-        <v>0.0086</v>
+        <v>0.34</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1107000</v>
+        <v>1416800</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="H117" t="n">
-        <v>62.18</v>
-      </c>
-      <c r="I117" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.96</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.54</v>
+        <v>0.336</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.485</v>
+        <v>0.343</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5769,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1045500</v>
+        <v>1391500</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.91</v>
+        <v>1.21</v>
       </c>
       <c r="H118" t="n">
         <v>68.98999999999999</v>
@@ -5799,28 +5807,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.305</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1015200</v>
+        <v>1374300</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.35</v>
+        <v>1.08</v>
       </c>
       <c r="H119" t="n">
-        <v>28.13</v>
+        <v>38.36</v>
       </c>
       <c r="I119" s="17" t="inlineStr">
         <is>
@@ -5828,10 +5836,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.528</v>
+        <v>0.315</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.328</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5844,28 +5852,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>-0.008100000000000001</v>
+        <v>2.98</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0.0567</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1013400</v>
+        <v>1364000</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="H120" t="n">
-        <v>42.11</v>
+        <v>61.58</v>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
@@ -5873,10 +5881,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.289</v>
+        <v>2.822</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.3</v>
+        <v>2.348</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5889,28 +5897,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>-0.0157</v>
+        <v>0.955</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>0.0437</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>976300</v>
+        <v>1354800</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.37</v>
+        <v>1.32</v>
       </c>
       <c r="H121" t="n">
-        <v>50.28</v>
+        <v>52.17</v>
       </c>
       <c r="I121" s="17" t="inlineStr">
         <is>
@@ -5918,10 +5926,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.264</v>
+        <v>0.927</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.186</v>
+        <v>1.011</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5934,28 +5942,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>-0.0299</v>
+        <v>-0.0204</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>964700</v>
+        <v>1303400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.32</v>
+        <v>1.28</v>
       </c>
       <c r="H122" t="n">
-        <v>51.71</v>
+        <v>29.26</v>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
@@ -5963,10 +5971,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.288</v>
+        <v>1.56</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.242</v>
+        <v>1.623</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5979,39 +5987,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.7</v>
+        <v>1.06</v>
       </c>
       <c r="E123" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>940800</v>
+        <v>1298500</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="H123" t="n">
-        <v>42.28</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.12</v>
+      </c>
+      <c r="I123" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.713</v>
+        <v>1.123</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.77</v>
+        <v>1.112</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6024,39 +6032,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.25</v>
+        <v>2.69</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>-0.0157</v>
+        <v>-0.011</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>937900</v>
+        <v>1296600</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="H124" t="n">
-        <v>52.78</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.52</v>
+      </c>
+      <c r="I124" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.244</v>
+        <v>2.832</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.115</v>
+        <v>2.97</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6069,28 +6077,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E125" s="16" t="n">
-        <v>0</v>
+        <v>0.46</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>936900</v>
+        <v>1267600</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H125" t="n">
-        <v>53.94</v>
+        <v>53.88</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6098,10 +6106,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>1.266</v>
+        <v>0.452</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>1.271</v>
+        <v>0.45</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6114,39 +6122,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>2.67</v>
+        <v>0.3</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>-0.0184</v>
+        <v>-0.0323</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>917600</v>
+        <v>1254000</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.26</v>
+        <v>0.95</v>
       </c>
       <c r="H126" t="n">
-        <v>35.48</v>
-      </c>
-      <c r="I126" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.39</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>2.83</v>
+        <v>0.296</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>2.97</v>
+        <v>0.327</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6159,28 +6167,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>0.0273</v>
+        <v>1.13</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>-0.0174</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>911400</v>
+        <v>1249000</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H127" t="n">
-        <v>50.04</v>
+        <v>29.22</v>
       </c>
       <c r="I127" s="17" t="inlineStr">
         <is>
@@ -6188,10 +6196,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.925</v>
+        <v>1.198</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1.011</v>
+        <v>1.303</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6204,39 +6212,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>6.5</v>
+        <v>3.39</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>-0.0015</v>
+        <v>-0.0029</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>909600</v>
+        <v>1245300</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.15</v>
+        <v>0.96</v>
       </c>
       <c r="H128" t="n">
-        <v>55.41</v>
-      </c>
-      <c r="I128" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.31</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>6.297</v>
+        <v>3.379</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>5.999</v>
+        <v>3.243</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6249,28 +6257,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.535</v>
+        <v>0.235</v>
       </c>
       <c r="E129" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0217</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>880300</v>
+        <v>1240100</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.17</v>
+        <v>0.68</v>
       </c>
       <c r="H129" t="n">
-        <v>47.92</v>
+        <v>38.25</v>
       </c>
       <c r="I129" s="17" t="inlineStr">
         <is>
@@ -6278,10 +6286,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.548</v>
+        <v>0.246</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.525</v>
+        <v>0.268</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6294,28 +6302,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.585</v>
+        <v>0.59</v>
       </c>
       <c r="E130" s="15" t="n">
-        <v>0.0086</v>
+        <v>0.0172</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>876600</v>
+        <v>1209200</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="H130" t="n">
-        <v>54.15</v>
+        <v>62.88</v>
       </c>
       <c r="I130" s="17" t="inlineStr">
         <is>
@@ -6323,7 +6331,7 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.575</v>
+        <v>0.541</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0.485</v>
@@ -6339,39 +6347,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0336</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>WINSTAR</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.38</v>
+        <v>0.63</v>
       </c>
       <c r="E131" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>870200</v>
+        <v>1173100</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.43</v>
+        <v>2.96</v>
       </c>
       <c r="H131" t="n">
-        <v>56.09</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.76</v>
+      </c>
+      <c r="I131" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>1.367</v>
+        <v>0.637</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.346</v>
+        <v>0.642</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6384,28 +6392,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>-0.0476</v>
+        <v>0.72</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>840900</v>
+        <v>1165900</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.83</v>
+        <v>0.49</v>
       </c>
       <c r="H132" t="n">
-        <v>26.29</v>
+        <v>42.27</v>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
@@ -6413,10 +6421,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>1.556</v>
+        <v>0.757</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.622</v>
+        <v>0.769</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6429,39 +6437,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0098</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>AUMAS</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E133" s="15" t="n">
-        <v>0.0071</v>
+        <v>0.355</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.0274</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>838200</v>
+        <v>1148500</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.35</v>
+        <v>0.96</v>
       </c>
       <c r="H133" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="I133" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.79</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.756</v>
+        <v>0.347</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.769</v>
+        <v>0.358</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6474,39 +6482,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="E134" s="15" t="n">
-        <v>0.0022</v>
+        <v>0.505</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>835300</v>
+        <v>1111900</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="H134" t="n">
-        <v>59.57</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.83</v>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>4.432</v>
+        <v>0.529</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>4.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6519,39 +6527,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>-0.0022</v>
+        <v>6.56</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>817300</v>
+        <v>1108700</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H135" t="n">
-        <v>38.17</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.36</v>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>4.56</v>
+        <v>6.303</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>4.641</v>
+        <v>6</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6564,39 +6572,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>TROP</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E136" s="16" t="n">
-        <v>0</v>
+        <v>1.18</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>805000</v>
+        <v>1108100</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.77</v>
+        <v>1.13</v>
       </c>
       <c r="H136" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.96</v>
+      </c>
+      <c r="I136" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.633</v>
+        <v>1.183</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.632</v>
+        <v>1.187</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6609,39 +6617,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E137" s="15" t="n">
-        <v>0.0124</v>
+        <v>1.28</v>
+      </c>
+      <c r="E137" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>790200</v>
+        <v>1094200</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>1.14</v>
+        <v>0.28</v>
       </c>
       <c r="H137" t="n">
-        <v>32.56</v>
-      </c>
-      <c r="I137" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.94</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.716</v>
+        <v>1.266</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.77</v>
+        <v>1.271</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6654,28 +6662,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E138" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.245</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>774200</v>
+        <v>1089400</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H138" t="n">
-        <v>49.88</v>
+        <v>39.46</v>
       </c>
       <c r="I138" s="17" t="inlineStr">
         <is>
@@ -6683,10 +6691,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.592</v>
+        <v>0.264</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.584</v>
+        <v>0.284</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6699,28 +6707,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TROP</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.17</v>
+        <v>0.375</v>
       </c>
       <c r="E139" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>764800</v>
+        <v>1084700</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="H139" t="n">
-        <v>46.26</v>
+        <v>39.94</v>
       </c>
       <c r="I139" s="17" t="inlineStr">
         <is>
@@ -6728,10 +6736,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.182</v>
+        <v>0.387</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.187</v>
+        <v>0.39</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6744,28 +6752,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.805</v>
+        <v>0.26</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>-0.0123</v>
+        <v>-0.0189</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>748400</v>
+        <v>1082800</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="H140" t="n">
-        <v>29.03</v>
+        <v>32.3</v>
       </c>
       <c r="I140" s="17" t="inlineStr">
         <is>
@@ -6773,10 +6781,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.832</v>
+        <v>0.296</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.856</v>
+        <v>0.323</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6789,28 +6797,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.93</v>
+        <v>1.27</v>
       </c>
       <c r="E141" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>734500</v>
+        <v>1080900</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.17</v>
+        <v>0.41</v>
       </c>
       <c r="H141" t="n">
-        <v>34.33</v>
+        <v>52.13</v>
       </c>
       <c r="I141" s="17" t="inlineStr">
         <is>
@@ -6818,10 +6826,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.952</v>
+        <v>1.266</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.033</v>
+        <v>1.186</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6834,39 +6842,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E142" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.595</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>0.0259</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>730100</v>
+        <v>1076200</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="H142" t="n">
-        <v>51.65</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.91</v>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.64</v>
+        <v>0.592</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.628</v>
+        <v>0.585</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6879,28 +6887,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E143" s="16" t="n">
-        <v>0</v>
+        <v>0.575</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>718600</v>
+        <v>1054400</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="H143" t="n">
-        <v>39.04</v>
+        <v>52.78</v>
       </c>
       <c r="I143" s="17" t="inlineStr">
         <is>
@@ -6908,10 +6916,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>1.272</v>
+        <v>0.574</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>1.316</v>
+        <v>0.485</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6924,39 +6932,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="E144" s="15" t="n">
-        <v>0.0141</v>
+        <v>1.22</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>705900</v>
+        <v>1025400</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="H144" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="I144" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.13</v>
+      </c>
+      <c r="I144" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>3.535</v>
+        <v>1.288</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>3.577</v>
+        <v>1.3</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6969,39 +6977,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="E145" s="16" t="n">
-        <v>0</v>
+        <v>0.33</v>
+      </c>
+      <c r="E145" s="15" t="n">
+        <v>0.0645</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>688000</v>
+        <v>1025300</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.21</v>
+        <v>5.43</v>
       </c>
       <c r="H145" t="n">
-        <v>47.23</v>
-      </c>
-      <c r="I145" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.2</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>3.799</v>
+        <v>0.306</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>3.741</v>
+        <v>0.295</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7014,28 +7022,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>10.6</v>
+        <v>0.545</v>
       </c>
       <c r="E146" s="15" t="n">
-        <v>0.0134</v>
+        <v>0.0283</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>686600</v>
+        <v>1018000</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H146" t="n">
-        <v>55.37</v>
+        <v>50.14</v>
       </c>
       <c r="I146" s="17" t="inlineStr">
         <is>
@@ -7043,10 +7051,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>10.461</v>
+        <v>0.549</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>9.872</v>
+        <v>0.525</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7059,28 +7067,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.32</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>678700</v>
+        <v>1006600</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="H147" t="n">
-        <v>58.53</v>
+        <v>43.38</v>
       </c>
       <c r="I147" s="17" t="inlineStr">
         <is>
@@ -7088,10 +7096,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.088</v>
+        <v>0.337</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.962</v>
+        <v>0.337</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7104,39 +7112,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E148" s="15" t="n">
-        <v>0.0284</v>
+        <v>0.7</v>
+      </c>
+      <c r="E148" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>667100</v>
+        <v>1005400</v>
       </c>
       <c r="G148" s="12" t="n">
         <v>0.16</v>
       </c>
       <c r="H148" t="n">
-        <v>58.66</v>
-      </c>
-      <c r="I148" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.28</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>2.815</v>
+        <v>0.713</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>2.347</v>
+        <v>0.77</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7149,39 +7157,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.635</v>
+        <v>1.26</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>658800</v>
+        <v>990500</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="H149" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I149" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.67</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.714</v>
+        <v>1.245</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.115</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7194,28 +7202,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E150" s="10" t="n">
-        <v>-0.004699999999999999</v>
+        <v>1.38</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>645000</v>
+        <v>986100</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.06</v>
+        <v>0.49</v>
       </c>
       <c r="H150" t="n">
-        <v>49.24</v>
+        <v>56.09</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7223,10 +7231,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>2.105</v>
+        <v>1.367</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>2.109</v>
+        <v>1.346</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7239,28 +7247,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.73</v>
+        <v>1.3</v>
       </c>
       <c r="E151" s="10" t="n">
-        <v>-0.0135</v>
+        <v>-0.0299</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>644300</v>
+        <v>983700</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="H151" t="n">
-        <v>49.48</v>
+        <v>51.71</v>
       </c>
       <c r="I151" s="17" t="inlineStr">
         <is>
@@ -7268,10 +7276,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.741</v>
+        <v>1.288</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.707</v>
+        <v>1.242</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7284,39 +7292,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>-0.0072</v>
+        <v>5.08</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>0.018</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>637000</v>
+        <v>937100</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1.04</v>
+        <v>0.23</v>
       </c>
       <c r="H152" t="n">
-        <v>56.44</v>
-      </c>
-      <c r="I152" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.47</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>5.058</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.663</v>
+        <v>5.037</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7329,39 +7337,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E153" s="15" t="n">
-        <v>0.112</v>
+        <v>0.705</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>627500</v>
+        <v>933500</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>2.31</v>
+        <v>0.54</v>
       </c>
       <c r="H153" t="n">
-        <v>77.52</v>
-      </c>
-      <c r="I153" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.17</v>
+      </c>
+      <c r="I153" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>1.166</v>
+        <v>0.721</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>1.192</v>
+        <v>0.739</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7374,28 +7382,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>1.74</v>
+        <v>0.745</v>
       </c>
       <c r="E154" s="15" t="n">
-        <v>0.0116</v>
+        <v>0.0068</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>588700</v>
+        <v>921000</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="H154" t="n">
-        <v>43.72</v>
+        <v>52.04</v>
       </c>
       <c r="I154" s="17" t="inlineStr">
         <is>
@@ -7403,10 +7411,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>1.753</v>
+        <v>0.742</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.854</v>
+        <v>0.708</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7419,28 +7427,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.64</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>575700</v>
+        <v>909700</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="H155" t="n">
-        <v>41.17</v>
+        <v>39.59</v>
       </c>
       <c r="I155" s="17" t="inlineStr">
         <is>
@@ -7448,10 +7456,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>0.721</v>
+        <v>0.715</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>0.739</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7464,39 +7472,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>1.06</v>
+        <v>4.66</v>
       </c>
       <c r="E156" s="15" t="n">
-        <v>0.0495</v>
+        <v>0.0022</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>573700</v>
+        <v>904600</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="H156" t="n">
-        <v>39.17</v>
-      </c>
-      <c r="I156" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.57</v>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>1.129</v>
+        <v>4.432</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1.256</v>
+        <v>4.44</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7509,28 +7517,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E157" s="15" t="n">
-        <v>0.0112</v>
+        <v>4.46</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>564400</v>
+        <v>900200</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
       <c r="H157" t="n">
-        <v>51.84</v>
+        <v>37.41</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7538,10 +7546,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>0.892</v>
+        <v>4.559</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>0.903</v>
+        <v>4.64</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7554,28 +7562,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E158" s="10" t="n">
-        <v>-0.0137</v>
+        <v>1.23</v>
+      </c>
+      <c r="E158" s="15" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>538700</v>
+        <v>895300</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="H158" t="n">
-        <v>46.19</v>
+        <v>41.01</v>
       </c>
       <c r="I158" s="17" t="inlineStr">
         <is>
@@ -7583,10 +7591,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>2.983</v>
+        <v>1.273</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>2.861</v>
+        <v>1.316</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7599,45 +7607,1170 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>5.11</v>
+        <v>1.63</v>
       </c>
       <c r="E159" s="15" t="n">
-        <v>0.024</v>
+        <v>0.0124</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>527600</v>
+        <v>867200</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.13</v>
+        <v>1.25</v>
       </c>
       <c r="H159" t="n">
-        <v>52.87</v>
-      </c>
-      <c r="I159" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.56</v>
+      </c>
+      <c r="I159" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>5.06</v>
+        <v>1.716</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>5.038</v>
+        <v>1.77</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="E160" s="15" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>864500</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H160" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="I160" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>10.455</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E161" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>829300</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H161" t="n">
+        <v>34.33</v>
+      </c>
+      <c r="I161" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>819100</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H162" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="I162" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>-0.004699999999999999</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>814900</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H163" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>2.105</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E164" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>805000</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H164" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E165" s="15" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>795200</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H165" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="I165" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E166" s="15" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>794600</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H166" t="n">
+        <v>47.21</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>1.069</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>MAXIS</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="E167" s="15" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>786500</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H167" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>3.535</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>3.577</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>730100</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H168" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>728500</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H169" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="I169" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>3.798</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>3.741</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E170" s="15" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>705600</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H170" t="n">
+        <v>60.49</v>
+      </c>
+      <c r="I170" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>694100</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H171" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="I171" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>2.883</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>3.023</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>679200</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H172" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E173" s="15" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>674400</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H173" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="I173" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>669700</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H174" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="I174" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>2.986</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>2.861</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E175" s="15" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>641800</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H175" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="I175" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>4.331</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>4.624</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>637000</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H176" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="I176" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>7197</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>GESHEN</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E177" s="15" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>627500</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H177" t="n">
+        <v>77.52</v>
+      </c>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E178" s="15" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>608800</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H178" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="I178" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E179" s="15" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>606900</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H179" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>2.724</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>2.361</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E180" s="15" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>592900</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H180" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="I180" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>588200</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H181" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="I181" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>7.915</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>7.933</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>-0.0129</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>555400</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H182" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="I182" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>8.558</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>8.667999999999999</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>TIMECOM</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="E183" s="15" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>553400</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H183" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="I183" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>5.465</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>5.738</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>514300</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H184" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>7.552</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>7.707</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M159"/>
+  <autoFilter ref="A1:M184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
+++ b/docs/downloads/2026-10-26/bursa-report-2026-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-26" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-26'!$A$1:$M$200</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
   </fonts>
   <fills count="4">
@@ -98,7 +98,7 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M184"/>
+  <dimension ref="A1:M200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.08109999999999999</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2908500</v>
+        <v>3104400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>68.59</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 68.59接近超买区，现价高于50日均线约23%，信号偏强但需留意RSI高位。</t>
+          <t>SAR转多信号，RSI 68.59接近超买区，现价高于50日均线约23%，技术面偏强但需留意RSI高位。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.735</v>
+        <v>0.74</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0571</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1495200</v>
+        <v>1584000</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>2.57</v>
+        <v>2.72</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>79.54000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>RSI 79.54 已超买，现价高于50日均线约19.5%，SAR转多信号可靠性偏弱。</t>
+          <t>RSI 80.1 已超买，现价高于50日均线约20%，SAR转多信号可靠性受限。</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.065</v>
+        <v>0.075</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-0.1333</v>
+        <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>105412400</v>
+        <v>135774400</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.29</v>
+        <v>0.37</v>
       </c>
       <c r="H4" t="n">
-        <v>31.79</v>
+        <v>33.53</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>0.259</v>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.19</v>
+        <v>0.195</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.3571</v>
+        <v>0.3929</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>70399600</v>
+        <v>75119600</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>76.16</v>
+        <v>81.27</v>
       </c>
       <c r="H5" t="n">
-        <v>86.39</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>0.12</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>-0.0306</v>
+        <v>0.48</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>51404400</v>
+        <v>52582200</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="H6" t="n">
-        <v>72.55</v>
+        <v>74.59</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -809,14 +809,14 @@
       <c r="D7" s="9" t="n">
         <v>0.155</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="16" t="n">
         <v>-0.06059999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>41289500</v>
+        <v>41837400</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H7" t="n">
         <v>48.93</v>
@@ -854,14 +854,14 @@
       <c r="D8" s="9" t="n">
         <v>0.055</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>36327700</v>
+        <v>38137700</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>4.43</v>
+        <v>4.65</v>
       </c>
       <c r="H8" t="n">
         <v>58.63</v>
@@ -888,28 +888,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.0217</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>26231400</v>
+        <v>28250900</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>10.77</v>
+        <v>0.38</v>
       </c>
       <c r="H9" t="n">
-        <v>78.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.078</v>
+        <v>0.861</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.076</v>
+        <v>0.763</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -944,14 +944,14 @@
       <c r="D10" s="9" t="n">
         <v>0.155</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="16" t="n">
         <v>-0.0313</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>24179100</v>
+        <v>27234500</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="H10" t="n">
         <v>47.73</v>
@@ -978,28 +978,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0069</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VINVEST</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.035</v>
+        <v>0.09</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0.1667</v>
+        <v>0.0588</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>20774100</v>
+        <v>27141000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>7.97</v>
+        <v>11.14</v>
       </c>
       <c r="H11" t="n">
-        <v>74.81</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.019</v>
+        <v>0.078</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.018</v>
+        <v>0.076</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1023,28 +1023,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0069</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>VINVEST</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.93</v>
+        <v>0.035</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.1667</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>18351300</v>
+        <v>23113200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.25</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>66.02</v>
+        <v>74.81</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.86</v>
+        <v>0.019</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.763</v>
+        <v>0.018</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.045</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.1818</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>18002600</v>
+        <v>20166000</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="H13" t="n">
-        <v>34.17</v>
+        <v>30.77</v>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
@@ -1113,28 +1113,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.305</v>
+        <v>4.84</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0</v>
+        <v>-0.0902</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>15831500</v>
+        <v>19935900</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.82</v>
+        <v>1.5</v>
       </c>
       <c r="H14" t="n">
-        <v>47.42</v>
+        <v>30.25</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.307</v>
+        <v>5.386</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.302</v>
+        <v>5.507</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1167,19 +1167,19 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.74</v>
+        <v>0.735</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0</v>
+        <v>-0.0068</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>15818300</v>
+        <v>19075700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H15" t="n">
-        <v>83.92</v>
+        <v>81.37</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.66</v>
+        <v>0.659</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0.5620000000000001</v>
@@ -1203,28 +1203,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>-0.0733</v>
+        <v>0.47</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.033</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>14679100</v>
+        <v>17512300</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1.11</v>
+        <v>0.87</v>
       </c>
       <c r="H16" t="n">
-        <v>32.11</v>
+        <v>62.83</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>5.395</v>
+        <v>0.433</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>5.508</v>
+        <v>0.385</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1259,14 +1259,14 @@
       <c r="D17" s="9" t="n">
         <v>0.82</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>14476000</v>
+        <v>16356900</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="H17" t="n">
         <v>54.27</v>
@@ -1293,28 +1293,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.305</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>13821500</v>
+        <v>15932500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.43</v>
+        <v>0.82</v>
       </c>
       <c r="H18" t="n">
-        <v>31.76</v>
+        <v>47.42</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.39</v>
+        <v>0.307</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.403</v>
+        <v>0.302</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1338,40 +1338,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.022</v>
+        <v>0.18</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>-0.0526</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>13708700</v>
+        <v>15578200</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H19" t="n">
-        <v>61.85</v>
+        <v>0.45</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J19" s="9" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>0.385</v>
-      </c>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
     </row>
@@ -1383,28 +1376,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>-0.0185</v>
+        <v>1.95</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>-0.058</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>12415700</v>
+        <v>14878800</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="H20" t="n">
-        <v>41.24</v>
+        <v>30.49</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -1412,10 +1405,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.286</v>
+        <v>2.102</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.279</v>
+        <v>2.229</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1439,14 +1432,14 @@
       <c r="D21" s="9" t="n">
         <v>0.865</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="16" t="n">
         <v>-0.005699999999999999</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>12326500</v>
+        <v>14264600</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H21" t="n">
         <v>46.13</v>
@@ -1473,28 +1466,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>-0.05309999999999999</v>
+        <v>0.38</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>12234000</v>
+        <v>13867300</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="H22" t="n">
-        <v>31.14</v>
+        <v>31.76</v>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
@@ -1502,10 +1495,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>2.103</v>
+        <v>0.39</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2.23</v>
+        <v>0.403</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1529,14 +1522,14 @@
       <c r="D23" s="9" t="n">
         <v>0.775</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>11455300</v>
+        <v>12984300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="H23" t="n">
         <v>50.44</v>
@@ -1563,28 +1556,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E24" s="16" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>11002900</v>
+        <v>12783400</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.13</v>
+        <v>1.2</v>
       </c>
       <c r="H24" t="n">
-        <v>60.52</v>
+        <v>42.93</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
@@ -1592,10 +1585,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.316</v>
+        <v>0.286</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.266</v>
+        <v>0.279</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1608,28 +1601,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.33</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>10662300</v>
+        <v>11647700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>2.08</v>
+        <v>0.14</v>
       </c>
       <c r="H25" t="n">
-        <v>56.73</v>
+        <v>60.52</v>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
@@ -1637,10 +1630,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.267</v>
+        <v>0.316</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.27</v>
+        <v>0.266</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1653,33 +1646,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>-0.0263</v>
+        <v>0.415</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9487100</v>
+        <v>11310900</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
+        <v>0.96</v>
+      </c>
+      <c r="H26" t="n">
+        <v>56.17</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.383</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
     </row>
@@ -1691,36 +1691,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.0217</v>
+        <v>0.27</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>9206700</v>
+        <v>11059800</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.45</v>
+        <v>2.16</v>
       </c>
       <c r="H27" t="n">
-        <v>51.42</v>
+        <v>56.73</v>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
+      <c r="J27" s="9" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.27</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
     </row>
@@ -1732,33 +1736,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>-0.0493</v>
+        <v>4.7</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>8912700</v>
+        <v>10769100</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
+        <v>0.49</v>
+      </c>
+      <c r="H28" t="n">
+        <v>46.16</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>4.726</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>4.811</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1770,40 +1781,36 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.41</v>
+        <v>0.225</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>0</v>
+        <v>-0.0217</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8780600</v>
+        <v>9753200</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.74</v>
+        <v>0.47</v>
       </c>
       <c r="H29" t="n">
-        <v>54.71</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>0.383</v>
-      </c>
+        <v>51.42</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
     </row>
@@ -1815,39 +1822,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.005</v>
+        <v>0.37</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>0</v>
+        <v>-0.0133</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>8270000</v>
+        <v>9650700</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>9.050000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="H30" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>27.15</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.005</v>
+        <v>0.468</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.006</v>
+        <v>0.583</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1860,40 +1867,33 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.0343</v>
+        <v>0.675</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>-0.0493</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7279000</v>
+        <v>9351800</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H31" t="n">
-        <v>48.12</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>0.897</v>
-      </c>
-      <c r="K31" s="9" t="n">
-        <v>0.958</v>
-      </c>
+        <v>0.27</v>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
     </row>
@@ -1905,39 +1905,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.715</v>
+        <v>0.635</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>-0.0272</v>
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>7162300</v>
+        <v>8306400</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="H32" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.81</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.734</v>
+        <v>0.624</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.724</v>
+        <v>0.618</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1950,39 +1950,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>0.029</v>
+        <v>0.005</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7067800</v>
+        <v>8270000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.15</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>70.38</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.969</v>
+        <v>0.005</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.961</v>
+        <v>0.006</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1995,39 +1995,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.635</v>
+        <v>0.715</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>0</v>
+        <v>-0.0272</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>6956700</v>
+        <v>8133700</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H34" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.06</v>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.624</v>
+        <v>0.734</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.618</v>
+        <v>0.724</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2040,39 +2040,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.9350000000000001</v>
+        <v>2.12</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>0.0331</v>
+        <v>0.0242</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>6713100</v>
+        <v>7979200</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.64</v>
+        <v>1.3</v>
       </c>
       <c r="H35" t="n">
-        <v>40.62</v>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.69</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>1.005</v>
+        <v>1.968</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.981</v>
+        <v>1.961</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2085,28 +2085,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.93</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0276</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6685900</v>
+        <v>7900700</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="H36" t="n">
-        <v>39.02</v>
+        <v>39.86</v>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.423</v>
+        <v>1.005</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.439</v>
+        <v>0.981</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2130,28 +2130,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>-0.0105</v>
+        <v>0.91</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.04</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>6615400</v>
+        <v>7572900</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.3</v>
+        <v>2.03</v>
       </c>
       <c r="H37" t="n">
-        <v>46.16</v>
+        <v>49.54</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>4.726</v>
+        <v>0.898</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>4.811</v>
+        <v>0.958</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2175,39 +2175,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>0.0133</v>
+        <v>1.14</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>6391900</v>
+        <v>6903300</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.59</v>
+        <v>0.9</v>
       </c>
       <c r="H38" t="n">
-        <v>28.85</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.43</v>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.469</v>
+        <v>1.203</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.583</v>
+        <v>1.29</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2220,28 +2220,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.0263</v>
+        <v>2.5</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>6257600</v>
+        <v>6762600</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H39" t="n">
-        <v>37.92</v>
+        <v>43.98</v>
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.209</v>
+        <v>2.594</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.229</v>
+        <v>2.56</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2265,28 +2265,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0163</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>CAREPLS</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>0.0101</v>
+        <v>0.08</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5896500</v>
+        <v>6747100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.21</v>
+        <v>1.35</v>
       </c>
       <c r="H40" t="n">
-        <v>55.8</v>
+        <v>48.65</v>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>1.967</v>
+        <v>0.081</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1.795</v>
+        <v>0.08</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2310,39 +2310,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.0476</v>
+        <v>0.385</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>-0.04940000000000001</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5883400</v>
+        <v>6732800</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>1.32</v>
+        <v>0.88</v>
       </c>
       <c r="H41" t="n">
-        <v>66.55</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.96</v>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.099</v>
+        <v>0.423</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.439</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2355,28 +2355,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>-0.008</v>
+        <v>2.02</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0.0151</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5867500</v>
+        <v>6542500</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H42" t="n">
-        <v>43.45</v>
+        <v>56.35</v>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.593</v>
+        <v>1.968</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.559</v>
+        <v>1.795</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2400,28 +2400,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.195</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>5866800</v>
+        <v>6541100</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.77</v>
+        <v>0.35</v>
       </c>
       <c r="H43" t="n">
-        <v>32.43</v>
+        <v>37.92</v>
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.203</v>
+        <v>0.209</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.29</v>
+        <v>0.229</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
         <v>0.0292</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5640700</v>
+        <v>6218100</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="H44" t="n">
         <v>27.3</v>
@@ -2490,28 +2490,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.5</v>
+        <v>0.525</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>0.0309</v>
+        <v>0.0294</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5600300</v>
+        <v>6179200</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>2.41</v>
+        <v>1.83</v>
       </c>
       <c r="H45" t="n">
-        <v>54.66</v>
+        <v>81.64</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.49</v>
+        <v>0.451</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.485</v>
+        <v>0.437</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2535,28 +2535,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>-0.0235</v>
+        <v>2.65</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5543100</v>
+        <v>6087900</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="H46" t="n">
-        <v>36.3</v>
+        <v>42.85</v>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.455</v>
+        <v>2.731</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.474</v>
+        <v>2.746</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2580,28 +2580,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>-0.0133</v>
+        <v>0.11</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5474800</v>
+        <v>6083400</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.8</v>
+        <v>1.36</v>
       </c>
       <c r="H47" t="n">
-        <v>48.14</v>
+        <v>66.55</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.372</v>
+        <v>0.099</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.37</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2625,39 +2625,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0.0196</v>
+        <v>0.455</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5191800</v>
+        <v>6083300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1.54</v>
+        <v>3.06</v>
       </c>
       <c r="H48" t="n">
-        <v>80.93000000000001</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.42</v>
+      </c>
+      <c r="I48" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.451</v>
+        <v>0.461</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.437</v>
+        <v>0.462</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2670,31 +2670,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0.0309</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5141100</v>
-      </c>
-      <c r="G49" s="12" t="n"/>
-      <c r="I49" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="n"/>
-      <c r="K49" s="9" t="n"/>
+        <v>5926000</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H49" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.485</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
     </row>
@@ -2706,28 +2715,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>-0.0187</v>
+        <v>4.81</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>5069600</v>
+        <v>5776200</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.48</v>
+        <v>0.24</v>
       </c>
       <c r="H50" t="n">
-        <v>41.52</v>
+        <v>47.19</v>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
@@ -2735,10 +2744,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>2.729</v>
+        <v>4.869</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.746</v>
+        <v>4.763</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2751,28 +2760,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>0.0268</v>
+        <v>0.42</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4861200</v>
+        <v>5748600</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.79</v>
+        <v>0.16</v>
       </c>
       <c r="H51" t="n">
-        <v>24.18</v>
+        <v>37.37</v>
       </c>
       <c r="I51" s="17" t="inlineStr">
         <is>
@@ -2780,10 +2789,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.301</v>
+        <v>0.455</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.502</v>
+        <v>0.475</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2796,28 +2805,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0</v>
+        <v>0.83</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4586100</v>
+        <v>5627900</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="H52" t="n">
-        <v>89.08</v>
+        <v>70.69</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2825,10 +2834,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>3.045</v>
+        <v>0.806</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2.578</v>
+        <v>0.779</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2841,28 +2850,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>0.0061</v>
+        <v>0.375</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4554700</v>
+        <v>5584800</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="H53" t="n">
-        <v>70.69</v>
+        <v>54.17</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2870,10 +2879,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.806</v>
+        <v>0.373</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.779</v>
+        <v>0.37</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2886,28 +2895,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.08699999999999999</v>
+        <v>1.15</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0268</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4534300</v>
+        <v>5201200</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.25</v>
+        <v>0.84</v>
       </c>
       <c r="H54" t="n">
-        <v>30.51</v>
+        <v>24.18</v>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
@@ -2915,10 +2924,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.131</v>
+        <v>1.301</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.146</v>
+        <v>1.502</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2931,40 +2940,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.0185</v>
+        <v>0.005</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4288500</v>
-      </c>
-      <c r="G55" s="12" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H55" t="n">
-        <v>52.12</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J55" s="9" t="n">
-        <v>1.626</v>
-      </c>
-      <c r="K55" s="9" t="n">
-        <v>1.676</v>
-      </c>
+        <v>5141100</v>
+      </c>
+      <c r="G55" s="12" t="n"/>
+      <c r="I55" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n"/>
+      <c r="K55" s="9" t="n"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
     </row>
@@ -2976,28 +2976,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>2.14</v>
+        <v>1.17</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>0.019</v>
+        <v>0.0174</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4214700</v>
+        <v>5134400</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>2.02</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>55.64</v>
+        <v>61.13</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3005,10 +3005,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>2.114</v>
+        <v>1.095</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2.078</v>
+        <v>1.057</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3021,28 +3021,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.16</v>
+        <v>2.15</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0238</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4182200</v>
+        <v>5006200</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.45</v>
+        <v>2.39</v>
       </c>
       <c r="H57" t="n">
-        <v>60.13</v>
+        <v>56.91</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.094</v>
+        <v>2.115</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1.056</v>
+        <v>2.078</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3066,39 +3066,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E58" s="16" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4180700</v>
+        <v>4908100</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>1.19</v>
+        <v>3.49</v>
       </c>
       <c r="H58" t="n">
-        <v>63.67</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.46</v>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.61</v>
+        <v>0.723</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3111,39 +3111,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>0</v>
+        <v>4.24</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0.06</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>4143400</v>
+        <v>4791800</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>1.22</v>
+        <v>0.51</v>
       </c>
       <c r="H59" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.39</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.295</v>
+        <v>3.986</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.295</v>
+        <v>3.645</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3156,28 +3156,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>-0.0299</v>
+        <v>0.11</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>4125100</v>
+        <v>4648500</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.51</v>
+        <v>0.25</v>
       </c>
       <c r="H60" t="n">
-        <v>41.45</v>
+        <v>32.48</v>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.348</v>
+        <v>0.131</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.33</v>
+        <v>0.146</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3201,39 +3201,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E61" s="16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E61" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>4104700</v>
+        <v>4625600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>2.91</v>
+        <v>1.48</v>
       </c>
       <c r="H61" t="n">
-        <v>55.46</v>
-      </c>
-      <c r="I61" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.08</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.75</v>
+        <v>3.045</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.723</v>
+        <v>2.578</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3246,39 +3246,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>-0.0552</v>
+        <v>1.65</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>4027700</v>
+        <v>4499500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.85</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="I62" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.12</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.819</v>
+        <v>1.626</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.627</v>
+        <v>1.676</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3291,39 +3291,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>0.0145</v>
+        <v>0.325</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>4022300</v>
+        <v>4382800</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="H63" t="n">
-        <v>65.56</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.45</v>
+      </c>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>3.801</v>
+        <v>0.348</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>3.249</v>
+        <v>0.33</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3336,39 +3336,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>0.06</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>-0.0483</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3769700</v>
+        <v>4341400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.4</v>
+        <v>0.91</v>
       </c>
       <c r="H64" t="n">
-        <v>61.39</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.98</v>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>3.986</v>
+        <v>0.82</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>3.645</v>
+        <v>0.627</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3381,39 +3381,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.17</v>
+        <v>4.2</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>0.0303</v>
+        <v>0.0169</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3544500</v>
+        <v>4220200</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="I65" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.76000000000001</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.166</v>
+        <v>3.802</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.156</v>
+        <v>3.249</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3426,28 +3426,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>0.0682</v>
+        <v>4.47</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3515000</v>
+        <v>4200400</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>2.06</v>
+        <v>0.47</v>
       </c>
       <c r="H66" t="n">
-        <v>53.26</v>
+        <v>38.17</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.369</v>
+        <v>4.56</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.44</v>
+        <v>4.641</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3471,39 +3471,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.26</v>
+        <v>0.625</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>-0.0189</v>
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3437400</v>
+        <v>4180700</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.49</v>
+        <v>1.19</v>
       </c>
       <c r="H67" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="I67" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.67</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.282</v>
+        <v>0.62</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.282</v>
+        <v>0.61</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3516,28 +3516,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>0.0116</v>
+        <v>0.29</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3350500</v>
+        <v>4153400</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.2</v>
+        <v>1.23</v>
       </c>
       <c r="H68" t="n">
-        <v>27.55</v>
+        <v>23.03</v>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.479</v>
+        <v>0.295</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.619</v>
+        <v>0.295</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3561,28 +3561,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>0.0278</v>
+        <v>7.1</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3290200</v>
+        <v>4007400</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="H69" t="n">
-        <v>48.66</v>
+        <v>31.47</v>
       </c>
       <c r="I69" s="17" t="inlineStr">
         <is>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.186</v>
+        <v>7.359</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.186</v>
+        <v>7.625</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>-0.0103</v>
+        <v>1.4</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.06059999999999999</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3278500</v>
+        <v>3890200</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.14</v>
+        <v>2.28</v>
       </c>
       <c r="H70" t="n">
-        <v>46.64</v>
-      </c>
-      <c r="I70" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.97</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>4.868</v>
+        <v>1.368</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>4.763</v>
+        <v>1.44</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3651,28 +3651,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>0</v>
+        <v>2.61</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.1154</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3126600</v>
+        <v>3764000</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>1.57</v>
+        <v>0.67</v>
       </c>
       <c r="H71" t="n">
-        <v>47.46</v>
+        <v>46.46</v>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.462</v>
+        <v>2.651</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.462</v>
+        <v>2.832</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3696,39 +3696,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PCCS</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.305</v>
+        <v>0.185</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.0278</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3043100</v>
+        <v>3692100</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>24.13</v>
+        <v>0.18</v>
       </c>
       <c r="H72" t="n">
-        <v>70.92</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.66</v>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.284</v>
+        <v>0.186</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.282</v>
+        <v>0.186</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3752,14 +3752,14 @@
       <c r="D73" s="9" t="n">
         <v>5.73</v>
       </c>
-      <c r="E73" s="10" t="n">
+      <c r="E73" s="16" t="n">
         <v>-0.0035</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2981500</v>
+        <v>3674400</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="H73" t="n">
         <v>39.34</v>
@@ -3786,39 +3786,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>0.0169</v>
+        <v>0.43</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2970700</v>
+        <v>3668000</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.45</v>
+        <v>0.22</v>
       </c>
       <c r="H74" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.46</v>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.315</v>
+        <v>0.479</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.359</v>
+        <v>0.618</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3831,28 +3831,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.175</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0.06059999999999999</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2967700</v>
+        <v>3546500</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.18</v>
+        <v>1.59</v>
       </c>
       <c r="H75" t="n">
-        <v>31.13</v>
+        <v>58.57</v>
       </c>
       <c r="I75" s="17" t="inlineStr">
         <is>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>7.359</v>
+        <v>0.167</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>7.624</v>
+        <v>0.156</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3876,28 +3876,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.26</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2880000</v>
+        <v>3460000</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.97</v>
+        <v>0.49</v>
       </c>
       <c r="H76" t="n">
-        <v>50.44</v>
+        <v>39.48</v>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.866</v>
+        <v>0.282</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.861</v>
+        <v>0.282</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3921,39 +3921,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>-0.0217</v>
+        <v>0.85</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0429</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2878500</v>
+        <v>3255400</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>2.06</v>
+        <v>0.53</v>
       </c>
       <c r="H77" t="n">
-        <v>43.32</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.12</v>
+      </c>
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.23</v>
+        <v>0.887</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.237</v>
+        <v>0.859</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         <v>0.0194</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2827700</v>
+        <v>3156100</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="H78" t="n">
         <v>38.17</v>
@@ -4011,28 +4011,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E79" s="16" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2785000</v>
+        <v>3087400</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.42</v>
+        <v>0.4</v>
       </c>
       <c r="H79" t="n">
-        <v>45.18</v>
+        <v>48.77</v>
       </c>
       <c r="I79" s="17" t="inlineStr">
         <is>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.768</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.771</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4056,39 +4056,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>PCCS</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>-0.0066</v>
+        <v>0.31</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2752700</v>
+        <v>3051300</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.36</v>
+        <v>24.2</v>
       </c>
       <c r="H80" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.39</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.767</v>
+        <v>0.285</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.771</v>
+        <v>0.282</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         <v>0.0049</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2645700</v>
+        <v>3043100</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.66</v>
+        <v>0.76</v>
       </c>
       <c r="H81" t="n">
         <v>48.91</v>
@@ -4146,28 +4146,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.975</v>
+        <v>0.3</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>0.0104</v>
+        <v>0.0169</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2615300</v>
+        <v>3036200</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="H82" t="n">
-        <v>65.22</v>
+        <v>38.96</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.315</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.892</v>
+        <v>0.359</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4191,28 +4191,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>0.0245</v>
+        <v>6.3</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2469700</v>
+        <v>2899200</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H83" t="n">
-        <v>43.04</v>
+        <v>44.57</v>
       </c>
       <c r="I83" s="17" t="inlineStr">
         <is>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.885</v>
+        <v>6.343</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.859</v>
+        <v>6.647</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4236,39 +4236,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>-0.0042</v>
+        <v>0.225</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2455900</v>
+        <v>2888500</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.22</v>
+        <v>2.06</v>
       </c>
       <c r="H84" t="n">
-        <v>42.66</v>
-      </c>
-      <c r="I84" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.32</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>2.433</v>
+        <v>0.23</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>2.412</v>
+        <v>0.237</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4281,28 +4281,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.865</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2431000</v>
+        <v>2880000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.34</v>
+        <v>0.97</v>
       </c>
       <c r="H85" t="n">
-        <v>44.57</v>
+        <v>50.44</v>
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>6.343</v>
+        <v>0.866</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>6.647</v>
+        <v>0.861</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4326,28 +4326,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.865</v>
+        <v>6.79</v>
       </c>
       <c r="E86" s="15" t="n">
-        <v>0.0298</v>
+        <v>0.0089</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2422800</v>
+        <v>2869100</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.63</v>
+        <v>0.26</v>
       </c>
       <c r="H86" t="n">
-        <v>58.16</v>
+        <v>37.48</v>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.83</v>
+        <v>7.053</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.799</v>
+        <v>7.494</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4371,28 +4371,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0.0472</v>
+        <v>0.555</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2380600</v>
+        <v>2785000</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.64</v>
+        <v>1.42</v>
       </c>
       <c r="H87" t="n">
-        <v>53.95</v>
+        <v>45.18</v>
       </c>
       <c r="I87" s="17" t="inlineStr">
         <is>
@@ -4400,10 +4400,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.927</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4416,39 +4416,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.555</v>
+        <v>0.965</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>-0.0089</v>
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2324300</v>
+        <v>2732300</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.11</v>
+        <v>0.57</v>
       </c>
       <c r="H88" t="n">
-        <v>48.36</v>
-      </c>
-      <c r="I88" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.7</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.546</v>
+        <v>0.892</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4461,38 +4461,40 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>0.0282</v>
+        <v>2.38</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2284200</v>
+        <v>2724500</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="H89" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.66</v>
+      </c>
+      <c r="I89" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="K89" s="9" t="n"/>
+        <v>2.433</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>2.412</v>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
     </row>
@@ -4504,28 +4506,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>-0.0039</v>
+        <v>0.555</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>-0.0089</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2150800</v>
+        <v>2668800</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="H90" t="n">
-        <v>45.76</v>
+        <v>48.36</v>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
@@ -4533,10 +4535,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>2.594</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>2.604</v>
+        <v>0.546</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4549,28 +4551,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.895</v>
+        <v>1.08</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.0189</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2118500</v>
+        <v>2660000</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>1.22</v>
+        <v>0.71</v>
       </c>
       <c r="H91" t="n">
-        <v>48.61</v>
+        <v>51.03</v>
       </c>
       <c r="I91" s="17" t="inlineStr">
         <is>
@@ -4578,10 +4580,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.905</v>
+        <v>1.097</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.892</v>
+        <v>0.927</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4594,28 +4596,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.755</v>
+        <v>1.22</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>0.0342</v>
+        <v>0.0252</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2095600</v>
+        <v>2651100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="H92" t="n">
-        <v>54.07</v>
+        <v>57.42</v>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
@@ -4623,10 +4625,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.74</v>
+        <v>1.178</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4639,40 +4641,38 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>2.47</v>
+        <v>0.36</v>
       </c>
       <c r="E93" s="15" t="n">
-        <v>0.0556</v>
+        <v>0.0141</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2027700</v>
+        <v>2605500</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="H93" t="n">
-        <v>40.03</v>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.89</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.637</v>
-      </c>
-      <c r="K93" s="9" t="n">
-        <v>2.829</v>
-      </c>
+        <v>0.336</v>
+      </c>
+      <c r="K93" s="9" t="n"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
     </row>
@@ -4684,28 +4684,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.2</v>
+        <v>0.865</v>
       </c>
       <c r="E94" s="15" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0298</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2016700</v>
+        <v>2470700</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.31</v>
+        <v>0.65</v>
       </c>
       <c r="H94" t="n">
-        <v>54.86</v>
+        <v>58.16</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.176</v>
+        <v>0.83</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.149</v>
+        <v>0.799</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4729,28 +4729,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.455</v>
+        <v>0.745</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>0.0225</v>
+        <v>0.0205</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1991900</v>
+        <v>2387600</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="H95" t="n">
-        <v>43.41</v>
+        <v>52.58</v>
       </c>
       <c r="I95" s="17" t="inlineStr">
         <is>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.492</v>
+        <v>0.739</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.469</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4774,28 +4774,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v>0.0165</v>
+        <v>2.55</v>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>-0.0039</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1880200</v>
+        <v>2255600</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="H96" t="n">
-        <v>35.18</v>
+        <v>45.76</v>
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.68</v>
+        <v>2.594</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.734</v>
+        <v>2.604</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4819,28 +4819,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>0.0072</v>
+        <v>0.545</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1853900</v>
+        <v>2252900</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H97" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="I97" s="17" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>2.788</v>
+        <v>0.608</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>2.69</v>
+        <v>0.616</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4864,28 +4864,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KEYFIELD</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>-0.0214</v>
+        <v>0.595</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0171</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1852000</v>
+        <v>2206600</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>9.34</v>
+        <v>0.27</v>
       </c>
       <c r="H98" t="n">
-        <v>46.47</v>
+        <v>37.87</v>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.387</v>
+        <v>0.647</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.372</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4909,28 +4909,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>-0.0092</v>
+        <v>0.6</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1851900</v>
+        <v>2161600</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>36.36</v>
+        <v>51.9</v>
       </c>
       <c r="I99" s="17" t="inlineStr">
         <is>
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.607</v>
+        <v>0.593</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.616</v>
+        <v>0.585</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4954,28 +4954,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>-0.0238</v>
+        <v>0.895</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1827700</v>
+        <v>2118500</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.17</v>
+        <v>1.22</v>
       </c>
       <c r="H100" t="n">
-        <v>30.88</v>
+        <v>48.61</v>
       </c>
       <c r="I100" s="17" t="inlineStr">
         <is>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.223</v>
+        <v>0.905</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.269</v>
+        <v>0.892</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4999,39 +4999,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>2.4</v>
+        <v>0.45</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>0.0042</v>
+        <v>0.0112</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1758600</v>
+        <v>2079400</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.51</v>
+        <v>0.22</v>
       </c>
       <c r="H101" t="n">
-        <v>61.67</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.42</v>
+      </c>
+      <c r="I101" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>2.287</v>
+        <v>0.492</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2.207</v>
+        <v>0.469</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5044,28 +5044,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>-0.0435</v>
+        <v>0.62</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>0.0248</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1743500</v>
+        <v>2056400</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H102" t="n">
-        <v>13.39</v>
+        <v>36.29</v>
       </c>
       <c r="I102" s="17" t="inlineStr">
         <is>
@@ -5073,9 +5073,11 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="K102" s="9" t="n"/>
+        <v>0.68</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>0.734</v>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
     </row>
@@ -5087,39 +5089,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.82</v>
+        <v>10</v>
       </c>
       <c r="E103" s="16" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1709500</v>
+        <v>2039400</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.6</v>
+        <v>0.16</v>
       </c>
       <c r="H103" t="n">
-        <v>30.27</v>
-      </c>
-      <c r="I103" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.61</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.868</v>
+        <v>9.997</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.931</v>
+        <v>10.112</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5132,39 +5134,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>6.87</v>
+        <v>0.82</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1705500</v>
+        <v>2033000</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.34</v>
+        <v>0.71</v>
       </c>
       <c r="H104" t="n">
-        <v>54.75</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.27</v>
+      </c>
+      <c r="I104" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>6.805</v>
+        <v>0.868</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>6.822</v>
+        <v>0.931</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5177,39 +5179,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.28</v>
+        <v>2.82</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>0.024</v>
+        <v>0.0144</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1695200</v>
+        <v>1974500</v>
       </c>
       <c r="G105" s="12" t="n">
         <v>0.24</v>
       </c>
       <c r="H105" t="n">
-        <v>59.18</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.1</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.228</v>
+        <v>2.79</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1.206</v>
+        <v>2.69</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5222,39 +5224,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E106" s="16" t="n">
-        <v>0</v>
+        <v>1.28</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0.024</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1694600</v>
+        <v>1958300</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H106" t="n">
-        <v>35.41</v>
-      </c>
-      <c r="I106" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.18</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.646</v>
+        <v>1.228</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.206</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5267,39 +5269,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0148</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SUNZEN</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.23</v>
+        <v>7.35</v>
       </c>
       <c r="E107" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1683800</v>
+        <v>1951800</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>3.9</v>
+        <v>0.17</v>
       </c>
       <c r="H107" t="n">
-        <v>61.36</v>
-      </c>
-      <c r="I107" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.06</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.225</v>
+        <v>7.412</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.224</v>
+        <v>7.819</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5312,28 +5314,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>9.99</v>
+        <v>0.435</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1655100</v>
+        <v>1931200</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="H108" t="n">
-        <v>48</v>
+        <v>52.42</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5341,10 +5343,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>9.996</v>
+        <v>0.429</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>10.112</v>
+        <v>0.418</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5357,39 +5359,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>0.0455</v>
+        <v>0.205</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1587000</v>
+        <v>1911400</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>1.61</v>
+        <v>0.18</v>
       </c>
       <c r="H109" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.88</v>
+      </c>
+      <c r="I109" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
         <v>0.223</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.23</v>
+        <v>0.269</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5402,28 +5404,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>7.35</v>
+        <v>2.41</v>
       </c>
       <c r="E110" s="15" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1582200</v>
+        <v>1886400</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.14</v>
+        <v>0.55</v>
       </c>
       <c r="H110" t="n">
-        <v>42.06</v>
+        <v>62.27</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5431,10 +5433,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>7.412</v>
+        <v>2.288</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>7.819</v>
+        <v>2.207</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5447,39 +5449,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E111" s="15" t="n">
-        <v>0.0104</v>
+        <v>6.85</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>-0.0144</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1575600</v>
+        <v>1855800</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.14</v>
+        <v>0.37</v>
       </c>
       <c r="H111" t="n">
-        <v>37.88</v>
-      </c>
-      <c r="I111" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.49</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>7.054</v>
+        <v>6.803</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>7.495</v>
+        <v>6.821</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5492,39 +5494,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>KEYFIELD</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>-0.0115</v>
+        <v>1.37</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>-0.0214</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1561700</v>
+        <v>1852000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.23</v>
+        <v>9.34</v>
       </c>
       <c r="H112" t="n">
-        <v>51.18</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.47</v>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.429</v>
+        <v>1.387</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.418</v>
+        <v>1.372</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5537,28 +5539,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MAGMA</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>-0.0042</v>
+        <v>0.27</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>0.0189</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1514800</v>
+        <v>1851200</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.37</v>
+        <v>2</v>
       </c>
       <c r="H113" t="n">
-        <v>33.15</v>
+        <v>39.46</v>
       </c>
       <c r="I113" s="17" t="inlineStr">
         <is>
@@ -5566,10 +5568,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>2.48</v>
+        <v>0.276</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>2.645</v>
+        <v>0.284</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5582,39 +5584,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>YNHPROP</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>0.0526</v>
+        <v>2.37</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1511100</v>
+        <v>1811200</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>4.07</v>
+        <v>0.44</v>
       </c>
       <c r="H114" t="n">
-        <v>51.46</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.15</v>
+      </c>
+      <c r="I114" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.294</v>
+        <v>2.48</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.31</v>
+        <v>2.645</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5627,28 +5629,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>-0.02</v>
+        <v>0.225</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1474800</v>
+        <v>1769900</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.41</v>
+        <v>0.67</v>
       </c>
       <c r="H115" t="n">
-        <v>44.11</v>
+        <v>14</v>
       </c>
       <c r="I115" s="17" t="inlineStr">
         <is>
@@ -5656,11 +5658,9 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>1.023</v>
-      </c>
-      <c r="K115" s="9" t="n">
-        <v>0.973</v>
-      </c>
+        <v>0.257</v>
+      </c>
+      <c r="K115" s="9" t="n"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
     </row>
@@ -5672,28 +5672,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>-0.0233</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>0.0566</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1439300</v>
+        <v>1768800</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.82</v>
+        <v>0.34</v>
       </c>
       <c r="H116" t="n">
-        <v>38.84</v>
+        <v>53.13</v>
       </c>
       <c r="I116" s="17" t="inlineStr">
         <is>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.445</v>
+        <v>0.551</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.457</v>
+        <v>0.526</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5717,39 +5717,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E117" s="16" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E117" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1416800</v>
+        <v>1753300</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="H117" t="n">
-        <v>52.96</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.62</v>
+      </c>
+      <c r="I117" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.336</v>
+        <v>0.296</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.343</v>
+        <v>0.323</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5762,39 +5762,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>EMETALL</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.445</v>
+        <v>1.46</v>
       </c>
       <c r="E118" s="16" t="n">
-        <v>0</v>
+        <v>-0.0068</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1391500</v>
+        <v>1703200</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>1.21</v>
+        <v>1.68</v>
       </c>
       <c r="H118" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.02</v>
+      </c>
+      <c r="I118" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.441</v>
+        <v>1.562</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.44</v>
+        <v>1.623</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5807,28 +5807,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0148</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>SUNZEN</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1374300</v>
+        <v>1683800</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>1.08</v>
+        <v>3.9</v>
       </c>
       <c r="H119" t="n">
-        <v>38.36</v>
+        <v>61.36</v>
       </c>
       <c r="I119" s="17" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.315</v>
+        <v>0.225</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.328</v>
+        <v>0.224</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5861,19 +5861,19 @@
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="E120" s="15" t="n">
-        <v>0.0567</v>
+        <v>0.0496</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1364000</v>
+        <v>1617700</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="H120" t="n">
-        <v>61.58</v>
+        <v>60.89</v>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>2.822</v>
+        <v>2.821</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>2.348</v>
@@ -5897,39 +5897,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.955</v>
+        <v>0.225</v>
       </c>
       <c r="E121" s="15" t="n">
-        <v>0.0437</v>
+        <v>0.0227</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1354800</v>
+        <v>1609400</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="H121" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="I121" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.21</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.927</v>
+        <v>0.223</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.011</v>
+        <v>0.23</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5942,39 +5942,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>YNHPROP</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>-0.0204</v>
+        <v>0.3</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>0.0526</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1303400</v>
+        <v>1601100</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>1.28</v>
+        <v>4.31</v>
       </c>
       <c r="H122" t="n">
-        <v>29.26</v>
-      </c>
-      <c r="I122" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.46</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.56</v>
+        <v>0.294</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.623</v>
+        <v>0.31</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5987,28 +5987,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="E123" s="16" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1298500</v>
+        <v>1523300</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="H123" t="n">
-        <v>40.12</v>
+        <v>45.58</v>
       </c>
       <c r="I123" s="17" t="inlineStr">
         <is>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>1.123</v>
+        <v>1.024</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>1.112</v>
+        <v>0.974</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6032,28 +6032,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>-0.011</v>
+        <v>0.945</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0.0328</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1296600</v>
+        <v>1522400</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.36</v>
+        <v>1.48</v>
       </c>
       <c r="H124" t="n">
-        <v>36.52</v>
+        <v>50.77</v>
       </c>
       <c r="I124" s="17" t="inlineStr">
         <is>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>2.832</v>
+        <v>0.926</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>2.97</v>
+        <v>1.011</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6077,39 +6077,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>0336</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>WINSTAR</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>-0.0108</v>
+        <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1267600</v>
+        <v>1516500</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.82</v>
       </c>
       <c r="H125" t="n">
-        <v>53.88</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.76</v>
+      </c>
+      <c r="I125" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.452</v>
+        <v>0.637</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.45</v>
+        <v>0.642</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6122,39 +6122,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>-0.0323</v>
+        <v>0.425</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>-0.0116</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1254000</v>
+        <v>1444400</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="H126" t="n">
-        <v>49.39</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.38</v>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.296</v>
+        <v>0.445</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.327</v>
+        <v>0.457</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6176,19 +6176,19 @@
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>-0.0174</v>
+        <v>1.12</v>
+      </c>
+      <c r="E127" s="16" t="n">
+        <v>-0.0261</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1249000</v>
+        <v>1433200</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H127" t="n">
-        <v>29.22</v>
+        <v>28.01</v>
       </c>
       <c r="I127" s="17" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>1.198</v>
+        <v>1.197</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>1.303</v>
@@ -6212,28 +6212,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>-0.0029</v>
+        <v>0.345</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1245300</v>
+        <v>1431900</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.96</v>
+        <v>0.31</v>
       </c>
       <c r="H128" t="n">
-        <v>52.31</v>
+        <v>57.71</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>3.379</v>
+        <v>0.337</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>3.243</v>
+        <v>0.343</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6257,28 +6257,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>TROP</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.235</v>
+        <v>1.18</v>
       </c>
       <c r="E129" s="15" t="n">
-        <v>0.0217</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1240100</v>
+        <v>1392400</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.68</v>
+        <v>1.43</v>
       </c>
       <c r="H129" t="n">
-        <v>38.25</v>
+        <v>48.96</v>
       </c>
       <c r="I129" s="17" t="inlineStr">
         <is>
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.246</v>
+        <v>1.183</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.268</v>
+        <v>1.187</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6302,39 +6302,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>EMETALL</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E130" s="15" t="n">
-        <v>0.0172</v>
+        <v>0.445</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1209200</v>
+        <v>1391500</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.25</v>
+        <v>1.21</v>
       </c>
       <c r="H130" t="n">
-        <v>62.88</v>
-      </c>
-      <c r="I130" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.98999999999999</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.541</v>
+        <v>0.441</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.485</v>
+        <v>0.44</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6347,28 +6347,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0336</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>WINSTAR</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E131" s="16" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E131" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1173100</v>
+        <v>1374300</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>2.96</v>
+        <v>1.08</v>
       </c>
       <c r="H131" t="n">
-        <v>33.76</v>
+        <v>38.36</v>
       </c>
       <c r="I131" s="17" t="inlineStr">
         <is>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.637</v>
+        <v>0.315</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.642</v>
+        <v>0.328</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6401,19 +6401,19 @@
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0.0286</v>
+        <v>0.7</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1165900</v>
+        <v>1372900</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H132" t="n">
-        <v>42.27</v>
+        <v>37.78</v>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6437,28 +6437,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0098</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AUMAS</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>-0.0274</v>
+        <v>0.695</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>-0.0071</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1148500</v>
+        <v>1371400</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.96</v>
+        <v>0.22</v>
       </c>
       <c r="H133" t="n">
-        <v>53.79</v>
+        <v>41.13</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.347</v>
+        <v>0.712</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.358</v>
+        <v>0.77</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6482,28 +6482,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.505</v>
+        <v>2.69</v>
       </c>
       <c r="E134" s="16" t="n">
-        <v>0</v>
+        <v>-0.011</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1111900</v>
+        <v>1349600</v>
       </c>
       <c r="G134" s="12" t="n">
         <v>0.38</v>
       </c>
       <c r="H134" t="n">
-        <v>29.83</v>
+        <v>36.52</v>
       </c>
       <c r="I134" s="17" t="inlineStr">
         <is>
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.529</v>
+        <v>2.832</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.97</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6536,19 +6536,19 @@
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>6.56</v>
+        <v>6.57</v>
       </c>
       <c r="E135" s="15" t="n">
-        <v>0.0077</v>
+        <v>0.0092</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1108700</v>
+        <v>1342500</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="H135" t="n">
-        <v>56.36</v>
+        <v>56.51</v>
       </c>
       <c r="I135" s="17" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>6.303</v>
+        <v>6.304</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>6</v>
@@ -6572,28 +6572,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TROP</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="E136" s="15" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1108100</v>
+        <v>1331800</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1.13</v>
+        <v>0.4</v>
       </c>
       <c r="H136" t="n">
-        <v>48.96</v>
+        <v>41.87</v>
       </c>
       <c r="I136" s="17" t="inlineStr">
         <is>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.183</v>
+        <v>1.124</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.187</v>
+        <v>1.112</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6617,39 +6617,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E137" s="16" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E137" s="15" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1094200</v>
+        <v>1321900</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.28</v>
+        <v>0.65</v>
       </c>
       <c r="H137" t="n">
-        <v>53.94</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.49</v>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.266</v>
+        <v>1.291</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.271</v>
+        <v>1.3</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6662,28 +6662,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>-0.02</v>
+        <v>1.23</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1089400</v>
+        <v>1301500</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H138" t="n">
-        <v>39.46</v>
+        <v>41.01</v>
       </c>
       <c r="I138" s="17" t="inlineStr">
         <is>
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.264</v>
+        <v>1.273</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.284</v>
+        <v>1.316</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6707,39 +6707,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.375</v>
+        <v>3.39</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>0</v>
+        <v>-0.0029</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1084700</v>
+        <v>1300700</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.61</v>
+        <v>1.01</v>
       </c>
       <c r="H139" t="n">
-        <v>39.94</v>
-      </c>
-      <c r="I139" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.31</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.387</v>
+        <v>3.379</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.39</v>
+        <v>3.243</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6752,28 +6752,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>-0.0189</v>
+        <v>0.585</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1082800</v>
+        <v>1295700</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H140" t="n">
-        <v>32.3</v>
+        <v>54.15</v>
       </c>
       <c r="I140" s="17" t="inlineStr">
         <is>
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.296</v>
+        <v>0.575</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.323</v>
+        <v>0.485</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6797,39 +6797,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E141" s="16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E141" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1080900</v>
+        <v>1291500</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="H141" t="n">
-        <v>52.13</v>
-      </c>
-      <c r="I141" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.94</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
         <v>1.266</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.186</v>
+        <v>1.271</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6842,12 +6842,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
@@ -6857,13 +6857,13 @@
         <v>0.0259</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1076200</v>
+        <v>1280000</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="H142" t="n">
-        <v>50.91</v>
+        <v>63.56</v>
       </c>
       <c r="I142" s="17" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.592</v>
+        <v>0.541</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.585</v>
+        <v>0.485</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.575</v>
+        <v>0.465</v>
       </c>
       <c r="E143" s="10" t="n">
-        <v>-0.0086</v>
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1054400</v>
+        <v>1277600</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="H143" t="n">
-        <v>52.78</v>
-      </c>
-      <c r="I143" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.97</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.574</v>
+        <v>0.452</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.485</v>
+        <v>0.45</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6932,39 +6932,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E144" s="10" t="n">
-        <v>-0.0161</v>
+        <v>0.3</v>
+      </c>
+      <c r="E144" s="16" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1025400</v>
+        <v>1271700</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.5</v>
+        <v>0.96</v>
       </c>
       <c r="H144" t="n">
-        <v>41.13</v>
-      </c>
-      <c r="I144" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.39</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>1.288</v>
+        <v>0.296</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>1.3</v>
+        <v>0.327</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6977,39 +6977,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E145" s="15" t="n">
-        <v>0.0645</v>
+        <v>0.375</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1025300</v>
+        <v>1271600</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>5.43</v>
+        <v>0.71</v>
       </c>
       <c r="H145" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="I145" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.94</v>
+      </c>
+      <c r="I145" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.306</v>
+        <v>0.387</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.295</v>
+        <v>0.39</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7022,28 +7022,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E146" s="15" t="n">
-        <v>0.0283</v>
+        <v>1.3</v>
+      </c>
+      <c r="E146" s="16" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1018000</v>
+        <v>1255500</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="H146" t="n">
-        <v>50.14</v>
+        <v>51.71</v>
       </c>
       <c r="I146" s="17" t="inlineStr">
         <is>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.549</v>
+        <v>1.288</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.525</v>
+        <v>1.242</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7067,28 +7067,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E147" s="16" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E147" s="15" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1006600</v>
+        <v>1240100</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.1</v>
+        <v>0.68</v>
       </c>
       <c r="H147" t="n">
-        <v>43.38</v>
+        <v>38.25</v>
       </c>
       <c r="I147" s="17" t="inlineStr">
         <is>
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.337</v>
+        <v>0.246</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.337</v>
+        <v>0.268</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7112,28 +7112,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.7</v>
+        <v>4.61</v>
       </c>
       <c r="E148" s="16" t="n">
-        <v>0</v>
+        <v>-0.0086</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1005400</v>
+        <v>1220600</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="H148" t="n">
-        <v>42.28</v>
+        <v>57.46</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7141,10 +7141,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.713</v>
+        <v>4.428</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.77</v>
+        <v>4.439</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7166,19 +7166,19 @@
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>990500</v>
+        <v>1210900</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="H149" t="n">
-        <v>53.67</v>
+        <v>54.58</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>1.245</v>
+        <v>1.246</v>
       </c>
       <c r="K149" s="9" t="n">
         <v>1.115</v>
@@ -7202,39 +7202,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E150" s="16" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E150" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>986100</v>
+        <v>1207600</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.49</v>
+        <v>0.12</v>
       </c>
       <c r="H150" t="n">
-        <v>56.09</v>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.38</v>
+      </c>
+      <c r="I150" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.367</v>
+        <v>0.337</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.346</v>
+        <v>0.337</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7247,28 +7247,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E151" s="10" t="n">
-        <v>-0.0299</v>
+        <v>0.645</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>983700</v>
+        <v>1204800</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="H151" t="n">
-        <v>51.71</v>
+        <v>40.37</v>
       </c>
       <c r="I151" s="17" t="inlineStr">
         <is>
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>1.288</v>
+        <v>0.715</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>1.242</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7292,39 +7292,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="E152" s="15" t="n">
-        <v>0.018</v>
+        <v>1.27</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>937100</v>
+        <v>1204200</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
       <c r="H152" t="n">
-        <v>51.47</v>
-      </c>
-      <c r="I152" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.13</v>
+      </c>
+      <c r="I152" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>5.058</v>
+        <v>1.266</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>5.037</v>
+        <v>1.186</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7337,28 +7337,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.705</v>
+        <v>0.505</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>933500</v>
+        <v>1179800</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.54</v>
+        <v>0.4</v>
       </c>
       <c r="H153" t="n">
-        <v>41.17</v>
+        <v>29.83</v>
       </c>
       <c r="I153" s="17" t="inlineStr">
         <is>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.721</v>
+        <v>0.529</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.739</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7382,28 +7382,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.745</v>
+        <v>3.77</v>
       </c>
       <c r="E154" s="15" t="n">
-        <v>0.0068</v>
+        <v>0.0107</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>921000</v>
+        <v>1175700</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H154" t="n">
-        <v>52.04</v>
+        <v>49.12</v>
       </c>
       <c r="I154" s="17" t="inlineStr">
         <is>
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.742</v>
+        <v>3.803</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.708</v>
+        <v>3.742</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7427,39 +7427,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0098</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>AUMAS</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>0.64</v>
+        <v>0.355</v>
       </c>
       <c r="E155" s="16" t="n">
-        <v>0</v>
+        <v>-0.0274</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>909700</v>
+        <v>1174000</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.18</v>
+        <v>0.98</v>
       </c>
       <c r="H155" t="n">
-        <v>39.59</v>
-      </c>
-      <c r="I155" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.79</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>0.715</v>
+        <v>0.347</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.358</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7472,39 +7472,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>T7GLOBAL</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="E156" s="15" t="n">
-        <v>0.0022</v>
+        <v>0.225</v>
+      </c>
+      <c r="E156" s="16" t="n">
+        <v>-0.0426</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>904600</v>
+        <v>1170500</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.18</v>
+        <v>2.22</v>
       </c>
       <c r="H156" t="n">
-        <v>59.57</v>
-      </c>
-      <c r="I156" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.54</v>
+      </c>
+      <c r="I156" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>4.432</v>
+        <v>0.244</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>4.44</v>
+        <v>0.259</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7517,39 +7517,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>4.46</v>
+        <v>0.25</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>-0.004500000000000001</v>
+        <v>0</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>900200</v>
+        <v>1156100</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H157" t="n">
-        <v>37.41</v>
-      </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.23</v>
+      </c>
+      <c r="I157" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>4.559</v>
+        <v>0.264</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>4.64</v>
+        <v>0.284</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7562,39 +7562,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>1.23</v>
+        <v>0.33</v>
       </c>
       <c r="E158" s="15" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0645</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>895300</v>
+        <v>1125300</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.12</v>
+        <v>5.95</v>
       </c>
       <c r="H158" t="n">
-        <v>41.01</v>
-      </c>
-      <c r="I158" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.2</v>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>1.273</v>
+        <v>0.306</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>1.316</v>
+        <v>0.295</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7607,39 +7607,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E159" s="15" t="n">
-        <v>0.0124</v>
+        <v>1.38</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>867200</v>
+        <v>1063100</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>1.25</v>
+        <v>0.53</v>
       </c>
       <c r="H159" t="n">
-        <v>32.56</v>
-      </c>
-      <c r="I159" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.09</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.716</v>
+        <v>1.367</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.77</v>
+        <v>1.346</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7652,39 +7652,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="E160" s="15" t="n">
-        <v>0.0076</v>
+        <v>2.09</v>
+      </c>
+      <c r="E160" s="16" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>864500</v>
+        <v>1045300</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="H160" t="n">
-        <v>54.33</v>
-      </c>
-      <c r="I160" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.43</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>10.455</v>
+        <v>2.104</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>9.869999999999999</v>
+        <v>2.108</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7697,39 +7697,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E161" s="16" t="n">
-        <v>0</v>
+        <v>5.09</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>0.02</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>829300</v>
+        <v>1029200</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="H161" t="n">
-        <v>34.33</v>
-      </c>
-      <c r="I161" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.95</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>0.952</v>
+        <v>5.059</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>1.033</v>
+        <v>5.037</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7742,39 +7742,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>-0.0061</v>
+        <v>0.64</v>
+      </c>
+      <c r="E162" s="15" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>819100</v>
+        <v>1004000</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.33</v>
+        <v>0.96</v>
       </c>
       <c r="H162" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="I162" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.09</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>0.832</v>
+        <v>0.634</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>0.856</v>
+        <v>0.632</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7787,39 +7787,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>-0.004699999999999999</v>
+        <v>1.64</v>
+      </c>
+      <c r="E163" s="15" t="n">
+        <v>0.0186</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>814900</v>
+        <v>1000000</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="H163" t="n">
-        <v>49.24</v>
-      </c>
-      <c r="I163" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.56</v>
+      </c>
+      <c r="I163" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>2.105</v>
+        <v>1.717</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>2.109</v>
+        <v>1.77</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7832,39 +7832,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E164" s="16" t="n">
-        <v>0</v>
+        <v>0.745</v>
+      </c>
+      <c r="E164" s="15" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>805000</v>
+        <v>993600</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.77</v>
+        <v>0.33</v>
       </c>
       <c r="H164" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I164" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.04</v>
+      </c>
+      <c r="I164" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>0.633</v>
+        <v>0.742</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>0.632</v>
+        <v>0.708</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7877,28 +7877,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E165" s="15" t="n">
-        <v>0.0396</v>
+        <v>0.925</v>
+      </c>
+      <c r="E165" s="16" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>795200</v>
+        <v>972300</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="H165" t="n">
-        <v>37.9</v>
+        <v>32.97</v>
       </c>
       <c r="I165" s="17" t="inlineStr">
         <is>
@@ -7906,10 +7906,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.128</v>
+        <v>0.951</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>1.255</v>
+        <v>1.033</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7922,39 +7922,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E166" s="15" t="n">
-        <v>0.0294</v>
+        <v>0.71</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>794600</v>
+        <v>948200</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.39</v>
+        <v>0.55</v>
       </c>
       <c r="H166" t="n">
-        <v>47.21</v>
-      </c>
-      <c r="I166" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.96</v>
+      </c>
+      <c r="I166" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>1.069</v>
+        <v>0.722</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>1.087</v>
+        <v>0.739</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7967,39 +7967,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>3.59</v>
+        <v>10.52</v>
       </c>
       <c r="E167" s="15" t="n">
-        <v>0.0141</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>786500</v>
+        <v>948100</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.57</v>
+        <v>0.26</v>
       </c>
       <c r="H167" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="I167" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.97</v>
+      </c>
+      <c r="I167" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>3.535</v>
+        <v>10.453</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>3.577</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8012,28 +8012,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="E168" s="15" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>884400</v>
+      </c>
+      <c r="G168" s="12" t="n">
         <v>0.64</v>
       </c>
-      <c r="E168" s="10" t="n">
-        <v>-0.007800000000000001</v>
-      </c>
-      <c r="F168" s="11" t="n">
-        <v>730100</v>
-      </c>
-      <c r="G168" s="12" t="n">
-        <v>0.34</v>
-      </c>
       <c r="H168" t="n">
-        <v>51.65</v>
+        <v>56.45</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8041,10 +8041,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.64</v>
+        <v>3.535</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.628</v>
+        <v>3.577</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8057,28 +8057,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="E169" s="10" t="n">
-        <v>-0.0027</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>728500</v>
+        <v>883600</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="H169" t="n">
-        <v>46.79</v>
+        <v>30.9</v>
       </c>
       <c r="I169" s="17" t="inlineStr">
         <is>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>3.798</v>
+        <v>0.832</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>3.741</v>
+        <v>0.856</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8102,39 +8102,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="E170" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0294</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>705600</v>
+        <v>880300</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="H170" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="I170" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.21</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.09</v>
+        <v>1.069</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>0.962</v>
+        <v>1.087</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8147,28 +8147,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>YTLREIT</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>2.81</v>
+        <v>0.96</v>
       </c>
       <c r="E171" s="16" t="n">
-        <v>0</v>
+        <v>-0.0052</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>694100</v>
+        <v>858300</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.53</v>
+        <v>1.8</v>
       </c>
       <c r="H171" t="n">
-        <v>33.28</v>
+        <v>38.92</v>
       </c>
       <c r="I171" s="17" t="inlineStr">
         <is>
@@ -8176,10 +8176,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>2.883</v>
+        <v>0.973</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>3.023</v>
+        <v>0.992</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8192,39 +8192,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E172" s="16" t="n">
-        <v>0</v>
+        <v>1.06</v>
+      </c>
+      <c r="E172" s="15" t="n">
+        <v>0.0495</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>679200</v>
+        <v>854200</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="H172" t="n">
-        <v>48.29</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.17</v>
+      </c>
+      <c r="I172" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>0.891</v>
+        <v>1.129</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>0.903</v>
+        <v>1.256</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8237,28 +8237,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E173" s="15" t="n">
-        <v>0.0458</v>
+        <v>8.4</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>674400</v>
+        <v>842100</v>
       </c>
       <c r="G173" s="12" t="n">
         <v>0.35</v>
       </c>
       <c r="H173" t="n">
-        <v>42.04</v>
+        <v>45.25</v>
       </c>
       <c r="I173" s="17" t="inlineStr">
         <is>
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>8.557</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>0.878</v>
+        <v>8.667999999999999</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8282,28 +8282,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E174" s="10" t="n">
-        <v>-0.0034</v>
+        <v>5.3</v>
+      </c>
+      <c r="E174" s="15" t="n">
+        <v>0.0095</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>669700</v>
+        <v>839400</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="H174" t="n">
-        <v>47.57</v>
+        <v>34.95</v>
       </c>
       <c r="I174" s="17" t="inlineStr">
         <is>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>2.986</v>
+        <v>5.466</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>2.861</v>
+        <v>5.738</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8327,39 +8327,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>GESHEN</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>4.23</v>
+        <v>1.38</v>
       </c>
       <c r="E175" s="15" t="n">
-        <v>0.0024</v>
+        <v>0.104</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>641800</v>
+        <v>823900</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.15</v>
+        <v>3.03</v>
       </c>
       <c r="H175" t="n">
-        <v>37.91</v>
-      </c>
-      <c r="I175" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.98999999999999</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>4.331</v>
+        <v>1.165</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>4.624</v>
+        <v>1.192</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8372,28 +8372,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E176" s="10" t="n">
-        <v>-0.0072</v>
+        <v>1.17</v>
+      </c>
+      <c r="E176" s="15" t="n">
+        <v>0.0174</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>637000</v>
+        <v>820700</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>1.04</v>
+        <v>0.17</v>
       </c>
       <c r="H176" t="n">
-        <v>56.44</v>
+        <v>61.26</v>
       </c>
       <c r="I176" s="17" t="inlineStr">
         <is>
@@ -8401,10 +8401,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>1.091</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>0.663</v>
+        <v>0.962</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8417,39 +8417,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>1.39</v>
+        <v>0.8</v>
       </c>
       <c r="E177" s="15" t="n">
-        <v>0.112</v>
+        <v>0.0458</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>627500</v>
+        <v>796400</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>2.31</v>
+        <v>0.42</v>
       </c>
       <c r="H177" t="n">
-        <v>77.52</v>
-      </c>
-      <c r="I177" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.04</v>
+      </c>
+      <c r="I177" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>1.166</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>1.192</v>
+        <v>0.878</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8462,28 +8462,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E178" s="15" t="n">
-        <v>0.0283</v>
+        <v>7.87</v>
+      </c>
+      <c r="E178" s="16" t="n">
+        <v>-0.0038</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>608800</v>
+        <v>753500</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H178" t="n">
-        <v>44.84</v>
+        <v>46.65</v>
       </c>
       <c r="I178" s="17" t="inlineStr">
         <is>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.556</v>
+        <v>7.914</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.591</v>
+        <v>7.933</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8507,39 +8507,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="E179" s="15" t="n">
-        <v>0.0145</v>
+        <v>2.81</v>
+      </c>
+      <c r="E179" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>606900</v>
+        <v>748200</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.21</v>
+        <v>0.58</v>
       </c>
       <c r="H179" t="n">
-        <v>57.06</v>
-      </c>
-      <c r="I179" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.28</v>
+      </c>
+      <c r="I179" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>2.724</v>
+        <v>2.883</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>2.361</v>
+        <v>3.023</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8552,39 +8552,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E180" s="15" t="n">
-        <v>0.0116</v>
+        <v>0.64</v>
+      </c>
+      <c r="E180" s="16" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>592900</v>
+        <v>735100</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="H180" t="n">
-        <v>43.72</v>
-      </c>
-      <c r="I180" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.65</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>1.753</v>
+        <v>0.64</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>1.854</v>
+        <v>0.628</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8597,39 +8597,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="E181" s="10" t="n">
-        <v>-0.0013</v>
+        <v>0.9</v>
+      </c>
+      <c r="E181" s="15" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>588200</v>
+        <v>730800</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="H181" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="I181" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.84</v>
+      </c>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>7.915</v>
+        <v>0.892</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>7.933</v>
+        <v>0.903</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8642,39 +8642,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="E182" s="10" t="n">
-        <v>-0.0129</v>
+        <v>2.77</v>
+      </c>
+      <c r="E182" s="15" t="n">
+        <v>0.0073</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>555400</v>
+        <v>722300</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H182" t="n">
-        <v>45.71</v>
-      </c>
-      <c r="I182" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.18</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>8.558</v>
+        <v>2.722</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>8.667999999999999</v>
+        <v>2.361</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8687,28 +8687,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="E183" s="15" t="n">
-        <v>0.0076</v>
+        <v>0.885</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>553400</v>
+        <v>720600</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.23</v>
+        <v>0.44</v>
       </c>
       <c r="H183" t="n">
-        <v>34.14</v>
+        <v>30.68</v>
       </c>
       <c r="I183" s="17" t="inlineStr">
         <is>
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>5.465</v>
+        <v>0.924</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>5.738</v>
+        <v>0.985</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8732,45 +8732,765 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="E184" s="10" t="n">
-        <v>-0.0053</v>
+        <v>4.23</v>
+      </c>
+      <c r="E184" s="15" t="n">
+        <v>0.0024</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>514300</v>
+        <v>713600</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H184" t="n">
-        <v>46.73</v>
-      </c>
-      <c r="I184" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.91</v>
+      </c>
+      <c r="I184" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>7.552</v>
+        <v>4.331</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>7.707</v>
+        <v>4.624</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="E185" s="16" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>709300</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H185" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>7.552</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>7.707</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E186" s="16" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>707000</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H186" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="I186" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E187" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>705600</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H187" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="I187" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>2.987</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>2.862</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E188" s="15" t="n">
+        <v>0.04650000000000001</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>698100</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H188" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="I188" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>691000</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H189" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E190" s="15" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>632700</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H190" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="I190" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E191" s="15" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>630800</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H191" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="I191" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E192" s="15" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>597900</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H192" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="I192" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>7235</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SUPERLN</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E193" s="15" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>583100</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H193" t="n">
+        <v>62.29</v>
+      </c>
+      <c r="I193" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>MALAKOF</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E194" s="15" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>559300</v>
+      </c>
+      <c r="G194" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H194" t="n">
+        <v>51.38</v>
+      </c>
+      <c r="I194" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J194" s="9" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K194" s="9" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="14" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="E195" s="16" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>557200</v>
+      </c>
+      <c r="G195" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H195" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="I195" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J195" s="9" t="n">
+        <v>3.312</v>
+      </c>
+      <c r="K195" s="9" t="n">
+        <v>3.547</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" s="14" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>7163</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>PJBUMI</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="E196" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="11" t="n">
+        <v>556300</v>
+      </c>
+      <c r="G196" s="12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H196" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="I196" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J196" s="9" t="n">
+        <v>4.175</v>
+      </c>
+      <c r="K196" s="9" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" s="14" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>5916</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E197" s="16" t="n">
+        <v>-0.0184</v>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>551300</v>
+      </c>
+      <c r="G197" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H197" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="I197" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J197" s="9" t="n">
+        <v>1.644</v>
+      </c>
+      <c r="K197" s="9" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" s="14" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="E198" s="16" t="n">
+        <v>-0.004500000000000001</v>
+      </c>
+      <c r="F198" s="11" t="n">
+        <v>536200</v>
+      </c>
+      <c r="G198" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H198" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="I198" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J198" s="9" t="n">
+        <v>13.079</v>
+      </c>
+      <c r="K198" s="9" t="n">
+        <v>13.315</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" s="14" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="E199" s="15" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F199" s="11" t="n">
+        <v>527200</v>
+      </c>
+      <c r="G199" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H199" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="I199" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J199" s="9" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="K199" s="9" t="n">
+        <v>5.378</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" s="14" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>3859</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>MAGNUM</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E200" s="16" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F200" s="11" t="n">
+        <v>517800</v>
+      </c>
+      <c r="G200" s="12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H200" t="n">
+        <v>37.57</v>
+      </c>
+      <c r="I200" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J200" s="9" t="n">
+        <v>1.181</v>
+      </c>
+      <c r="K200" s="9" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M184"/>
+  <autoFilter ref="A1:M200"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>